--- a/data/Herrnhuter NaturkundlerInnen.xlsx
+++ b/data/Herrnhuter NaturkundlerInnen.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29825"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tudresdende-my.sharepoint.com/personal/s5468259_tu-dresden_de/Documents/Herrnhut BMBF/Personenlexikon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10246" documentId="11_7EEC7FA32A5B5C2B1F465E45D27E15B46640A7DA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B90F128-AD06-4495-84E2-E339D32A0E8F}"/>
+  <xr:revisionPtr revIDLastSave="10249" documentId="11_7EEC7FA32A5B5C2B1F465E45D27E15B46640A7DA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{296827EC-1C4C-4404-9C5F-4208FCE6884E}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="14100" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7319" uniqueCount="4068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7319" uniqueCount="4069">
   <si>
     <t>interessante Belege in DR</t>
   </si>
@@ -6969,7 +6969,8 @@
     </r>
   </si>
   <si>
-    <t>Spalte1</t>
+    <t>Name - Vorzugsname
+String</t>
   </si>
   <si>
     <r>
@@ -13017,6 +13018,9 @@
       </rPr>
       <t>String</t>
     </r>
+  </si>
+  <si>
+    <t>Spalte1</t>
   </si>
   <si>
     <t>Ludwig Becker: "Die Pflege der Naturwissenschaften in der Herrnhuter Brüdergemeine", in: Unitas Fratrum 55/56 (2005), S. 17-51.</t>
@@ -15831,7 +15835,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="282">
+  <cellXfs count="277">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -16613,25 +16617,10 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="126">
     <dxf>
@@ -19007,7 +18996,7 @@
   <tableColumns count="68">
     <tableColumn id="1" xr3:uid="{87B4D233-19A0-4A0B-A3FE-D4C957CA22D0}" name="ID*_x000a_P-ID" dataDxfId="123"/>
     <tableColumn id="41" xr3:uid="{EA6CA05C-727B-4A80-87B6-D97BA12EA08D}" name="Übernahme in Personenlexikon*_x000a_Boolean" dataDxfId="122"/>
-    <tableColumn id="2" xr3:uid="{35F418E0-703B-4AFF-9B1A-35C077C4198A}" name="Spalte1" dataDxfId="121"/>
+    <tableColumn id="2" xr3:uid="{35F418E0-703B-4AFF-9B1A-35C077C4198A}" name="Name - Vorzugsname_x000a_String" dataDxfId="121"/>
     <tableColumn id="3" xr3:uid="{B31E0A8E-4A9F-4EF1-9C3F-6BF09701A924}" name="Name - Nachname(n)_x000a_String" dataDxfId="120"/>
     <tableColumn id="69" xr3:uid="{F15A3F8F-AF45-491B-B8FB-B9F7807C48AD}" name="Name - Geburtsname(n)_x000a_String" dataDxfId="119"/>
     <tableColumn id="4" xr3:uid="{15C6DC36-C9D1-42D6-9302-7F6E18EE4A99}" name="Name - Vorname(n)_x000a_String" dataDxfId="118"/>
@@ -19652,7 +19641,7 @@
         <v>3079</v>
       </c>
       <c r="E1" s="119" t="s">
-        <v>1957</v>
+        <v>3390</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="32.25">
@@ -19660,7 +19649,7 @@
         <v>2855</v>
       </c>
       <c r="B2" s="126" t="s">
-        <v>3390</v>
+        <v>3391</v>
       </c>
       <c r="C2" s="182"/>
       <c r="D2" s="126"/>
@@ -19668,10 +19657,10 @@
     </row>
     <row r="3" spans="1:5" ht="32.25">
       <c r="A3" s="182" t="s">
-        <v>3391</v>
+        <v>3392</v>
       </c>
       <c r="B3" s="126" t="s">
-        <v>3392</v>
+        <v>3393</v>
       </c>
       <c r="C3" s="182"/>
       <c r="D3" s="126"/>
@@ -19679,25 +19668,25 @@
     </row>
     <row r="4" spans="1:5" ht="48.75">
       <c r="A4" s="182" t="s">
-        <v>3393</v>
+        <v>3394</v>
       </c>
       <c r="B4" s="126" t="s">
-        <v>3394</v>
+        <v>3395</v>
       </c>
       <c r="C4" s="183" t="s">
-        <v>3395</v>
+        <v>3396</v>
       </c>
       <c r="D4" s="126" t="s">
-        <v>3396</v>
+        <v>3397</v>
       </c>
       <c r="E4" s="182"/>
     </row>
     <row r="5" spans="1:5" ht="32.25">
       <c r="A5" s="182" t="s">
-        <v>3397</v>
+        <v>3398</v>
       </c>
       <c r="B5" s="126" t="s">
-        <v>3398</v>
+        <v>3399</v>
       </c>
       <c r="C5" s="182"/>
       <c r="D5" s="126"/>
@@ -19708,7 +19697,7 @@
         <v>2271</v>
       </c>
       <c r="B6" s="126" t="s">
-        <v>3399</v>
+        <v>3400</v>
       </c>
       <c r="C6" s="182"/>
       <c r="D6" s="126"/>
@@ -19716,13 +19705,13 @@
     </row>
     <row r="7" spans="1:5" ht="32.25">
       <c r="A7" s="182" t="s">
-        <v>3400</v>
+        <v>3401</v>
       </c>
       <c r="B7" s="126" t="s">
-        <v>3401</v>
+        <v>3402</v>
       </c>
       <c r="C7" s="184" t="s">
-        <v>3402</v>
+        <v>3403</v>
       </c>
       <c r="D7" s="126"/>
       <c r="E7" s="182"/>
@@ -19732,19 +19721,19 @@
         <v>2058</v>
       </c>
       <c r="B8" s="126" t="s">
-        <v>3403</v>
+        <v>3404</v>
       </c>
       <c r="C8" s="183" t="s">
-        <v>3404</v>
+        <v>3405</v>
       </c>
       <c r="D8" s="182" t="s">
-        <v>3405</v>
+        <v>3406</v>
       </c>
       <c r="E8" s="182"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="182" t="s">
-        <v>3406</v>
+        <v>3407</v>
       </c>
       <c r="B9" s="126"/>
       <c r="C9" s="61"/>
@@ -19753,13 +19742,13 @@
     </row>
     <row r="10" spans="1:5" ht="16.5">
       <c r="A10" s="182" t="s">
-        <v>3407</v>
+        <v>3408</v>
       </c>
       <c r="B10" s="126" t="s">
-        <v>3408</v>
+        <v>3409</v>
       </c>
       <c r="C10" s="183" t="s">
-        <v>3409</v>
+        <v>3410</v>
       </c>
       <c r="D10" s="126"/>
       <c r="E10" s="182"/>
@@ -19769,23 +19758,23 @@
         <v>2036</v>
       </c>
       <c r="B11" s="126" t="s">
-        <v>3410</v>
+        <v>3411</v>
       </c>
       <c r="C11" s="183" t="s">
-        <v>3411</v>
+        <v>3412</v>
       </c>
       <c r="D11" s="126"/>
       <c r="E11" s="182"/>
     </row>
     <row r="12" spans="1:5" ht="32.25">
       <c r="A12" s="182" t="s">
-        <v>3412</v>
+        <v>3413</v>
       </c>
       <c r="B12" s="126" t="s">
-        <v>3413</v>
+        <v>3414</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>3414</v>
+        <v>3415</v>
       </c>
       <c r="D12" s="126"/>
       <c r="E12" s="182"/>
@@ -19795,37 +19784,37 @@
         <v>2768</v>
       </c>
       <c r="B13" s="126" t="s">
-        <v>3415</v>
+        <v>3416</v>
       </c>
       <c r="C13" s="183" t="s">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="D13" s="126" t="s">
-        <v>3417</v>
+        <v>3418</v>
       </c>
       <c r="E13" s="182"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="182" t="s">
-        <v>3418</v>
+        <v>3419</v>
       </c>
       <c r="B14" s="126" t="s">
-        <v>3419</v>
+        <v>3420</v>
       </c>
       <c r="C14" s="183" t="s">
-        <v>3420</v>
+        <v>3421</v>
       </c>
       <c r="D14" s="126" t="s">
-        <v>3421</v>
+        <v>3422</v>
       </c>
       <c r="E14" s="182"/>
     </row>
     <row r="15" spans="1:5" ht="32.25">
       <c r="A15" s="182" t="s">
-        <v>3422</v>
+        <v>3423</v>
       </c>
       <c r="B15" s="126" t="s">
-        <v>3423</v>
+        <v>3424</v>
       </c>
       <c r="C15" s="182"/>
       <c r="D15" s="126"/>
@@ -19836,22 +19825,22 @@
         <v>2029</v>
       </c>
       <c r="B16" s="126" t="s">
-        <v>3424</v>
+        <v>3425</v>
       </c>
       <c r="C16" s="242" t="s">
-        <v>3425</v>
+        <v>3426</v>
       </c>
       <c r="D16" s="126" t="s">
-        <v>3426</v>
+        <v>3427</v>
       </c>
       <c r="E16" s="182"/>
     </row>
     <row r="17" spans="1:5" ht="32.25">
       <c r="A17" s="182" t="s">
-        <v>3427</v>
+        <v>3428</v>
       </c>
       <c r="B17" s="126" t="s">
-        <v>3428</v>
+        <v>3429</v>
       </c>
       <c r="C17" s="182"/>
       <c r="D17" s="126"/>
@@ -19859,16 +19848,16 @@
     </row>
     <row r="18" spans="1:5" ht="64.5">
       <c r="A18" s="182" t="s">
-        <v>3429</v>
+        <v>3430</v>
       </c>
       <c r="B18" s="126" t="s">
-        <v>3430</v>
+        <v>3431</v>
       </c>
       <c r="C18" s="183" t="s">
-        <v>3431</v>
+        <v>3432</v>
       </c>
       <c r="D18" s="126" t="s">
-        <v>3432</v>
+        <v>3433</v>
       </c>
       <c r="E18" s="182"/>
     </row>
@@ -19881,17 +19870,17 @@
     </row>
     <row r="20" spans="1:5" ht="32.25">
       <c r="A20" s="257" t="s">
-        <v>3433</v>
+        <v>3434</v>
       </c>
       <c r="B20" s="126" t="s">
-        <v>3434</v>
+        <v>3435</v>
       </c>
       <c r="C20" s="183" t="s">
-        <v>3435</v>
+        <v>3436</v>
       </c>
       <c r="D20" s="126"/>
       <c r="E20" s="183" t="s">
-        <v>3436</v>
+        <v>3437</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="32.25">
@@ -19899,43 +19888,43 @@
         <v>2839</v>
       </c>
       <c r="B21" s="126" t="s">
-        <v>3437</v>
+        <v>3438</v>
       </c>
       <c r="C21" s="183" t="s">
-        <v>3438</v>
+        <v>3439</v>
       </c>
       <c r="D21" s="126" t="s">
-        <v>3439</v>
+        <v>3440</v>
       </c>
       <c r="E21" s="182"/>
     </row>
     <row r="22" spans="1:5" ht="48.75">
       <c r="A22" s="257" t="s">
-        <v>3440</v>
+        <v>3441</v>
       </c>
       <c r="B22" s="126" t="s">
-        <v>3441</v>
+        <v>3442</v>
       </c>
       <c r="C22" s="183" t="s">
-        <v>3442</v>
+        <v>3443</v>
       </c>
       <c r="D22" s="126" t="s">
-        <v>3443</v>
+        <v>3444</v>
       </c>
       <c r="E22" s="182"/>
     </row>
     <row r="23" spans="1:5" ht="32.25">
       <c r="A23" s="257" t="s">
-        <v>3444</v>
+        <v>3445</v>
       </c>
       <c r="B23" s="126" t="s">
-        <v>3445</v>
+        <v>3446</v>
       </c>
       <c r="C23" s="183" t="s">
-        <v>3446</v>
+        <v>3447</v>
       </c>
       <c r="D23" s="126" t="s">
-        <v>3447</v>
+        <v>3448</v>
       </c>
       <c r="E23" s="182"/>
     </row>
@@ -19947,22 +19936,22 @@
         <v>752</v>
       </c>
       <c r="C24" s="183" t="s">
-        <v>3448</v>
+        <v>3449</v>
       </c>
       <c r="D24" s="126"/>
       <c r="E24" s="183" t="s">
-        <v>3449</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="48.75">
       <c r="A25" s="257" t="s">
-        <v>3450</v>
+        <v>3451</v>
       </c>
       <c r="B25" s="126" t="s">
-        <v>3451</v>
+        <v>3452</v>
       </c>
       <c r="C25" s="183" t="s">
-        <v>3452</v>
+        <v>3453</v>
       </c>
       <c r="D25" s="126"/>
       <c r="E25" s="182"/>
@@ -19972,91 +19961,91 @@
         <v>2140</v>
       </c>
       <c r="B26" s="195" t="s">
-        <v>3453</v>
+        <v>3454</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>3454</v>
+        <v>3455</v>
       </c>
       <c r="D26" s="126"/>
       <c r="E26" s="183" t="s">
-        <v>3455</v>
+        <v>3456</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="64.5">
       <c r="A27" s="257" t="s">
-        <v>3456</v>
+        <v>3457</v>
       </c>
       <c r="B27" s="126" t="s">
-        <v>3457</v>
+        <v>3458</v>
       </c>
       <c r="C27" s="183" t="s">
-        <v>3458</v>
+        <v>3459</v>
       </c>
       <c r="D27" s="126" t="s">
-        <v>3459</v>
+        <v>3460</v>
       </c>
       <c r="E27" s="183" t="s">
-        <v>3460</v>
+        <v>3461</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="32.25">
       <c r="A28" s="257" t="s">
-        <v>3461</v>
+        <v>3462</v>
       </c>
       <c r="B28" s="126" t="s">
-        <v>3462</v>
+        <v>3463</v>
       </c>
       <c r="C28" s="183" t="s">
-        <v>3463</v>
+        <v>3464</v>
       </c>
       <c r="D28" s="126"/>
       <c r="E28" s="182"/>
     </row>
     <row r="29" spans="1:5" ht="32.25">
       <c r="A29" s="257" t="s">
-        <v>3464</v>
+        <v>3465</v>
       </c>
       <c r="B29" s="126" t="s">
-        <v>3465</v>
+        <v>3466</v>
       </c>
       <c r="C29" s="182"/>
       <c r="D29" s="126" t="s">
-        <v>3466</v>
+        <v>3467</v>
       </c>
       <c r="E29" s="182"/>
     </row>
     <row r="30" spans="1:5" ht="32.25">
       <c r="A30" s="257" t="s">
-        <v>3467</v>
+        <v>3468</v>
       </c>
       <c r="B30" s="126" t="s">
-        <v>3468</v>
+        <v>3469</v>
       </c>
       <c r="C30" s="182"/>
       <c r="D30" s="126" t="s">
-        <v>3469</v>
+        <v>3470</v>
       </c>
       <c r="E30" s="182"/>
     </row>
     <row r="31" spans="1:5" ht="48.75">
       <c r="A31" s="257" t="s">
-        <v>3470</v>
+        <v>3471</v>
       </c>
       <c r="B31" s="126" t="s">
-        <v>3471</v>
+        <v>3472</v>
       </c>
       <c r="C31" s="182"/>
       <c r="D31" s="126" t="s">
-        <v>3469</v>
+        <v>3470</v>
       </c>
       <c r="E31" s="182"/>
     </row>
     <row r="32" spans="1:5" ht="48.75">
       <c r="A32" s="257" t="s">
-        <v>3472</v>
+        <v>3473</v>
       </c>
       <c r="B32" s="126" t="s">
-        <v>3473</v>
+        <v>3474</v>
       </c>
       <c r="C32" s="182"/>
       <c r="D32" s="126"/>
@@ -20067,10 +20056,10 @@
         <v>2165</v>
       </c>
       <c r="B33" s="126" t="s">
-        <v>3474</v>
+        <v>3475</v>
       </c>
       <c r="C33" s="183" t="s">
-        <v>3475</v>
+        <v>3476</v>
       </c>
       <c r="D33" s="126"/>
       <c r="E33" s="182"/>
@@ -20080,40 +20069,40 @@
         <v>2856</v>
       </c>
       <c r="B34" s="276" t="s">
-        <v>3476</v>
+        <v>3477</v>
       </c>
       <c r="C34" s="183" t="s">
-        <v>3477</v>
+        <v>3478</v>
       </c>
       <c r="D34" t="s">
-        <v>3478</v>
+        <v>3479</v>
       </c>
       <c r="E34" s="182"/>
     </row>
     <row r="35" spans="1:5" ht="16.5">
       <c r="A35" s="257" t="s">
-        <v>3479</v>
+        <v>3480</v>
       </c>
       <c r="B35" s="276" t="s">
-        <v>3480</v>
+        <v>3481</v>
       </c>
       <c r="C35" s="183" t="s">
-        <v>3481</v>
+        <v>3482</v>
       </c>
       <c r="D35" s="126" t="s">
-        <v>3482</v>
+        <v>3483</v>
       </c>
       <c r="E35" s="182"/>
     </row>
     <row r="36" spans="1:5" ht="32.25">
       <c r="A36" s="257" t="s">
-        <v>3483</v>
+        <v>3484</v>
       </c>
       <c r="B36" s="126" t="s">
-        <v>3484</v>
+        <v>3485</v>
       </c>
       <c r="C36" s="183" t="s">
-        <v>3485</v>
+        <v>3486</v>
       </c>
       <c r="D36" s="126"/>
       <c r="E36" s="182"/>
@@ -20123,39 +20112,39 @@
         <v>2447</v>
       </c>
       <c r="B37" s="126" t="s">
-        <v>3486</v>
+        <v>3487</v>
       </c>
       <c r="C37" s="182"/>
       <c r="D37" s="126" t="s">
-        <v>3487</v>
+        <v>3488</v>
       </c>
       <c r="E37" s="182"/>
     </row>
     <row r="38" spans="1:5" ht="48.75">
       <c r="A38" s="182" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="B38" s="126" t="s">
-        <v>3489</v>
+        <v>3490</v>
       </c>
       <c r="C38" s="182"/>
       <c r="D38" s="126" t="s">
-        <v>3490</v>
+        <v>3491</v>
       </c>
       <c r="E38" s="182"/>
     </row>
     <row r="39" spans="1:5" ht="32.25">
       <c r="A39" s="257" t="s">
-        <v>3491</v>
+        <v>3492</v>
       </c>
       <c r="B39" s="126" t="s">
-        <v>3492</v>
+        <v>3493</v>
       </c>
       <c r="C39" s="183" t="s">
-        <v>3493</v>
+        <v>3494</v>
       </c>
       <c r="D39" s="126" t="s">
-        <v>3494</v>
+        <v>3495</v>
       </c>
       <c r="E39" s="182"/>
     </row>
@@ -20164,39 +20153,39 @@
         <v>2217</v>
       </c>
       <c r="B40" s="126" t="s">
-        <v>3495</v>
+        <v>3496</v>
       </c>
       <c r="C40" s="183" t="s">
-        <v>3496</v>
+        <v>3497</v>
       </c>
       <c r="D40" s="126"/>
       <c r="E40" s="182"/>
     </row>
     <row r="41" spans="1:5" ht="32.25">
       <c r="A41" s="257" t="s">
-        <v>3497</v>
+        <v>3498</v>
       </c>
       <c r="B41" s="126" t="s">
-        <v>3498</v>
+        <v>3499</v>
       </c>
       <c r="C41" s="182"/>
       <c r="D41" s="126" t="s">
-        <v>3499</v>
+        <v>3500</v>
       </c>
       <c r="E41" s="182"/>
     </row>
     <row r="42" spans="1:5" ht="32.25">
       <c r="A42" s="182" t="s">
-        <v>3500</v>
+        <v>3501</v>
       </c>
       <c r="B42" s="126" t="s">
-        <v>3501</v>
+        <v>3502</v>
       </c>
       <c r="C42" s="183" t="s">
-        <v>3502</v>
+        <v>3503</v>
       </c>
       <c r="D42" s="126" t="s">
-        <v>3503</v>
+        <v>3504</v>
       </c>
       <c r="E42" s="182"/>
     </row>
@@ -20205,17 +20194,17 @@
         <v>2742</v>
       </c>
       <c r="B43" s="126" t="s">
-        <v>3504</v>
+        <v>3505</v>
       </c>
       <c r="C43" s="182"/>
       <c r="D43" s="126" t="s">
-        <v>3505</v>
+        <v>3506</v>
       </c>
       <c r="E43" s="182"/>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="182" t="s">
-        <v>3506</v>
+        <v>3507</v>
       </c>
       <c r="B44" s="126"/>
       <c r="C44" s="182"/>
@@ -20224,38 +20213,38 @@
     </row>
     <row r="45" spans="1:5" ht="32.25">
       <c r="A45" s="257" t="s">
-        <v>3507</v>
+        <v>3508</v>
       </c>
       <c r="B45" s="126" t="s">
-        <v>3508</v>
+        <v>3509</v>
       </c>
       <c r="C45" s="183" t="s">
-        <v>3509</v>
+        <v>3510</v>
       </c>
       <c r="D45" s="126" t="s">
-        <v>3510</v>
+        <v>3511</v>
       </c>
       <c r="E45" s="182"/>
     </row>
     <row r="46" spans="1:5" ht="48.75">
       <c r="A46" s="182" t="s">
-        <v>3511</v>
+        <v>3512</v>
       </c>
       <c r="B46" s="126" t="s">
-        <v>3512</v>
+        <v>3513</v>
       </c>
       <c r="C46" s="182"/>
       <c r="D46" s="126" t="s">
-        <v>3513</v>
+        <v>3514</v>
       </c>
       <c r="E46" s="182"/>
     </row>
     <row r="47" spans="1:5" ht="32.25">
       <c r="A47" s="257" t="s">
-        <v>3514</v>
+        <v>3515</v>
       </c>
       <c r="B47" s="126" t="s">
-        <v>3515</v>
+        <v>3516</v>
       </c>
       <c r="C47" s="182"/>
       <c r="D47" s="126"/>
@@ -20266,11 +20255,11 @@
         <v>2294</v>
       </c>
       <c r="B48" s="126" t="s">
-        <v>3516</v>
+        <v>3517</v>
       </c>
       <c r="C48" s="182"/>
       <c r="D48" s="126" t="s">
-        <v>3517</v>
+        <v>3518</v>
       </c>
       <c r="E48" s="182"/>
     </row>
@@ -20279,11 +20268,11 @@
         <v>2356</v>
       </c>
       <c r="B49" s="126" t="s">
-        <v>3518</v>
+        <v>3519</v>
       </c>
       <c r="C49" s="182"/>
       <c r="D49" s="126" t="s">
-        <v>3519</v>
+        <v>3520</v>
       </c>
       <c r="E49" s="182"/>
     </row>
@@ -20348,16 +20337,16 @@
         <v>3388</v>
       </c>
       <c r="B1" s="118" t="s">
-        <v>3520</v>
+        <v>3521</v>
       </c>
       <c r="C1" s="118" t="s">
-        <v>3521</v>
+        <v>3522</v>
       </c>
       <c r="D1" s="120" t="s">
-        <v>3522</v>
+        <v>3523</v>
       </c>
       <c r="E1" s="118" t="s">
-        <v>3523</v>
+        <v>3524</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5">
@@ -20365,13 +20354,13 @@
         <v>3082</v>
       </c>
       <c r="B2" s="164" t="s">
-        <v>3524</v>
+        <v>3525</v>
       </c>
       <c r="C2" s="185" t="s">
-        <v>3525</v>
+        <v>3526</v>
       </c>
       <c r="D2" s="186" t="s">
-        <v>3526</v>
+        <v>3527</v>
       </c>
       <c r="E2" s="185"/>
     </row>
@@ -20380,24 +20369,24 @@
         <v>3096</v>
       </c>
       <c r="B3" s="181" t="s">
-        <v>3527</v>
+        <v>3528</v>
       </c>
       <c r="C3" s="185"/>
       <c r="D3" s="186" t="s">
-        <v>3528</v>
+        <v>3529</v>
       </c>
       <c r="E3" s="185"/>
     </row>
     <row r="4" spans="1:5" ht="32.25">
       <c r="A4" s="185" t="s">
-        <v>3529</v>
+        <v>3530</v>
       </c>
       <c r="B4" s="126" t="s">
-        <v>3530</v>
+        <v>3531</v>
       </c>
       <c r="C4" s="185"/>
       <c r="D4" s="186" t="s">
-        <v>3531</v>
+        <v>3532</v>
       </c>
       <c r="E4" s="185"/>
     </row>
@@ -20406,11 +20395,11 @@
         <v>3104</v>
       </c>
       <c r="B5" s="179" t="s">
-        <v>3532</v>
+        <v>3533</v>
       </c>
       <c r="C5" s="185"/>
       <c r="D5" s="186" t="s">
-        <v>3533</v>
+        <v>3534</v>
       </c>
       <c r="E5" s="185"/>
     </row>
@@ -20419,11 +20408,11 @@
         <v>2093</v>
       </c>
       <c r="B6" t="s">
-        <v>3534</v>
+        <v>3535</v>
       </c>
       <c r="C6" s="185"/>
       <c r="D6" s="186" t="s">
-        <v>3535</v>
+        <v>3536</v>
       </c>
       <c r="E6" s="185"/>
     </row>
@@ -20432,13 +20421,13 @@
         <v>3115</v>
       </c>
       <c r="B7" s="185" t="s">
-        <v>3536</v>
+        <v>3537</v>
       </c>
       <c r="C7" s="185" t="s">
-        <v>3537</v>
+        <v>3538</v>
       </c>
       <c r="D7" s="186" t="s">
-        <v>3538</v>
+        <v>3539</v>
       </c>
       <c r="E7" s="185"/>
     </row>
@@ -20447,7 +20436,7 @@
         <v>3121</v>
       </c>
       <c r="B8" s="185" t="s">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="C8" s="185"/>
       <c r="D8" s="186"/>
@@ -20458,12 +20447,12 @@
         <v>2867</v>
       </c>
       <c r="B9" s="185" t="s">
-        <v>3540</v>
+        <v>3541</v>
       </c>
       <c r="C9" s="185"/>
       <c r="D9" s="186"/>
       <c r="E9" s="185" t="s">
-        <v>3541</v>
+        <v>3542</v>
       </c>
     </row>
   </sheetData>
@@ -20499,32 +20488,32 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16.5">
       <c r="A1" s="82" t="s">
-        <v>3542</v>
+        <v>3543</v>
       </c>
       <c r="B1" s="94" t="s">
-        <v>3543</v>
+        <v>3544</v>
       </c>
       <c r="C1" s="83" t="s">
-        <v>3544</v>
+        <v>3545</v>
       </c>
       <c r="D1" s="83" t="s">
-        <v>3545</v>
+        <v>3546</v>
       </c>
       <c r="E1" s="84" t="s">
-        <v>3546</v>
+        <v>3547</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="162">
       <c r="A2" s="85"/>
       <c r="B2" s="95"/>
       <c r="C2" s="86" t="s">
-        <v>3547</v>
+        <v>3548</v>
       </c>
       <c r="D2" s="86" t="s">
-        <v>3547</v>
+        <v>3548</v>
       </c>
       <c r="E2" s="87" t="s">
-        <v>3548</v>
+        <v>3549</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="48.75">
@@ -20535,13 +20524,13 @@
         <v>300008347</v>
       </c>
       <c r="C3" s="89" t="s">
-        <v>3549</v>
+        <v>3550</v>
       </c>
       <c r="D3" s="89" t="s">
-        <v>3550</v>
+        <v>3551</v>
       </c>
       <c r="E3" s="90" t="s">
-        <v>3551</v>
+        <v>3552</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="32.25">
@@ -20552,13 +20541,13 @@
         <v>300008389</v>
       </c>
       <c r="C4" s="88" t="s">
-        <v>3552</v>
+        <v>3553</v>
       </c>
       <c r="D4" s="88" t="s">
-        <v>3553</v>
+        <v>3554</v>
       </c>
       <c r="E4" s="90" t="s">
-        <v>3554</v>
+        <v>3555</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="32.25">
@@ -20569,13 +20558,13 @@
         <v>300008375</v>
       </c>
       <c r="C5" s="88" t="s">
-        <v>3555</v>
+        <v>3556</v>
       </c>
       <c r="D5" s="88" t="s">
-        <v>3556</v>
+        <v>3557</v>
       </c>
       <c r="E5" s="90" t="s">
-        <v>3557</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="32.25">
@@ -20586,13 +20575,13 @@
         <v>300008372</v>
       </c>
       <c r="C6" s="88" t="s">
-        <v>3558</v>
+        <v>3559</v>
       </c>
       <c r="D6" s="88" t="s">
-        <v>3559</v>
+        <v>3560</v>
       </c>
       <c r="E6" s="90" t="s">
-        <v>3560</v>
+        <v>3561</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="32.25">
@@ -20603,13 +20592,13 @@
         <v>300120599</v>
       </c>
       <c r="C7" s="88" t="s">
-        <v>3561</v>
+        <v>3562</v>
       </c>
       <c r="D7" s="88" t="s">
-        <v>3562</v>
+        <v>3563</v>
       </c>
       <c r="E7" s="90" t="s">
-        <v>3563</v>
+        <v>3564</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16.5">
@@ -20620,13 +20609,13 @@
         <v>300387272</v>
       </c>
       <c r="C8" s="88" t="s">
-        <v>3564</v>
+        <v>3565</v>
       </c>
       <c r="D8" s="88" t="s">
-        <v>3565</v>
+        <v>3566</v>
       </c>
       <c r="E8" s="90" t="s">
-        <v>3566</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="32.25">
@@ -20637,13 +20626,13 @@
         <v>300008537</v>
       </c>
       <c r="C9" s="88" t="s">
-        <v>3567</v>
+        <v>3568</v>
       </c>
       <c r="D9" s="88" t="s">
-        <v>3568</v>
+        <v>3569</v>
       </c>
       <c r="E9" s="90" t="s">
-        <v>3569</v>
+        <v>3570</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="16.5">
@@ -20654,13 +20643,13 @@
         <v>300387216</v>
       </c>
       <c r="C10" s="88" t="s">
-        <v>3570</v>
+        <v>3571</v>
       </c>
       <c r="D10" s="88" t="s">
-        <v>3571</v>
+        <v>3572</v>
       </c>
       <c r="E10" s="90" t="s">
-        <v>3572</v>
+        <v>3573</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="16.5">
@@ -20671,13 +20660,13 @@
         <v>300008542</v>
       </c>
       <c r="C11" s="88" t="s">
+        <v>3574</v>
+      </c>
+      <c r="D11" s="88" t="s">
+        <v>3575</v>
+      </c>
+      <c r="E11" s="90" t="s">
         <v>3573</v>
-      </c>
-      <c r="D11" s="88" t="s">
-        <v>3574</v>
-      </c>
-      <c r="E11" s="90" t="s">
-        <v>3572</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="16.5">
@@ -20688,13 +20677,13 @@
         <v>300167671</v>
       </c>
       <c r="C12" s="88" t="s">
-        <v>3575</v>
+        <v>3576</v>
       </c>
       <c r="D12" s="88" t="s">
-        <v>3576</v>
+        <v>3577</v>
       </c>
       <c r="E12" s="90" t="s">
-        <v>3577</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="48.75">
@@ -20705,13 +20694,13 @@
         <v>300387318</v>
       </c>
       <c r="C13" s="88" t="s">
-        <v>3578</v>
+        <v>3579</v>
       </c>
       <c r="D13" s="88" t="s">
-        <v>3579</v>
+        <v>3580</v>
       </c>
       <c r="E13" s="90" t="s">
-        <v>3580</v>
+        <v>3581</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="16.5">
@@ -20722,13 +20711,13 @@
         <v>300387326</v>
       </c>
       <c r="C14" s="88" t="s">
-        <v>3581</v>
+        <v>3582</v>
       </c>
       <c r="D14" s="88" t="s">
-        <v>3582</v>
+        <v>3583</v>
       </c>
       <c r="E14" s="90" t="s">
-        <v>3583</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="32.25">
@@ -20739,13 +20728,13 @@
         <v>300387203</v>
       </c>
       <c r="C15" s="88" t="s">
-        <v>3584</v>
+        <v>3585</v>
       </c>
       <c r="D15" s="88" t="s">
-        <v>3585</v>
+        <v>3586</v>
       </c>
       <c r="E15" s="90" t="s">
-        <v>3586</v>
+        <v>3587</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="16.5">
@@ -20756,26 +20745,26 @@
         <v>300387323</v>
       </c>
       <c r="C16" s="88" t="s">
-        <v>3587</v>
+        <v>3588</v>
       </c>
       <c r="D16" s="88" t="s">
-        <v>3588</v>
+        <v>3589</v>
       </c>
       <c r="E16" s="90" t="s">
-        <v>3589</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="32.25">
       <c r="A17" s="85"/>
       <c r="B17" s="95"/>
       <c r="C17" s="89" t="s">
-        <v>3590</v>
+        <v>3591</v>
       </c>
       <c r="D17" s="89" t="s">
-        <v>3590</v>
+        <v>3591</v>
       </c>
       <c r="E17" s="90" t="s">
-        <v>3591</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="48.75">
@@ -20786,13 +20775,13 @@
         <v>300182722</v>
       </c>
       <c r="C18" s="91" t="s">
-        <v>3592</v>
+        <v>3593</v>
       </c>
       <c r="D18" s="91" t="s">
-        <v>3593</v>
+        <v>3594</v>
       </c>
       <c r="E18" s="90" t="s">
-        <v>3594</v>
+        <v>3595</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="32.25">
@@ -20803,13 +20792,13 @@
         <v>300387178</v>
       </c>
       <c r="C19" s="88" t="s">
-        <v>3595</v>
+        <v>3596</v>
       </c>
       <c r="D19" s="88" t="s">
-        <v>3596</v>
+        <v>3597</v>
       </c>
       <c r="E19" s="90" t="s">
-        <v>3597</v>
+        <v>3598</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="16.5">
@@ -20820,26 +20809,26 @@
         <v>300387347</v>
       </c>
       <c r="C20" s="88" t="s">
-        <v>3598</v>
+        <v>3599</v>
       </c>
       <c r="D20" s="88" t="s">
-        <v>3599</v>
+        <v>3600</v>
       </c>
       <c r="E20" s="90" t="s">
-        <v>3600</v>
+        <v>3601</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="16.5">
       <c r="A21" s="85"/>
       <c r="B21" s="95"/>
       <c r="C21" s="89" t="s">
-        <v>3601</v>
+        <v>3602</v>
       </c>
       <c r="D21" s="89" t="s">
-        <v>3601</v>
+        <v>3602</v>
       </c>
       <c r="E21" s="90" t="s">
-        <v>3602</v>
+        <v>3603</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="32.25">
@@ -20850,13 +20839,13 @@
         <v>300387616</v>
       </c>
       <c r="C22" s="88" t="s">
-        <v>3603</v>
+        <v>3604</v>
       </c>
       <c r="D22" s="88" t="s">
-        <v>3604</v>
+        <v>3605</v>
       </c>
       <c r="E22" s="90" t="s">
-        <v>3605</v>
+        <v>3606</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="32.25">
@@ -20867,13 +20856,13 @@
         <v>300386114</v>
       </c>
       <c r="C23" s="88" t="s">
-        <v>3606</v>
+        <v>3607</v>
       </c>
       <c r="D23" s="88" t="s">
-        <v>3607</v>
+        <v>3608</v>
       </c>
       <c r="E23" s="90" t="s">
-        <v>3608</v>
+        <v>3609</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="32.25">
@@ -20882,13 +20871,13 @@
         <v>300261086</v>
       </c>
       <c r="C24" s="89" t="s">
-        <v>3609</v>
+        <v>3610</v>
       </c>
       <c r="D24" s="89" t="s">
-        <v>3610</v>
+        <v>3611</v>
       </c>
       <c r="E24" s="90" t="s">
-        <v>3611</v>
+        <v>3612</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="16.5">
@@ -20899,13 +20888,13 @@
         <v>300232420</v>
       </c>
       <c r="C25" s="91" t="s">
-        <v>3612</v>
+        <v>3613</v>
       </c>
       <c r="D25" s="91" t="s">
-        <v>3613</v>
+        <v>3614</v>
       </c>
       <c r="E25" s="90" t="s">
-        <v>3614</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="32.25">
@@ -20916,13 +20905,13 @@
         <v>300128207</v>
       </c>
       <c r="C26" s="88" t="s">
-        <v>3615</v>
+        <v>3616</v>
       </c>
       <c r="D26" s="88" t="s">
-        <v>3616</v>
+        <v>3617</v>
       </c>
       <c r="E26" s="90" t="s">
-        <v>3617</v>
+        <v>3618</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="16.5">
@@ -20933,13 +20922,13 @@
         <v>300403959</v>
       </c>
       <c r="C27" s="88" t="s">
-        <v>3618</v>
+        <v>3619</v>
       </c>
       <c r="D27" s="88" t="s">
-        <v>3619</v>
+        <v>3620</v>
       </c>
       <c r="E27" s="90" t="s">
-        <v>3620</v>
+        <v>3621</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="16.5">
@@ -20950,13 +20939,13 @@
         <v>300387062</v>
       </c>
       <c r="C28" s="88" t="s">
-        <v>3618</v>
+        <v>3619</v>
       </c>
       <c r="D28" s="88" t="s">
-        <v>3621</v>
+        <v>3622</v>
       </c>
       <c r="E28" s="90" t="s">
-        <v>3622</v>
+        <v>3623</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="32.25">
@@ -20967,13 +20956,13 @@
         <v>300387506</v>
       </c>
       <c r="C29" s="88" t="s">
-        <v>3623</v>
+        <v>3624</v>
       </c>
       <c r="D29" s="88" t="s">
-        <v>3624</v>
+        <v>3625</v>
       </c>
       <c r="E29" s="90" t="s">
-        <v>3625</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="32.25">
@@ -20984,13 +20973,13 @@
         <v>300128214</v>
       </c>
       <c r="C30" s="88" t="s">
-        <v>3626</v>
+        <v>3627</v>
       </c>
       <c r="D30" s="88" t="s">
-        <v>3627</v>
+        <v>3628</v>
       </c>
       <c r="E30" s="90" t="s">
-        <v>3628</v>
+        <v>3629</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="16.5">
@@ -21001,13 +20990,13 @@
         <v>300417385</v>
       </c>
       <c r="C31" s="88" t="s">
-        <v>3629</v>
+        <v>3630</v>
       </c>
       <c r="D31" s="88" t="s">
-        <v>3630</v>
+        <v>3631</v>
       </c>
       <c r="E31" s="90" t="s">
-        <v>3631</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="32.25">
@@ -21018,13 +21007,13 @@
         <v>300235114</v>
       </c>
       <c r="C32" s="91" t="s">
-        <v>3632</v>
+        <v>3633</v>
       </c>
       <c r="D32" s="91" t="s">
-        <v>3633</v>
+        <v>3634</v>
       </c>
       <c r="E32" s="90" t="s">
-        <v>3634</v>
+        <v>3635</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="32.25">
@@ -21035,13 +21024,13 @@
         <v>300387137</v>
       </c>
       <c r="C33" s="88" t="s">
-        <v>3635</v>
+        <v>3636</v>
       </c>
       <c r="D33" s="88" t="s">
-        <v>3636</v>
+        <v>3637</v>
       </c>
       <c r="E33" s="90" t="s">
-        <v>3637</v>
+        <v>3638</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="16.5">
@@ -21052,13 +21041,13 @@
         <v>300235118</v>
       </c>
       <c r="C34" s="88" t="s">
-        <v>3638</v>
+        <v>3639</v>
       </c>
       <c r="D34" s="88" t="s">
-        <v>3639</v>
+        <v>3640</v>
       </c>
       <c r="E34" s="90" t="s">
-        <v>3640</v>
+        <v>3641</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="32.25">
@@ -21069,13 +21058,13 @@
         <v>300235115</v>
       </c>
       <c r="C35" s="88" t="s">
-        <v>3641</v>
+        <v>3642</v>
       </c>
       <c r="D35" s="88" t="s">
-        <v>3642</v>
+        <v>3643</v>
       </c>
       <c r="E35" s="90" t="s">
-        <v>3643</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="16.5">
@@ -21086,13 +21075,13 @@
         <v>300412029</v>
       </c>
       <c r="C36" s="88" t="s">
-        <v>3644</v>
+        <v>3645</v>
       </c>
       <c r="D36" s="88" t="s">
-        <v>3645</v>
+        <v>3646</v>
       </c>
       <c r="E36" s="90" t="s">
-        <v>3646</v>
+        <v>3647</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="32.25">
@@ -21103,13 +21092,13 @@
         <v>300232418</v>
       </c>
       <c r="C37" s="91" t="s">
-        <v>3647</v>
+        <v>3648</v>
       </c>
       <c r="D37" s="91" t="s">
-        <v>3648</v>
+        <v>3649</v>
       </c>
       <c r="E37" s="90" t="s">
-        <v>3649</v>
+        <v>3650</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="16.5">
@@ -21120,13 +21109,13 @@
         <v>300236157</v>
       </c>
       <c r="C38" s="91" t="s">
-        <v>3650</v>
+        <v>3651</v>
       </c>
       <c r="D38" s="91" t="s">
-        <v>3651</v>
+        <v>3652</v>
       </c>
       <c r="E38" s="90" t="s">
-        <v>3652</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="32.25">
@@ -21137,13 +21126,13 @@
         <v>300000774</v>
       </c>
       <c r="C39" s="88" t="s">
-        <v>3653</v>
+        <v>3654</v>
       </c>
       <c r="D39" s="88" t="s">
-        <v>3654</v>
+        <v>3655</v>
       </c>
       <c r="E39" s="90" t="s">
-        <v>3655</v>
+        <v>3656</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="64.5">
@@ -21154,13 +21143,13 @@
         <v>300000771</v>
       </c>
       <c r="C40" s="88" t="s">
-        <v>3656</v>
+        <v>3657</v>
       </c>
       <c r="D40" s="88" t="s">
-        <v>3657</v>
+        <v>3658</v>
       </c>
       <c r="E40" s="90" t="s">
-        <v>3658</v>
+        <v>3659</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="32.25">
@@ -21171,13 +21160,13 @@
         <v>300000776</v>
       </c>
       <c r="C41" s="88" t="s">
-        <v>3659</v>
+        <v>3660</v>
       </c>
       <c r="D41" s="88" t="s">
-        <v>3660</v>
+        <v>3661</v>
       </c>
       <c r="E41" s="90" t="s">
-        <v>3661</v>
+        <v>3662</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="32.25">
@@ -21188,13 +21177,13 @@
         <v>300135982</v>
       </c>
       <c r="C42" s="88" t="s">
-        <v>3662</v>
+        <v>3663</v>
       </c>
       <c r="D42" s="88" t="s">
-        <v>3663</v>
+        <v>3664</v>
       </c>
       <c r="E42" s="90" t="s">
-        <v>3664</v>
+        <v>3665</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="64.5">
@@ -21205,13 +21194,13 @@
         <v>300387107</v>
       </c>
       <c r="C43" s="88" t="s">
-        <v>3665</v>
+        <v>3666</v>
       </c>
       <c r="D43" s="88" t="s">
-        <v>3666</v>
+        <v>3667</v>
       </c>
       <c r="E43" s="90" t="s">
-        <v>3667</v>
+        <v>3668</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="64.5">
@@ -21222,13 +21211,13 @@
         <v>300387130</v>
       </c>
       <c r="C44" s="88" t="s">
-        <v>3668</v>
+        <v>3669</v>
       </c>
       <c r="D44" s="88" t="s">
-        <v>3669</v>
+        <v>3670</v>
       </c>
       <c r="E44" s="90" t="s">
-        <v>3670</v>
+        <v>3671</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="16.5">
@@ -21239,13 +21228,13 @@
         <v>300236153</v>
       </c>
       <c r="C45" s="88" t="s">
-        <v>3671</v>
+        <v>3672</v>
       </c>
       <c r="D45" s="88" t="s">
-        <v>3672</v>
+        <v>3673</v>
       </c>
       <c r="E45" s="90" t="s">
-        <v>3673</v>
+        <v>3674</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="16.5">
@@ -21256,13 +21245,13 @@
         <v>300235087</v>
       </c>
       <c r="C46" s="88" t="s">
-        <v>3674</v>
+        <v>3675</v>
       </c>
       <c r="D46" s="88" t="s">
-        <v>3675</v>
+        <v>3676</v>
       </c>
       <c r="E46" s="90" t="s">
-        <v>3676</v>
+        <v>3677</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="16.5">
@@ -21273,13 +21262,13 @@
         <v>300264084</v>
       </c>
       <c r="C47" s="88" t="s">
-        <v>3677</v>
+        <v>3678</v>
       </c>
       <c r="D47" s="88" t="s">
-        <v>3678</v>
+        <v>3679</v>
       </c>
       <c r="E47" s="90" t="s">
-        <v>3679</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="64.5">
@@ -21290,13 +21279,13 @@
         <v>300264389</v>
       </c>
       <c r="C48" s="88" t="s">
-        <v>3680</v>
+        <v>3681</v>
       </c>
       <c r="D48" s="88" t="s">
-        <v>3681</v>
+        <v>3682</v>
       </c>
       <c r="E48" s="90" t="s">
-        <v>3682</v>
+        <v>3683</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="16.5">
@@ -21307,13 +21296,13 @@
         <v>300374944</v>
       </c>
       <c r="C49" s="88" t="s">
-        <v>3683</v>
+        <v>3684</v>
       </c>
       <c r="D49" s="88" t="s">
-        <v>3684</v>
+        <v>3685</v>
       </c>
       <c r="E49" s="90" t="s">
-        <v>3685</v>
+        <v>3686</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="16.5">
@@ -21324,13 +21313,13 @@
         <v>300235088</v>
       </c>
       <c r="C50" s="88" t="s">
-        <v>3686</v>
+        <v>3687</v>
       </c>
       <c r="D50" s="88" t="s">
-        <v>3687</v>
+        <v>3688</v>
       </c>
       <c r="E50" s="90" t="s">
-        <v>3688</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="16.5">
@@ -21341,13 +21330,13 @@
         <v>300387184</v>
       </c>
       <c r="C51" s="88" t="s">
-        <v>3689</v>
+        <v>3690</v>
       </c>
       <c r="D51" s="88" t="s">
-        <v>3690</v>
+        <v>3691</v>
       </c>
       <c r="E51" s="90" t="s">
-        <v>3691</v>
+        <v>3692</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="16.5">
@@ -21358,13 +21347,13 @@
         <v>300235095</v>
       </c>
       <c r="C52" s="88" t="s">
-        <v>3692</v>
+        <v>3693</v>
       </c>
       <c r="D52" s="88" t="s">
-        <v>3693</v>
+        <v>3694</v>
       </c>
       <c r="E52" s="90" t="s">
-        <v>3694</v>
+        <v>3695</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="16.5">
@@ -21375,13 +21364,13 @@
         <v>300235096</v>
       </c>
       <c r="C53" s="88" t="s">
-        <v>3695</v>
+        <v>3696</v>
       </c>
       <c r="D53" s="88" t="s">
-        <v>3696</v>
+        <v>3697</v>
       </c>
       <c r="E53" s="90" t="s">
-        <v>3697</v>
+        <v>3698</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="16.5">
@@ -21392,13 +21381,13 @@
         <v>300235101</v>
       </c>
       <c r="C54" s="88" t="s">
-        <v>3698</v>
+        <v>3699</v>
       </c>
       <c r="D54" s="88" t="s">
-        <v>3699</v>
+        <v>3700</v>
       </c>
       <c r="E54" s="90" t="s">
-        <v>3700</v>
+        <v>3701</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="16.5">
@@ -21409,13 +21398,13 @@
         <v>300235105</v>
       </c>
       <c r="C55" s="88" t="s">
-        <v>3701</v>
+        <v>3702</v>
       </c>
       <c r="D55" s="88" t="s">
-        <v>3702</v>
+        <v>3703</v>
       </c>
       <c r="E55" s="90" t="s">
-        <v>3703</v>
+        <v>3704</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="16.5">
@@ -21426,13 +21415,13 @@
         <v>300235106</v>
       </c>
       <c r="C56" s="88" t="s">
-        <v>3704</v>
+        <v>3705</v>
       </c>
       <c r="D56" s="88" t="s">
-        <v>3705</v>
+        <v>3706</v>
       </c>
       <c r="E56" s="90" t="s">
-        <v>3706</v>
+        <v>3707</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="16.5">
@@ -21443,13 +21432,13 @@
         <v>300235099</v>
       </c>
       <c r="C57" s="88" t="s">
-        <v>3707</v>
+        <v>3708</v>
       </c>
       <c r="D57" s="88" t="s">
-        <v>3708</v>
+        <v>3709</v>
       </c>
       <c r="E57" s="90" t="s">
-        <v>3709</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="16.5">
@@ -21460,13 +21449,13 @@
         <v>300192630</v>
       </c>
       <c r="C58" s="89" t="s">
-        <v>3710</v>
+        <v>3711</v>
       </c>
       <c r="D58" s="89" t="s">
-        <v>3711</v>
+        <v>3712</v>
       </c>
       <c r="E58" s="90" t="s">
-        <v>3712</v>
+        <v>3713</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="32.25">
@@ -21477,13 +21466,13 @@
         <v>300387171</v>
       </c>
       <c r="C59" s="88" t="s">
-        <v>3713</v>
+        <v>3714</v>
       </c>
       <c r="D59" s="88" t="s">
-        <v>3714</v>
+        <v>3715</v>
       </c>
       <c r="E59" s="90" t="s">
-        <v>3715</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="32.25">
@@ -21494,26 +21483,26 @@
         <v>300386176</v>
       </c>
       <c r="C60" s="88" t="s">
-        <v>3716</v>
+        <v>3717</v>
       </c>
       <c r="D60" s="88" t="s">
-        <v>3717</v>
+        <v>3718</v>
       </c>
       <c r="E60" s="90" t="s">
-        <v>3718</v>
+        <v>3719</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="243">
       <c r="A61" s="85"/>
       <c r="B61" s="95"/>
       <c r="C61" s="92" t="s">
-        <v>3719</v>
+        <v>3720</v>
       </c>
       <c r="D61" s="92" t="s">
-        <v>3719</v>
+        <v>3720</v>
       </c>
       <c r="E61" s="90" t="s">
-        <v>3720</v>
+        <v>3721</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="32.25">
@@ -21524,13 +21513,13 @@
         <v>300000202</v>
       </c>
       <c r="C62" s="92" t="s">
-        <v>3721</v>
+        <v>3722</v>
       </c>
       <c r="D62" s="92" t="s">
-        <v>3721</v>
+        <v>3722</v>
       </c>
       <c r="E62" s="90" t="s">
-        <v>3722</v>
+        <v>3723</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="32.25">
@@ -21541,13 +21530,13 @@
         <v>300000809</v>
       </c>
       <c r="C63" s="89" t="s">
-        <v>3723</v>
+        <v>3724</v>
       </c>
       <c r="D63" s="89" t="s">
-        <v>3724</v>
+        <v>3725</v>
       </c>
       <c r="E63" s="90" t="s">
-        <v>3725</v>
+        <v>3726</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="64.5">
@@ -21558,13 +21547,13 @@
         <v>300000810</v>
       </c>
       <c r="C64" s="88" t="s">
-        <v>3726</v>
+        <v>3727</v>
       </c>
       <c r="D64" s="88" t="s">
-        <v>3727</v>
+        <v>3728</v>
       </c>
       <c r="E64" s="90" t="s">
-        <v>3728</v>
+        <v>3729</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="16.5">
@@ -21575,13 +21564,13 @@
         <v>300387006</v>
       </c>
       <c r="C65" s="88" t="s">
-        <v>3729</v>
+        <v>3730</v>
       </c>
       <c r="D65" s="88" t="s">
-        <v>3730</v>
+        <v>3731</v>
       </c>
       <c r="E65" s="90" t="s">
-        <v>3731</v>
+        <v>3732</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="16.5">
@@ -21592,13 +21581,13 @@
         <v>300387007</v>
       </c>
       <c r="C66" s="88" t="s">
-        <v>3732</v>
+        <v>3733</v>
       </c>
       <c r="D66" s="88" t="s">
-        <v>3733</v>
+        <v>3734</v>
       </c>
       <c r="E66" s="90" t="s">
-        <v>3734</v>
+        <v>3735</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="16.5">
@@ -21609,13 +21598,13 @@
         <v>300387000</v>
       </c>
       <c r="C67" s="88" t="s">
-        <v>3735</v>
+        <v>3736</v>
       </c>
       <c r="D67" s="88" t="s">
-        <v>3736</v>
+        <v>3737</v>
       </c>
       <c r="E67" s="90" t="s">
-        <v>3737</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="16.5">
@@ -21626,13 +21615,13 @@
         <v>300000835</v>
       </c>
       <c r="C68" s="88" t="s">
-        <v>3738</v>
+        <v>3739</v>
       </c>
       <c r="D68" s="88" t="s">
-        <v>3739</v>
+        <v>3740</v>
       </c>
       <c r="E68" s="90" t="s">
-        <v>3740</v>
+        <v>3741</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="32.25">
@@ -21643,13 +21632,13 @@
         <v>300386998</v>
       </c>
       <c r="C69" s="88" t="s">
-        <v>3741</v>
+        <v>3742</v>
       </c>
       <c r="D69" s="88" t="s">
-        <v>3742</v>
+        <v>3743</v>
       </c>
       <c r="E69" s="90" t="s">
-        <v>3743</v>
+        <v>3744</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="32.25">
@@ -21660,13 +21649,13 @@
         <v>300263063</v>
       </c>
       <c r="C70" s="88" t="s">
-        <v>3744</v>
+        <v>3745</v>
       </c>
       <c r="D70" s="88" t="s">
-        <v>3745</v>
+        <v>3746</v>
       </c>
       <c r="E70" s="90" t="s">
-        <v>3746</v>
+        <v>3747</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="16.5">
@@ -21677,13 +21666,13 @@
         <v>300387268</v>
       </c>
       <c r="C71" s="88" t="s">
-        <v>3747</v>
+        <v>3748</v>
       </c>
       <c r="D71" s="88" t="s">
-        <v>3748</v>
+        <v>3749</v>
       </c>
       <c r="E71" s="90" t="s">
-        <v>3749</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="16.5">
@@ -21694,13 +21683,13 @@
         <v>300387004</v>
       </c>
       <c r="C72" s="88" t="s">
-        <v>3750</v>
+        <v>3751</v>
       </c>
       <c r="D72" s="88" t="s">
-        <v>3751</v>
+        <v>3752</v>
       </c>
       <c r="E72" s="90" t="s">
-        <v>3752</v>
+        <v>3753</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="48.75">
@@ -21711,13 +21700,13 @@
         <v>300266755</v>
       </c>
       <c r="C73" s="88" t="s">
-        <v>3753</v>
+        <v>3754</v>
       </c>
       <c r="D73" s="88" t="s">
-        <v>3754</v>
+        <v>3755</v>
       </c>
       <c r="E73" s="90" t="s">
-        <v>3755</v>
+        <v>3756</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="48.75">
@@ -21728,13 +21717,13 @@
         <v>300000277</v>
       </c>
       <c r="C74" s="88" t="s">
-        <v>3756</v>
+        <v>3757</v>
       </c>
       <c r="D74" s="88" t="s">
-        <v>3757</v>
+        <v>3758</v>
       </c>
       <c r="E74" s="90" t="s">
-        <v>3758</v>
+        <v>3759</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="16.5">
@@ -21745,13 +21734,13 @@
         <v>300164060</v>
       </c>
       <c r="C75" s="88" t="s">
-        <v>3759</v>
+        <v>3760</v>
       </c>
       <c r="D75" s="88" t="s">
-        <v>3760</v>
+        <v>3761</v>
       </c>
       <c r="E75" s="90" t="s">
-        <v>3761</v>
+        <v>3762</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="32.25">
@@ -21762,13 +21751,13 @@
         <v>300000455</v>
       </c>
       <c r="C76" s="88" t="s">
-        <v>3762</v>
+        <v>3763</v>
       </c>
       <c r="D76" s="88" t="s">
-        <v>3763</v>
+        <v>3764</v>
       </c>
       <c r="E76" s="90" t="s">
-        <v>3764</v>
+        <v>3765</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="16.5">
@@ -21779,13 +21768,13 @@
         <v>300008439</v>
       </c>
       <c r="C77" s="88" t="s">
-        <v>3765</v>
+        <v>3766</v>
       </c>
       <c r="D77" s="88" t="s">
-        <v>3766</v>
+        <v>3767</v>
       </c>
       <c r="E77" s="90" t="s">
-        <v>3767</v>
+        <v>3768</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="32.25">
@@ -21796,13 +21785,13 @@
         <v>300410262</v>
       </c>
       <c r="C78" s="88" t="s">
-        <v>3768</v>
+        <v>3769</v>
       </c>
       <c r="D78" s="88" t="s">
-        <v>3769</v>
+        <v>3770</v>
       </c>
       <c r="E78" s="90" t="s">
-        <v>3770</v>
+        <v>3771</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="16.5">
@@ -21813,13 +21802,13 @@
         <v>300417317</v>
       </c>
       <c r="C79" s="88" t="s">
-        <v>3771</v>
+        <v>3772</v>
       </c>
       <c r="D79" s="88" t="s">
-        <v>3772</v>
+        <v>3773</v>
       </c>
       <c r="E79" s="90" t="s">
-        <v>3773</v>
+        <v>3774</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="16.5">
@@ -21830,13 +21819,13 @@
         <v>300263741</v>
       </c>
       <c r="C80" s="88" t="s">
-        <v>3774</v>
+        <v>3775</v>
       </c>
       <c r="D80" s="88" t="s">
-        <v>3775</v>
+        <v>3776</v>
       </c>
       <c r="E80" s="90" t="s">
-        <v>3776</v>
+        <v>3777</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="16.5">
@@ -21847,13 +21836,13 @@
         <v>300000678</v>
       </c>
       <c r="C81" s="88" t="s">
-        <v>3777</v>
+        <v>3778</v>
       </c>
       <c r="D81" s="88" t="s">
-        <v>3778</v>
+        <v>3779</v>
       </c>
       <c r="E81" s="90" t="s">
-        <v>3779</v>
+        <v>3780</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="48.75">
@@ -21864,13 +21853,13 @@
         <v>300000681</v>
       </c>
       <c r="C82" s="88" t="s">
-        <v>3780</v>
+        <v>3781</v>
       </c>
       <c r="D82" s="88" t="s">
-        <v>3781</v>
+        <v>3782</v>
       </c>
       <c r="E82" s="90" t="s">
-        <v>3782</v>
+        <v>3783</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="16.5">
@@ -21881,13 +21870,13 @@
         <v>300125766</v>
       </c>
       <c r="C83" s="88" t="s">
-        <v>3783</v>
+        <v>3784</v>
       </c>
       <c r="D83" s="88" t="s">
-        <v>3784</v>
+        <v>3785</v>
       </c>
       <c r="E83" s="90" t="s">
-        <v>3785</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="32.25">
@@ -21898,13 +21887,13 @@
         <v>300000401</v>
       </c>
       <c r="C84" s="88" t="s">
-        <v>3786</v>
+        <v>3787</v>
       </c>
       <c r="D84" s="88" t="s">
-        <v>3787</v>
+        <v>3788</v>
       </c>
       <c r="E84" s="90" t="s">
-        <v>3788</v>
+        <v>3789</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="32.25">
@@ -21915,13 +21904,13 @@
         <v>300000390</v>
       </c>
       <c r="C85" s="88" t="s">
-        <v>3789</v>
+        <v>3790</v>
       </c>
       <c r="D85" s="88" t="s">
-        <v>3790</v>
+        <v>3791</v>
       </c>
       <c r="E85" s="90" t="s">
-        <v>3791</v>
+        <v>3792</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="16.5">
@@ -21932,13 +21921,13 @@
         <v>300132656</v>
       </c>
       <c r="C86" s="88" t="s">
-        <v>3792</v>
+        <v>3793</v>
       </c>
       <c r="D86" s="88" t="s">
-        <v>3793</v>
+        <v>3794</v>
       </c>
       <c r="E86" s="90" t="s">
-        <v>3794</v>
+        <v>3795</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="32.25">
@@ -21949,13 +21938,13 @@
         <v>300257640</v>
       </c>
       <c r="C87" s="88" t="s">
-        <v>3795</v>
+        <v>3796</v>
       </c>
       <c r="D87" s="88" t="s">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="E87" s="90" t="s">
-        <v>3797</v>
+        <v>3798</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="16.5">
@@ -21966,13 +21955,13 @@
         <v>300000705</v>
       </c>
       <c r="C88" s="89" t="s">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="D88" s="89" t="s">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="E88" s="90" t="s">
-        <v>3800</v>
+        <v>3801</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="16.5">
@@ -21983,13 +21972,13 @@
         <v>300000742</v>
       </c>
       <c r="C89" s="88" t="s">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="D89" s="88" t="s">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="E89" s="90" t="s">
-        <v>3803</v>
+        <v>3804</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="32.25">
@@ -22000,13 +21989,13 @@
         <v>300000745</v>
       </c>
       <c r="C90" s="88" t="s">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="D90" s="88" t="s">
-        <v>3805</v>
+        <v>3806</v>
       </c>
       <c r="E90" s="90" t="s">
-        <v>3806</v>
+        <v>3807</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="16.5">
@@ -22017,13 +22006,13 @@
         <v>300000750</v>
       </c>
       <c r="C91" s="88" t="s">
-        <v>3807</v>
+        <v>3808</v>
       </c>
       <c r="D91" s="88" t="s">
-        <v>3808</v>
+        <v>3809</v>
       </c>
       <c r="E91" s="90" t="s">
-        <v>3809</v>
+        <v>3810</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="16.5">
@@ -22034,13 +22023,13 @@
         <v>300387143</v>
       </c>
       <c r="C92" s="88" t="s">
-        <v>3810</v>
+        <v>3811</v>
       </c>
       <c r="D92" s="88" t="s">
-        <v>3811</v>
+        <v>3812</v>
       </c>
       <c r="E92" s="90" t="s">
-        <v>3812</v>
+        <v>3813</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="16.5">
@@ -22049,13 +22038,13 @@
         <v>300004790</v>
       </c>
       <c r="C93" s="89" t="s">
-        <v>3813</v>
+        <v>3814</v>
       </c>
       <c r="D93" s="89" t="s">
-        <v>3814</v>
+        <v>3815</v>
       </c>
       <c r="E93" s="90" t="s">
-        <v>3815</v>
+        <v>3816</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="16.5">
@@ -22066,13 +22055,13 @@
         <v>300007836</v>
       </c>
       <c r="C94" s="88" t="s">
-        <v>3816</v>
+        <v>3817</v>
       </c>
       <c r="D94" s="88" t="s">
-        <v>3817</v>
+        <v>3818</v>
       </c>
       <c r="E94" s="90" t="s">
-        <v>3818</v>
+        <v>3819</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="16.5">
@@ -22083,13 +22072,13 @@
         <v>300008057</v>
       </c>
       <c r="C95" s="88" t="s">
-        <v>3819</v>
+        <v>3820</v>
       </c>
       <c r="D95" s="88" t="s">
-        <v>3820</v>
+        <v>3821</v>
       </c>
       <c r="E95" s="90" t="s">
-        <v>3821</v>
+        <v>3822</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="48.75">
@@ -22100,13 +22089,13 @@
         <v>300008063</v>
       </c>
       <c r="C96" s="88" t="s">
-        <v>3822</v>
+        <v>3823</v>
       </c>
       <c r="D96" s="88" t="s">
-        <v>3823</v>
+        <v>3824</v>
       </c>
       <c r="E96" s="90" t="s">
-        <v>3824</v>
+        <v>3825</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="16.5">
@@ -22117,13 +22106,13 @@
         <v>300006073</v>
       </c>
       <c r="C97" s="88" t="s">
-        <v>3825</v>
+        <v>3826</v>
       </c>
       <c r="D97" s="88" t="s">
-        <v>3826</v>
+        <v>3827</v>
       </c>
       <c r="E97" s="90" t="s">
-        <v>3827</v>
+        <v>3828</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="16.5">
@@ -22134,13 +22123,13 @@
         <v>300006075</v>
       </c>
       <c r="C98" s="88" t="s">
-        <v>3828</v>
+        <v>3829</v>
       </c>
       <c r="D98" s="88" t="s">
-        <v>3829</v>
+        <v>3830</v>
       </c>
       <c r="E98" s="90" t="s">
-        <v>3830</v>
+        <v>3831</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="16.5">
@@ -22151,13 +22140,13 @@
         <v>300006084</v>
       </c>
       <c r="C99" s="88" t="s">
-        <v>3831</v>
+        <v>3832</v>
       </c>
       <c r="D99" s="88" t="s">
-        <v>3832</v>
+        <v>3833</v>
       </c>
       <c r="E99" s="90" t="s">
-        <v>3833</v>
+        <v>3834</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="64.5">
@@ -22168,13 +22157,13 @@
         <v>300006084</v>
       </c>
       <c r="C100" s="88" t="s">
-        <v>3834</v>
+        <v>3835</v>
       </c>
       <c r="D100" s="88" t="s">
-        <v>3835</v>
+        <v>3836</v>
       </c>
       <c r="E100" s="90" t="s">
-        <v>3836</v>
+        <v>3837</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="16.5">
@@ -22185,13 +22174,13 @@
         <v>300006191</v>
       </c>
       <c r="C101" s="88" t="s">
-        <v>3837</v>
+        <v>3838</v>
       </c>
       <c r="D101" s="88" t="s">
-        <v>3838</v>
+        <v>3839</v>
       </c>
       <c r="E101" s="90" t="s">
-        <v>3839</v>
+        <v>3840</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="32.25">
@@ -22202,13 +22191,13 @@
         <v>300006207</v>
       </c>
       <c r="C102" s="88" t="s">
-        <v>3840</v>
+        <v>3841</v>
       </c>
       <c r="D102" s="88" t="s">
-        <v>3841</v>
+        <v>3842</v>
       </c>
       <c r="E102" s="90" t="s">
-        <v>3842</v>
+        <v>3843</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="16.5">
@@ -22219,13 +22208,13 @@
         <v>300263489</v>
       </c>
       <c r="C103" s="88" t="s">
-        <v>3843</v>
+        <v>3844</v>
       </c>
       <c r="D103" s="88" t="s">
-        <v>3844</v>
+        <v>3845</v>
       </c>
       <c r="E103" s="90" t="s">
-        <v>3845</v>
+        <v>3846</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="32.25">
@@ -22236,13 +22225,13 @@
         <v>300005903</v>
       </c>
       <c r="C104" s="88" t="s">
-        <v>3846</v>
+        <v>3847</v>
       </c>
       <c r="D104" s="88" t="s">
-        <v>3847</v>
+        <v>3848</v>
       </c>
       <c r="E104" s="90" t="s">
-        <v>3848</v>
+        <v>3849</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="16.5">
@@ -22253,13 +22242,13 @@
         <v>300120364</v>
       </c>
       <c r="C105" s="88" t="s">
-        <v>3849</v>
+        <v>3850</v>
       </c>
       <c r="D105" s="88" t="s">
-        <v>3850</v>
+        <v>3851</v>
       </c>
       <c r="E105" s="90" t="s">
-        <v>3851</v>
+        <v>3852</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="32.25">
@@ -22270,13 +22259,13 @@
         <v>300007486</v>
       </c>
       <c r="C106" s="88" t="s">
-        <v>3852</v>
+        <v>3853</v>
       </c>
       <c r="D106" s="88" t="s">
-        <v>3853</v>
+        <v>3854</v>
       </c>
       <c r="E106" s="90" t="s">
-        <v>3854</v>
+        <v>3855</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="32.25">
@@ -22287,13 +22276,13 @@
         <v>300007501</v>
       </c>
       <c r="C107" s="88" t="s">
-        <v>3855</v>
+        <v>3856</v>
       </c>
       <c r="D107" s="88" t="s">
-        <v>3856</v>
+        <v>3857</v>
       </c>
       <c r="E107" s="90" t="s">
-        <v>3857</v>
+        <v>3858</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="16.5">
@@ -22304,13 +22293,13 @@
         <v>300007544</v>
       </c>
       <c r="C108" s="88" t="s">
-        <v>3858</v>
+        <v>3859</v>
       </c>
       <c r="D108" s="88" t="s">
-        <v>3859</v>
+        <v>3860</v>
       </c>
       <c r="E108" s="90" t="s">
-        <v>3860</v>
+        <v>3861</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="32.25">
@@ -22321,13 +22310,13 @@
         <v>300007595</v>
       </c>
       <c r="C109" s="88" t="s">
-        <v>3861</v>
+        <v>3862</v>
       </c>
       <c r="D109" s="88" t="s">
-        <v>3862</v>
+        <v>3863</v>
       </c>
       <c r="E109" s="90" t="s">
-        <v>3863</v>
+        <v>3864</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="32.25">
@@ -22338,13 +22327,13 @@
         <v>300004829</v>
       </c>
       <c r="C110" s="88" t="s">
-        <v>3864</v>
+        <v>3865</v>
       </c>
       <c r="D110" s="88" t="s">
-        <v>3865</v>
+        <v>3866</v>
       </c>
       <c r="E110" s="90" t="s">
-        <v>3866</v>
+        <v>3867</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="16.5">
@@ -22355,13 +22344,13 @@
         <v>300007590</v>
       </c>
       <c r="C111" s="88" t="s">
-        <v>3867</v>
+        <v>3868</v>
       </c>
       <c r="D111" s="88" t="s">
-        <v>3868</v>
+        <v>3869</v>
       </c>
       <c r="E111" s="90" t="s">
-        <v>3869</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="32.25">
@@ -22372,13 +22361,13 @@
         <v>300005734</v>
       </c>
       <c r="C112" s="88" t="s">
-        <v>3870</v>
+        <v>3871</v>
       </c>
       <c r="D112" s="88" t="s">
-        <v>3871</v>
+        <v>3872</v>
       </c>
       <c r="E112" s="90" t="s">
-        <v>3872</v>
+        <v>3873</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="16.5">
@@ -22389,13 +22378,13 @@
         <v>300387025</v>
       </c>
       <c r="C113" s="88" t="s">
-        <v>3873</v>
+        <v>3874</v>
       </c>
       <c r="D113" s="88" t="s">
-        <v>3874</v>
+        <v>3875</v>
       </c>
       <c r="E113" s="90" t="s">
-        <v>3875</v>
+        <v>3876</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="16.5">
@@ -22406,13 +22395,13 @@
         <v>300006888</v>
       </c>
       <c r="C114" s="88" t="s">
-        <v>3876</v>
+        <v>3877</v>
       </c>
       <c r="D114" s="88" t="s">
-        <v>3877</v>
+        <v>3878</v>
       </c>
       <c r="E114" s="90" t="s">
-        <v>3878</v>
+        <v>3879</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="16.5">
@@ -22423,13 +22412,13 @@
         <v>300006891</v>
       </c>
       <c r="C115" s="88" t="s">
-        <v>3879</v>
+        <v>3880</v>
       </c>
       <c r="D115" s="88" t="s">
-        <v>3880</v>
+        <v>3881</v>
       </c>
       <c r="E115" s="90" t="s">
-        <v>3881</v>
+        <v>3882</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="16.5">
@@ -22440,13 +22429,13 @@
         <v>300005072</v>
       </c>
       <c r="C116" s="88" t="s">
-        <v>3882</v>
+        <v>3883</v>
       </c>
       <c r="D116" s="88" t="s">
-        <v>3883</v>
+        <v>3884</v>
       </c>
       <c r="E116" s="90" t="s">
-        <v>3884</v>
+        <v>3885</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="32.25">
@@ -22457,13 +22446,13 @@
         <v>300006617</v>
       </c>
       <c r="C117" s="88" t="s">
-        <v>3885</v>
+        <v>3886</v>
       </c>
       <c r="D117" s="88" t="s">
-        <v>3886</v>
+        <v>3887</v>
       </c>
       <c r="E117" s="90" t="s">
-        <v>3887</v>
+        <v>3888</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="16.5">
@@ -22472,13 +22461,13 @@
         <v>300155846</v>
       </c>
       <c r="C118" s="89" t="s">
-        <v>3888</v>
+        <v>3889</v>
       </c>
       <c r="D118" s="89" t="s">
-        <v>3889</v>
+        <v>3890</v>
       </c>
       <c r="E118" s="90" t="s">
-        <v>3890</v>
+        <v>3891</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="32.25">
@@ -22489,13 +22478,13 @@
         <v>300008591</v>
       </c>
       <c r="C119" s="88" t="s">
-        <v>3891</v>
+        <v>3892</v>
       </c>
       <c r="D119" s="88" t="s">
-        <v>3892</v>
+        <v>3893</v>
       </c>
       <c r="E119" s="90" t="s">
-        <v>3893</v>
+        <v>3894</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="48.75">
@@ -22504,13 +22493,13 @@
         <v>300008072</v>
       </c>
       <c r="C120" s="92" t="s">
-        <v>3894</v>
+        <v>3895</v>
       </c>
       <c r="D120" s="92" t="s">
-        <v>3895</v>
+        <v>3896</v>
       </c>
       <c r="E120" s="90" t="s">
-        <v>3896</v>
+        <v>3897</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="16.5">
@@ -22521,13 +22510,13 @@
         <v>300008304</v>
       </c>
       <c r="C121" s="88" t="s">
-        <v>3897</v>
+        <v>3898</v>
       </c>
       <c r="D121" s="88" t="s">
-        <v>3898</v>
+        <v>3899</v>
       </c>
       <c r="E121" s="90" t="s">
-        <v>3899</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="16.5">
@@ -22538,13 +22527,13 @@
         <v>300008187</v>
       </c>
       <c r="C122" s="88" t="s">
-        <v>3900</v>
+        <v>3901</v>
       </c>
       <c r="D122" s="88" t="s">
-        <v>3901</v>
+        <v>3902</v>
       </c>
       <c r="E122" s="90" t="s">
-        <v>3902</v>
+        <v>3903</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="16.5">
@@ -22555,13 +22544,13 @@
         <v>300122438</v>
       </c>
       <c r="C123" s="88" t="s">
-        <v>3903</v>
+        <v>3904</v>
       </c>
       <c r="D123" s="88" t="s">
-        <v>3904</v>
+        <v>3905</v>
       </c>
       <c r="E123" s="90" t="s">
-        <v>3905</v>
+        <v>3906</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="32.25">
@@ -22572,13 +22561,13 @@
         <v>300008217</v>
       </c>
       <c r="C124" s="88" t="s">
-        <v>3906</v>
+        <v>3907</v>
       </c>
       <c r="D124" s="88" t="s">
-        <v>3907</v>
+        <v>3908</v>
       </c>
       <c r="E124" s="90" t="s">
-        <v>3908</v>
+        <v>3909</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="16.5">
@@ -22589,13 +22578,13 @@
         <v>300265365</v>
       </c>
       <c r="C125" s="88" t="s">
-        <v>3909</v>
+        <v>3910</v>
       </c>
       <c r="D125" s="88" t="s">
-        <v>3910</v>
+        <v>3911</v>
       </c>
       <c r="E125" s="90" t="s">
-        <v>3911</v>
+        <v>3912</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="32.25">
@@ -22606,13 +22595,13 @@
         <v>300386595</v>
       </c>
       <c r="C126" s="88" t="s">
-        <v>3912</v>
+        <v>3913</v>
       </c>
       <c r="D126" s="88" t="s">
-        <v>3913</v>
+        <v>3914</v>
       </c>
       <c r="E126" s="90" t="s">
-        <v>3914</v>
+        <v>3915</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="16.5">
@@ -22623,13 +22612,13 @@
         <v>300265367</v>
       </c>
       <c r="C127" s="88" t="s">
-        <v>3915</v>
+        <v>3916</v>
       </c>
       <c r="D127" s="88" t="s">
-        <v>3916</v>
+        <v>3917</v>
       </c>
       <c r="E127" s="90" t="s">
-        <v>3917</v>
+        <v>3918</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="16.5">
@@ -22640,13 +22629,13 @@
         <v>300265366</v>
       </c>
       <c r="C128" s="88" t="s">
-        <v>3918</v>
+        <v>3919</v>
       </c>
       <c r="D128" s="88" t="s">
-        <v>3919</v>
+        <v>3920</v>
       </c>
       <c r="E128" s="90" t="s">
-        <v>3920</v>
+        <v>3921</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="32.25">
@@ -22657,13 +22646,13 @@
         <v>300008312</v>
       </c>
       <c r="C129" s="88" t="s">
-        <v>3921</v>
+        <v>3922</v>
       </c>
       <c r="D129" s="88" t="s">
-        <v>3922</v>
+        <v>3923</v>
       </c>
       <c r="E129" s="90" t="s">
-        <v>3923</v>
+        <v>3924</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="16.5">
@@ -22674,13 +22663,13 @@
         <v>300008321</v>
       </c>
       <c r="C130" s="88" t="s">
-        <v>3924</v>
+        <v>3925</v>
       </c>
       <c r="D130" s="88" t="s">
-        <v>3925</v>
+        <v>3926</v>
       </c>
       <c r="E130" s="90" t="s">
-        <v>3926</v>
+        <v>3927</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="32.25">
@@ -22691,13 +22680,13 @@
         <v>300132294</v>
       </c>
       <c r="C131" s="86" t="s">
-        <v>3927</v>
+        <v>3928</v>
       </c>
       <c r="D131" s="86" t="s">
-        <v>3928</v>
+        <v>3929</v>
       </c>
       <c r="E131" s="90" t="s">
-        <v>3929</v>
+        <v>3930</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="48.75">
@@ -22708,13 +22697,13 @@
         <v>300266060</v>
       </c>
       <c r="C132" s="89" t="s">
-        <v>3930</v>
+        <v>3931</v>
       </c>
       <c r="D132" s="89" t="s">
-        <v>3931</v>
+        <v>3932</v>
       </c>
       <c r="E132" s="90" t="s">
-        <v>3932</v>
+        <v>3933</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="16.5">
@@ -22725,13 +22714,13 @@
         <v>300386845</v>
       </c>
       <c r="C133" s="88" t="s">
-        <v>3933</v>
+        <v>3934</v>
       </c>
       <c r="D133" s="88" t="s">
-        <v>3934</v>
+        <v>3935</v>
       </c>
       <c r="E133" s="90" t="s">
-        <v>3935</v>
+        <v>3936</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="16.5">
@@ -22742,13 +22731,13 @@
         <v>300008850</v>
       </c>
       <c r="C134" s="88" t="s">
-        <v>3936</v>
+        <v>3937</v>
       </c>
       <c r="D134" s="88" t="s">
-        <v>3937</v>
+        <v>3938</v>
       </c>
       <c r="E134" s="90" t="s">
-        <v>3938</v>
+        <v>3939</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="16.5">
@@ -22759,13 +22748,13 @@
         <v>300386846</v>
       </c>
       <c r="C135" s="88" t="s">
-        <v>3939</v>
+        <v>3940</v>
       </c>
       <c r="D135" s="88" t="s">
-        <v>3940</v>
+        <v>3941</v>
       </c>
       <c r="E135" s="90" t="s">
-        <v>3941</v>
+        <v>3942</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="16.5">
@@ -22776,13 +22765,13 @@
         <v>300008804</v>
       </c>
       <c r="C136" s="88" t="s">
-        <v>3942</v>
+        <v>3943</v>
       </c>
       <c r="D136" s="88" t="s">
-        <v>3943</v>
+        <v>3944</v>
       </c>
       <c r="E136" s="90" t="s">
-        <v>3944</v>
+        <v>3945</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="32.25">
@@ -22793,13 +22782,13 @@
         <v>300128176</v>
       </c>
       <c r="C137" s="88" t="s">
-        <v>3945</v>
+        <v>3946</v>
       </c>
       <c r="D137" s="88" t="s">
-        <v>3946</v>
+        <v>3947</v>
       </c>
       <c r="E137" s="90" t="s">
-        <v>3947</v>
+        <v>3948</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="32.25">
@@ -22810,13 +22799,13 @@
         <v>300008760</v>
       </c>
       <c r="C138" s="88" t="s">
-        <v>3948</v>
+        <v>3949</v>
       </c>
       <c r="D138" s="88" t="s">
-        <v>3949</v>
+        <v>3950</v>
       </c>
       <c r="E138" s="90" t="s">
-        <v>3950</v>
+        <v>3951</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="16.5">
@@ -22827,13 +22816,13 @@
         <v>300386860</v>
       </c>
       <c r="C139" s="88" t="s">
-        <v>3951</v>
+        <v>3952</v>
       </c>
       <c r="D139" s="88" t="s">
-        <v>3952</v>
+        <v>3953</v>
       </c>
       <c r="E139" s="90" t="s">
-        <v>3953</v>
+        <v>3954</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="16.5">
@@ -22844,13 +22833,13 @@
         <v>300008916</v>
       </c>
       <c r="C140" s="88" t="s">
-        <v>3954</v>
+        <v>3955</v>
       </c>
       <c r="D140" s="88" t="s">
-        <v>3955</v>
+        <v>3956</v>
       </c>
       <c r="E140" s="90" t="s">
-        <v>3956</v>
+        <v>3957</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="32.25">
@@ -22861,13 +22850,13 @@
         <v>300387498</v>
       </c>
       <c r="C141" s="88" t="s">
-        <v>3957</v>
+        <v>3958</v>
       </c>
       <c r="D141" s="88" t="s">
-        <v>3958</v>
+        <v>3959</v>
       </c>
       <c r="E141" s="90" t="s">
-        <v>3959</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="32.25">
@@ -22878,13 +22867,13 @@
         <v>300387499</v>
       </c>
       <c r="C142" s="88" t="s">
-        <v>3960</v>
+        <v>3961</v>
       </c>
       <c r="D142" s="88" t="s">
-        <v>3961</v>
+        <v>3962</v>
       </c>
       <c r="E142" s="90" t="s">
-        <v>3962</v>
+        <v>3963</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="16.5">
@@ -22895,13 +22884,13 @@
         <v>300008777</v>
       </c>
       <c r="C143" s="88" t="s">
-        <v>3963</v>
+        <v>3964</v>
       </c>
       <c r="D143" s="88" t="s">
-        <v>3964</v>
+        <v>3965</v>
       </c>
       <c r="E143" s="90" t="s">
-        <v>3965</v>
+        <v>3966</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="16.5">
@@ -22912,13 +22901,13 @@
         <v>300008791</v>
       </c>
       <c r="C144" s="88" t="s">
-        <v>3966</v>
+        <v>3967</v>
       </c>
       <c r="D144" s="88" t="s">
-        <v>3967</v>
+        <v>3968</v>
       </c>
       <c r="E144" s="90" t="s">
-        <v>3968</v>
+        <v>3969</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="16.5">
@@ -22929,13 +22918,13 @@
         <v>300386853</v>
       </c>
       <c r="C145" s="88" t="s">
-        <v>3969</v>
+        <v>3970</v>
       </c>
       <c r="D145" s="88" t="s">
-        <v>3970</v>
+        <v>3971</v>
       </c>
       <c r="E145" s="90" t="s">
-        <v>3971</v>
+        <v>3972</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="16.5">
@@ -22946,13 +22935,13 @@
         <v>300386831</v>
       </c>
       <c r="C146" s="88" t="s">
-        <v>3972</v>
+        <v>3973</v>
       </c>
       <c r="D146" s="88" t="s">
-        <v>3973</v>
+        <v>3974</v>
       </c>
       <c r="E146" s="90" t="s">
-        <v>3974</v>
+        <v>3975</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="32.25">
@@ -22963,13 +22952,13 @@
         <v>300008795</v>
       </c>
       <c r="C147" s="88" t="s">
-        <v>3975</v>
+        <v>3976</v>
       </c>
       <c r="D147" s="88" t="s">
-        <v>3976</v>
+        <v>3977</v>
       </c>
       <c r="E147" s="90" t="s">
-        <v>3977</v>
+        <v>3978</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="16.5">
@@ -22980,13 +22969,13 @@
         <v>300008686</v>
       </c>
       <c r="C148" s="88" t="s">
-        <v>3978</v>
+        <v>3979</v>
       </c>
       <c r="D148" s="88" t="s">
-        <v>3979</v>
+        <v>3980</v>
       </c>
       <c r="E148" s="90" t="s">
-        <v>3980</v>
+        <v>3981</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="16.5">
@@ -22997,13 +22986,13 @@
         <v>300259572</v>
       </c>
       <c r="C149" s="88" t="s">
-        <v>3981</v>
+        <v>3982</v>
       </c>
       <c r="D149" s="88" t="s">
-        <v>3982</v>
+        <v>3983</v>
       </c>
       <c r="E149" s="93" t="s">
-        <v>3983</v>
+        <v>3984</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="16.5">
@@ -23014,13 +23003,13 @@
         <v>300008805</v>
       </c>
       <c r="C150" s="88" t="s">
-        <v>3984</v>
+        <v>3985</v>
       </c>
       <c r="D150" s="88" t="s">
-        <v>3985</v>
+        <v>3986</v>
       </c>
       <c r="E150" s="90" t="s">
-        <v>3986</v>
+        <v>3987</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="16.5">
@@ -23031,13 +23020,13 @@
         <v>300132339</v>
       </c>
       <c r="C151" s="85" t="s">
-        <v>3987</v>
+        <v>3988</v>
       </c>
       <c r="D151" s="85" t="s">
-        <v>3988</v>
+        <v>3989</v>
       </c>
       <c r="E151" s="90" t="s">
-        <v>3989</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="16.5">
@@ -23048,13 +23037,13 @@
         <v>300008761</v>
       </c>
       <c r="C152" s="88" t="s">
-        <v>3990</v>
+        <v>3991</v>
       </c>
       <c r="D152" s="88" t="s">
-        <v>3991</v>
+        <v>3992</v>
       </c>
       <c r="E152" s="90" t="s">
-        <v>3992</v>
+        <v>3993</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="16.5">
@@ -23065,13 +23054,13 @@
         <v>300129031</v>
       </c>
       <c r="C153" s="88" t="s">
-        <v>3993</v>
+        <v>3994</v>
       </c>
       <c r="D153" s="88" t="s">
-        <v>3994</v>
+        <v>3995</v>
       </c>
       <c r="E153" s="90" t="s">
-        <v>3995</v>
+        <v>3996</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="32.25">
@@ -23082,13 +23071,13 @@
         <v>300008746</v>
       </c>
       <c r="C154" s="88" t="s">
-        <v>3996</v>
+        <v>3997</v>
       </c>
       <c r="D154" s="88" t="s">
-        <v>3997</v>
+        <v>3998</v>
       </c>
       <c r="E154" s="90" t="s">
-        <v>3998</v>
+        <v>3999</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="16.5">
@@ -23099,13 +23088,13 @@
         <v>300379998</v>
       </c>
       <c r="C155" s="88" t="s">
-        <v>3999</v>
+        <v>4000</v>
       </c>
       <c r="D155" s="88" t="s">
-        <v>4000</v>
+        <v>4001</v>
       </c>
       <c r="E155" s="90" t="s">
-        <v>4001</v>
+        <v>4002</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="16.5">
@@ -23116,13 +23105,13 @@
         <v>300386857</v>
       </c>
       <c r="C156" s="88" t="s">
-        <v>4002</v>
+        <v>4003</v>
       </c>
       <c r="D156" s="88" t="s">
-        <v>4002</v>
+        <v>4003</v>
       </c>
       <c r="E156" s="90" t="s">
-        <v>4003</v>
+        <v>4004</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="162">
@@ -23133,13 +23122,13 @@
         <v>300266059</v>
       </c>
       <c r="C157" s="89" t="s">
-        <v>4004</v>
+        <v>4005</v>
       </c>
       <c r="D157" s="89" t="s">
-        <v>4005</v>
+        <v>4006</v>
       </c>
       <c r="E157" s="90" t="s">
-        <v>3548</v>
+        <v>3549</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="16.5">
@@ -23150,13 +23139,13 @@
         <v>300008678</v>
       </c>
       <c r="C158" s="88" t="s">
-        <v>4006</v>
+        <v>4007</v>
       </c>
       <c r="D158" s="88" t="s">
-        <v>4007</v>
+        <v>4008</v>
       </c>
       <c r="E158" s="90" t="s">
-        <v>4008</v>
+        <v>4009</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="16.5">
@@ -23167,13 +23156,13 @@
         <v>300132312</v>
       </c>
       <c r="C159" s="88" t="s">
-        <v>4009</v>
+        <v>4010</v>
       </c>
       <c r="D159" s="88" t="s">
-        <v>4009</v>
+        <v>4010</v>
       </c>
       <c r="E159" s="90" t="s">
-        <v>4010</v>
+        <v>4011</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="16.5">
@@ -23184,13 +23173,13 @@
         <v>300008707</v>
       </c>
       <c r="C160" s="88" t="s">
-        <v>4011</v>
+        <v>4012</v>
       </c>
       <c r="D160" s="88" t="s">
-        <v>4012</v>
+        <v>4013</v>
       </c>
       <c r="E160" s="90" t="s">
-        <v>4013</v>
+        <v>4014</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="32.25">
@@ -23201,13 +23190,13 @@
         <v>300008736</v>
       </c>
       <c r="C161" s="88" t="s">
-        <v>4014</v>
+        <v>4015</v>
       </c>
       <c r="D161" s="88" t="s">
-        <v>4015</v>
+        <v>4016</v>
       </c>
       <c r="E161" s="90" t="s">
-        <v>4016</v>
+        <v>4017</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="16.5">
@@ -23218,13 +23207,13 @@
         <v>300008697</v>
       </c>
       <c r="C162" s="88" t="s">
-        <v>4017</v>
+        <v>4018</v>
       </c>
       <c r="D162" s="88" t="s">
-        <v>4018</v>
+        <v>4019</v>
       </c>
       <c r="E162" s="90" t="s">
-        <v>4019</v>
+        <v>4020</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="32.25">
@@ -23235,13 +23224,13 @@
         <v>300008899</v>
       </c>
       <c r="C163" s="88" t="s">
-        <v>4020</v>
+        <v>4021</v>
       </c>
       <c r="D163" s="88" t="s">
-        <v>4021</v>
+        <v>4022</v>
       </c>
       <c r="E163" s="90" t="s">
-        <v>4022</v>
+        <v>4023</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="16.5">
@@ -23252,13 +23241,13 @@
         <v>300132316</v>
       </c>
       <c r="C164" s="88" t="s">
-        <v>4023</v>
+        <v>4024</v>
       </c>
       <c r="D164" s="88" t="s">
-        <v>4024</v>
+        <v>4025</v>
       </c>
       <c r="E164" s="90" t="s">
-        <v>4025</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="16.5">
@@ -23269,13 +23258,13 @@
         <v>300132315</v>
       </c>
       <c r="C165" s="88" t="s">
-        <v>4026</v>
+        <v>4027</v>
       </c>
       <c r="D165" s="88" t="s">
-        <v>4027</v>
+        <v>4028</v>
       </c>
       <c r="E165" s="90" t="s">
-        <v>4028</v>
+        <v>4029</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="16.5">
@@ -23286,13 +23275,13 @@
         <v>300008835</v>
       </c>
       <c r="C166" s="88" t="s">
-        <v>4029</v>
+        <v>4030</v>
       </c>
       <c r="D166" s="88" t="s">
-        <v>4030</v>
+        <v>4031</v>
       </c>
       <c r="E166" s="90" t="s">
-        <v>4031</v>
+        <v>4032</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="16.5">
@@ -23303,13 +23292,13 @@
         <v>300008676</v>
       </c>
       <c r="C167" s="88" t="s">
-        <v>4032</v>
+        <v>4033</v>
       </c>
       <c r="D167" s="88" t="s">
-        <v>4033</v>
+        <v>4034</v>
       </c>
       <c r="E167" s="90" t="s">
-        <v>4034</v>
+        <v>4035</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="16.5">
@@ -23320,13 +23309,13 @@
         <v>300008679</v>
       </c>
       <c r="C168" s="88" t="s">
-        <v>4035</v>
+        <v>4036</v>
       </c>
       <c r="D168" s="88" t="s">
-        <v>4036</v>
+        <v>4037</v>
       </c>
       <c r="E168" s="90" t="s">
-        <v>4037</v>
+        <v>4038</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="16.5">
@@ -23337,13 +23326,13 @@
         <v>300387217</v>
       </c>
       <c r="C169" s="88" t="s">
-        <v>4038</v>
+        <v>4039</v>
       </c>
       <c r="D169" s="88" t="s">
-        <v>4039</v>
+        <v>4040</v>
       </c>
       <c r="E169" s="90" t="s">
-        <v>4040</v>
+        <v>4041</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="16.5">
@@ -23354,13 +23343,13 @@
         <v>300266556</v>
       </c>
       <c r="C170" s="88" t="s">
-        <v>4041</v>
+        <v>4042</v>
       </c>
       <c r="D170" s="88" t="s">
-        <v>4042</v>
+        <v>4043</v>
       </c>
       <c r="E170" s="90" t="s">
-        <v>4043</v>
+        <v>4044</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="16.5">
@@ -23371,13 +23360,13 @@
         <v>300266558</v>
       </c>
       <c r="C171" s="88" t="s">
-        <v>4044</v>
+        <v>4045</v>
       </c>
       <c r="D171" s="88" t="s">
-        <v>4045</v>
+        <v>4046</v>
       </c>
       <c r="E171" s="90" t="s">
-        <v>4046</v>
+        <v>4047</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="32.25">
@@ -23388,13 +23377,13 @@
         <v>300008687</v>
       </c>
       <c r="C172" s="88" t="s">
-        <v>4047</v>
+        <v>4048</v>
       </c>
       <c r="D172" s="88" t="s">
-        <v>4048</v>
+        <v>4049</v>
       </c>
       <c r="E172" s="90" t="s">
-        <v>4049</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="32.25">
@@ -23405,13 +23394,13 @@
         <v>300008694</v>
       </c>
       <c r="C173" s="88" t="s">
-        <v>4050</v>
+        <v>4051</v>
       </c>
       <c r="D173" s="88" t="s">
-        <v>4051</v>
+        <v>4052</v>
       </c>
       <c r="E173" s="90" t="s">
-        <v>4052</v>
+        <v>4053</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="48.75">
@@ -23422,13 +23411,13 @@
         <v>300266571</v>
       </c>
       <c r="C174" s="88" t="s">
-        <v>4053</v>
+        <v>4054</v>
       </c>
       <c r="D174" s="88" t="s">
-        <v>4054</v>
+        <v>4055</v>
       </c>
       <c r="E174" s="90" t="s">
-        <v>4055</v>
+        <v>4056</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="16.5">
@@ -23439,13 +23428,13 @@
         <v>300008680</v>
       </c>
       <c r="C175" s="88" t="s">
-        <v>4056</v>
+        <v>4057</v>
       </c>
       <c r="D175" s="88" t="s">
-        <v>4057</v>
+        <v>4058</v>
       </c>
       <c r="E175" s="90" t="s">
-        <v>4058</v>
+        <v>4059</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="16.5">
@@ -23456,13 +23445,13 @@
         <v>300387029</v>
       </c>
       <c r="C176" s="88" t="s">
-        <v>4059</v>
+        <v>4060</v>
       </c>
       <c r="D176" s="88" t="s">
-        <v>4060</v>
+        <v>4061</v>
       </c>
       <c r="E176" s="90" t="s">
-        <v>4061</v>
+        <v>4062</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="16.5">
@@ -23473,13 +23462,13 @@
         <v>300185707</v>
       </c>
       <c r="C177" s="88" t="s">
-        <v>4062</v>
+        <v>4063</v>
       </c>
       <c r="D177" s="88" t="s">
-        <v>4063</v>
+        <v>4064</v>
       </c>
       <c r="E177" s="90" t="s">
-        <v>4064</v>
+        <v>4065</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="32.25">
@@ -23490,13 +23479,13 @@
         <v>300008932</v>
       </c>
       <c r="C178" s="89" t="s">
-        <v>4065</v>
+        <v>4066</v>
       </c>
       <c r="D178" s="89" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="E178" s="90" t="s">
-        <v>4067</v>
+        <v>4068</v>
       </c>
     </row>
   </sheetData>
@@ -33621,7 +33610,7 @@
   <sheetFormatPr defaultColWidth="30.625" defaultRowHeight="72.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.75" style="109" customWidth="1"/>
-    <col min="2" max="2" width="8.125" style="75" customWidth="1"/>
+    <col min="2" max="2" width="15.75" style="75" customWidth="1"/>
     <col min="3" max="3" width="21.875" style="75" customWidth="1"/>
     <col min="4" max="4" width="18.875" style="75" customWidth="1"/>
     <col min="5" max="5" width="9.5" style="75" customWidth="1"/>
@@ -37866,7 +37855,7 @@
       <c r="AR39" s="160"/>
       <c r="AS39" s="160"/>
       <c r="AT39" s="160"/>
-      <c r="AU39" s="277" t="s">
+      <c r="AU39" s="160" t="s">
         <v>2205</v>
       </c>
       <c r="AV39" s="160"/>
@@ -42458,28 +42447,28 @@
       <c r="B85" s="193" t="s">
         <v>168</v>
       </c>
-      <c r="C85" s="278" t="s">
+      <c r="C85" s="159" t="s">
         <v>2374</v>
       </c>
-      <c r="D85" s="279" t="s">
+      <c r="D85" s="164" t="s">
         <v>2375</v>
       </c>
       <c r="E85" s="164"/>
-      <c r="F85" s="280" t="s">
+      <c r="F85" s="165" t="s">
         <v>2376</v>
       </c>
-      <c r="G85" s="280"/>
-      <c r="H85" s="280"/>
-      <c r="I85" s="280"/>
-      <c r="J85" s="280"/>
-      <c r="K85" s="280"/>
-      <c r="L85" s="280"/>
+      <c r="G85" s="165"/>
+      <c r="H85" s="165"/>
+      <c r="I85" s="165"/>
+      <c r="J85" s="165"/>
+      <c r="K85" s="165"/>
+      <c r="L85" s="165"/>
       <c r="M85" s="161"/>
-      <c r="N85" s="281"/>
+      <c r="N85" s="126"/>
       <c r="O85" s="162"/>
-      <c r="P85" s="281"/>
-      <c r="Q85" s="281"/>
-      <c r="R85" s="281"/>
+      <c r="P85" s="126"/>
+      <c r="Q85" s="126"/>
+      <c r="R85" s="126"/>
       <c r="S85" s="163"/>
       <c r="T85" s="163"/>
       <c r="U85" s="161"/>
@@ -42488,45 +42477,45 @@
       <c r="X85" s="161"/>
       <c r="Y85" s="161"/>
       <c r="Z85" s="127"/>
-      <c r="AA85" s="277" t="s">
+      <c r="AA85" s="160" t="s">
         <v>2377</v>
       </c>
       <c r="AB85" s="182"/>
-      <c r="AC85" s="277"/>
-      <c r="AD85" s="277"/>
+      <c r="AC85" s="160"/>
+      <c r="AD85" s="160"/>
       <c r="AE85" s="197"/>
-      <c r="AF85" s="277"/>
-      <c r="AG85" s="277"/>
+      <c r="AF85" s="160"/>
+      <c r="AG85" s="160"/>
       <c r="AH85" s="197"/>
-      <c r="AI85" s="277"/>
-      <c r="AJ85" s="277"/>
+      <c r="AI85" s="160"/>
+      <c r="AJ85" s="160"/>
       <c r="AK85" s="197"/>
-      <c r="AL85" s="277"/>
+      <c r="AL85" s="160"/>
       <c r="AM85" t="s">
         <v>2378</v>
       </c>
-      <c r="AN85" s="277" t="s">
+      <c r="AN85" s="160" t="s">
         <v>2379</v>
       </c>
-      <c r="AO85" s="277"/>
-      <c r="AP85" s="277"/>
-      <c r="AQ85" s="277"/>
-      <c r="AR85" s="277" t="s">
+      <c r="AO85" s="160"/>
+      <c r="AP85" s="160"/>
+      <c r="AQ85" s="160"/>
+      <c r="AR85" s="160" t="s">
         <v>2380</v>
       </c>
-      <c r="AS85" s="277"/>
-      <c r="AT85" s="277"/>
-      <c r="AU85" s="277" t="s">
+      <c r="AS85" s="160"/>
+      <c r="AT85" s="160"/>
+      <c r="AU85" s="160" t="s">
         <v>2381</v>
       </c>
       <c r="AV85" s="160"/>
       <c r="AW85" s="160"/>
       <c r="AX85" s="160"/>
-      <c r="AY85" s="277"/>
-      <c r="AZ85" s="277"/>
-      <c r="BA85" s="277"/>
-      <c r="BB85" s="277"/>
-      <c r="BC85" s="277"/>
+      <c r="AY85" s="160"/>
+      <c r="AZ85" s="160"/>
+      <c r="BA85" s="160"/>
+      <c r="BB85" s="160"/>
+      <c r="BC85" s="160"/>
       <c r="BD85" s="205"/>
       <c r="BE85" s="132"/>
       <c r="BF85" s="132"/>

--- a/data/Herrnhuter NaturkundlerInnen.xlsx
+++ b/data/Herrnhuter NaturkundlerInnen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tudresdende-my.sharepoint.com/personal/s5468259_tu-dresden_de/Documents/Herrnhut BMBF/Personenlexikon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11217" documentId="11_7EEC7FA32A5B5C2B1F465E45D27E15B46640A7DA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{269BA793-8020-472C-BF1F-39BE7CE8C872}"/>
+  <xr:revisionPtr revIDLastSave="11224" documentId="11_7EEC7FA32A5B5C2B1F465E45D27E15B46640A7DA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CDA363E-C241-48BB-BF1C-70DEFDB68368}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="14100" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="14100" firstSheet="8" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Objekte TU DR und andere" sheetId="5" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7688" uniqueCount="4392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7692" uniqueCount="4396">
   <si>
     <t>interessante Belege in DR</t>
   </si>
@@ -12059,7 +12059,7 @@
     <t>University of Tartu</t>
   </si>
   <si>
-    <t>c-suzhou</t>
+    <t>C-suzhou</t>
   </si>
   <si>
     <t>C-US</t>
@@ -13810,6 +13810,12 @@
     <t>L0013000</t>
   </si>
   <si>
+    <t>Igdlorpait | Illorpaat</t>
+  </si>
+  <si>
+    <t>https://www.wikidata.org/wiki/Q67087304</t>
+  </si>
+  <si>
     <t>L0014000</t>
   </si>
   <si>
@@ -13904,6 +13910,9 @@
   </si>
   <si>
     <t>Salem</t>
+  </si>
+  <si>
+    <t>https://www.wikidata.org/wiki/Q2027197</t>
   </si>
   <si>
     <t>L0023000</t>
@@ -13957,6 +13966,9 @@
   </si>
   <si>
     <t>Meisenheim am Glan</t>
+  </si>
+  <si>
+    <t>https://www.wikidata.org/wiki/Q520103</t>
   </si>
   <si>
     <r>
@@ -16772,7 +16784,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -16881,6 +16893,12 @@
         <bgColor theme="8" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -16950,7 +16968,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="297">
+  <cellXfs count="293">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -17773,25 +17791,13 @@
     <xf numFmtId="49" fontId="30" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="126">
     <dxf>
@@ -20806,10 +20812,10 @@
   <sheetData>
     <row r="1" spans="1:5" s="102" customFormat="1" ht="32.25">
       <c r="A1" s="119" t="s">
-        <v>3674</v>
+        <v>3678</v>
       </c>
       <c r="B1" s="119" t="s">
-        <v>3675</v>
+        <v>3679</v>
       </c>
       <c r="C1" s="119" t="s">
         <v>3240</v>
@@ -20818,7 +20824,7 @@
         <v>3241</v>
       </c>
       <c r="E1" s="119" t="s">
-        <v>3676</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="32.25">
@@ -20826,7 +20832,7 @@
         <v>3009</v>
       </c>
       <c r="B2" s="126" t="s">
-        <v>3677</v>
+        <v>3681</v>
       </c>
       <c r="C2" s="182"/>
       <c r="D2" s="126"/>
@@ -20834,10 +20840,10 @@
     </row>
     <row r="3" spans="1:5" ht="32.25">
       <c r="A3" s="182" t="s">
-        <v>3678</v>
+        <v>3682</v>
       </c>
       <c r="B3" s="126" t="s">
-        <v>3679</v>
+        <v>3683</v>
       </c>
       <c r="C3" s="182"/>
       <c r="D3" s="126"/>
@@ -20845,16 +20851,16 @@
     </row>
     <row r="4" spans="1:5" ht="48.75">
       <c r="A4" s="182" t="s">
-        <v>3680</v>
+        <v>3684</v>
       </c>
       <c r="B4" s="126" t="s">
-        <v>3681</v>
+        <v>3685</v>
       </c>
       <c r="C4" s="183" t="s">
-        <v>3682</v>
+        <v>3686</v>
       </c>
       <c r="D4" s="126" t="s">
-        <v>3683</v>
+        <v>3687</v>
       </c>
       <c r="E4" s="182"/>
     </row>
@@ -20863,7 +20869,7 @@
         <v>2270</v>
       </c>
       <c r="B5" s="126" t="s">
-        <v>3684</v>
+        <v>3688</v>
       </c>
       <c r="C5" s="182"/>
       <c r="D5" s="126"/>
@@ -20874,7 +20880,7 @@
         <v>2368</v>
       </c>
       <c r="B6" s="126" t="s">
-        <v>3685</v>
+        <v>3689</v>
       </c>
       <c r="C6" s="182"/>
       <c r="D6" s="126"/>
@@ -20882,13 +20888,13 @@
     </row>
     <row r="7" spans="1:5" ht="32.25">
       <c r="A7" s="182" t="s">
-        <v>3686</v>
+        <v>3690</v>
       </c>
       <c r="B7" s="126" t="s">
-        <v>3687</v>
+        <v>3691</v>
       </c>
       <c r="C7" s="184" t="s">
-        <v>3688</v>
+        <v>3692</v>
       </c>
       <c r="D7" s="126"/>
       <c r="E7" s="182"/>
@@ -20898,38 +20904,38 @@
         <v>2061</v>
       </c>
       <c r="B8" s="126" t="s">
-        <v>3689</v>
+        <v>3693</v>
       </c>
       <c r="C8" s="183" t="s">
-        <v>3690</v>
+        <v>3694</v>
       </c>
       <c r="D8" s="182" t="s">
-        <v>3691</v>
+        <v>3695</v>
       </c>
       <c r="E8" s="182"/>
     </row>
     <row r="9" spans="1:5" ht="32.25">
       <c r="A9" s="182" t="s">
-        <v>3692</v>
+        <v>3696</v>
       </c>
       <c r="B9" t="s">
-        <v>3693</v>
+        <v>3697</v>
       </c>
       <c r="C9" s="61"/>
       <c r="D9" s="126" t="s">
-        <v>3694</v>
+        <v>3698</v>
       </c>
       <c r="E9" s="182"/>
     </row>
     <row r="10" spans="1:5" ht="16.5">
       <c r="A10" s="182" t="s">
-        <v>3695</v>
+        <v>3699</v>
       </c>
       <c r="B10" s="126" t="s">
-        <v>3696</v>
+        <v>3700</v>
       </c>
       <c r="C10" s="183" t="s">
-        <v>3697</v>
+        <v>3701</v>
       </c>
       <c r="D10" s="126"/>
       <c r="E10" s="182"/>
@@ -20939,23 +20945,23 @@
         <v>2036</v>
       </c>
       <c r="B11" s="126" t="s">
-        <v>3698</v>
+        <v>3702</v>
       </c>
       <c r="C11" s="183" t="s">
-        <v>3699</v>
+        <v>3703</v>
       </c>
       <c r="D11" s="126"/>
       <c r="E11" s="182"/>
     </row>
     <row r="12" spans="1:5" ht="32.25">
       <c r="A12" s="182" t="s">
-        <v>3700</v>
+        <v>3704</v>
       </c>
       <c r="B12" s="126" t="s">
-        <v>3701</v>
+        <v>3705</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="D12" s="126"/>
       <c r="E12" s="182"/>
@@ -20965,37 +20971,37 @@
         <v>2892</v>
       </c>
       <c r="B13" s="126" t="s">
-        <v>3703</v>
+        <v>3707</v>
       </c>
       <c r="C13" s="183" t="s">
-        <v>3704</v>
+        <v>3708</v>
       </c>
       <c r="D13" s="126" t="s">
-        <v>3705</v>
+        <v>3709</v>
       </c>
       <c r="E13" s="182"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="182" t="s">
-        <v>3706</v>
+        <v>3710</v>
       </c>
       <c r="B14" s="126" t="s">
-        <v>3707</v>
+        <v>3711</v>
       </c>
       <c r="C14" s="183" t="s">
-        <v>3708</v>
+        <v>3712</v>
       </c>
       <c r="D14" s="126" t="s">
-        <v>3709</v>
+        <v>3713</v>
       </c>
       <c r="E14" s="182"/>
     </row>
     <row r="15" spans="1:5" ht="32.25">
       <c r="A15" s="182" t="s">
-        <v>3710</v>
+        <v>3714</v>
       </c>
       <c r="B15" s="126" t="s">
-        <v>3711</v>
+        <v>3715</v>
       </c>
       <c r="C15" s="182"/>
       <c r="D15" s="126"/>
@@ -21006,22 +21012,22 @@
         <v>2029</v>
       </c>
       <c r="B16" s="126" t="s">
-        <v>3712</v>
+        <v>3716</v>
       </c>
       <c r="C16" s="242" t="s">
-        <v>3713</v>
+        <v>3717</v>
       </c>
       <c r="D16" s="126" t="s">
-        <v>3714</v>
+        <v>3718</v>
       </c>
       <c r="E16" s="182"/>
     </row>
     <row r="17" spans="1:5" ht="32.25">
       <c r="A17" s="182" t="s">
-        <v>3715</v>
+        <v>3719</v>
       </c>
       <c r="B17" s="126" t="s">
-        <v>3716</v>
+        <v>3720</v>
       </c>
       <c r="C17" s="182"/>
       <c r="D17" s="126"/>
@@ -21029,16 +21035,16 @@
     </row>
     <row r="18" spans="1:5" ht="64.5">
       <c r="A18" s="182" t="s">
-        <v>3717</v>
+        <v>3721</v>
       </c>
       <c r="B18" s="126" t="s">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="C18" s="183" t="s">
-        <v>3719</v>
+        <v>3723</v>
       </c>
       <c r="D18" s="126" t="s">
-        <v>3720</v>
+        <v>3724</v>
       </c>
       <c r="E18" s="182"/>
     </row>
@@ -21051,17 +21057,17 @@
     </row>
     <row r="20" spans="1:5" ht="32.25">
       <c r="A20" s="256" t="s">
-        <v>3721</v>
+        <v>3725</v>
       </c>
       <c r="B20" s="126" t="s">
-        <v>3722</v>
+        <v>3726</v>
       </c>
       <c r="C20" s="183" t="s">
-        <v>3723</v>
+        <v>3727</v>
       </c>
       <c r="D20" s="126"/>
       <c r="E20" s="183" t="s">
-        <v>3724</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="32.25">
@@ -21069,43 +21075,43 @@
         <v>2994</v>
       </c>
       <c r="B21" s="126" t="s">
-        <v>3725</v>
+        <v>3729</v>
       </c>
       <c r="C21" s="183" t="s">
-        <v>3726</v>
+        <v>3730</v>
       </c>
       <c r="D21" s="126" t="s">
-        <v>3727</v>
+        <v>3731</v>
       </c>
       <c r="E21" s="182"/>
     </row>
     <row r="22" spans="1:5" ht="48.75">
       <c r="A22" s="256" t="s">
-        <v>3728</v>
+        <v>3732</v>
       </c>
       <c r="B22" s="126" t="s">
-        <v>3729</v>
+        <v>3733</v>
       </c>
       <c r="C22" s="183" t="s">
-        <v>3730</v>
+        <v>3734</v>
       </c>
       <c r="D22" s="126" t="s">
-        <v>3731</v>
+        <v>3735</v>
       </c>
       <c r="E22" s="182"/>
     </row>
     <row r="23" spans="1:5" ht="32.25">
       <c r="A23" s="256" t="s">
-        <v>3732</v>
+        <v>3736</v>
       </c>
       <c r="B23" s="126" t="s">
-        <v>3733</v>
+        <v>3737</v>
       </c>
       <c r="C23" s="183" t="s">
-        <v>3734</v>
+        <v>3738</v>
       </c>
       <c r="D23" s="126" t="s">
-        <v>3735</v>
+        <v>3739</v>
       </c>
       <c r="E23" s="182"/>
     </row>
@@ -21117,22 +21123,22 @@
         <v>752</v>
       </c>
       <c r="C24" s="183" t="s">
-        <v>3736</v>
+        <v>3740</v>
       </c>
       <c r="D24" s="126"/>
       <c r="E24" s="183" t="s">
-        <v>3737</v>
+        <v>3741</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="48.75">
       <c r="A25" s="256" t="s">
-        <v>3738</v>
+        <v>3742</v>
       </c>
       <c r="B25" s="126" t="s">
-        <v>3739</v>
+        <v>3743</v>
       </c>
       <c r="C25" s="183" t="s">
-        <v>3740</v>
+        <v>3744</v>
       </c>
       <c r="D25" s="126"/>
       <c r="E25" s="182"/>
@@ -21142,91 +21148,91 @@
         <v>2215</v>
       </c>
       <c r="B26" s="195" t="s">
-        <v>3741</v>
+        <v>3745</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>3742</v>
+        <v>3746</v>
       </c>
       <c r="D26" s="126"/>
       <c r="E26" s="183" t="s">
-        <v>3743</v>
+        <v>3747</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="64.5">
       <c r="A27" s="256" t="s">
-        <v>3744</v>
+        <v>3748</v>
       </c>
       <c r="B27" s="126" t="s">
-        <v>3745</v>
+        <v>3749</v>
       </c>
       <c r="C27" s="183" t="s">
-        <v>3746</v>
+        <v>3750</v>
       </c>
       <c r="D27" s="126" t="s">
-        <v>3747</v>
+        <v>3751</v>
       </c>
       <c r="E27" s="183" t="s">
-        <v>3748</v>
+        <v>3752</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="32.25">
       <c r="A28" s="256" t="s">
-        <v>3749</v>
+        <v>3753</v>
       </c>
       <c r="B28" s="126" t="s">
-        <v>3750</v>
+        <v>3754</v>
       </c>
       <c r="C28" s="183" t="s">
-        <v>3751</v>
+        <v>3755</v>
       </c>
       <c r="D28" s="126"/>
       <c r="E28" s="182"/>
     </row>
     <row r="29" spans="1:5" ht="32.25">
       <c r="A29" s="256" t="s">
-        <v>3752</v>
+        <v>3756</v>
       </c>
       <c r="B29" s="126" t="s">
-        <v>3753</v>
+        <v>3757</v>
       </c>
       <c r="C29" s="182"/>
       <c r="D29" s="126" t="s">
-        <v>3754</v>
+        <v>3758</v>
       </c>
       <c r="E29" s="182"/>
     </row>
     <row r="30" spans="1:5" ht="32.25">
       <c r="A30" s="256" t="s">
-        <v>3755</v>
+        <v>3759</v>
       </c>
       <c r="B30" s="126" t="s">
-        <v>3756</v>
+        <v>3760</v>
       </c>
       <c r="C30" s="182"/>
       <c r="D30" s="126" t="s">
-        <v>3757</v>
+        <v>3761</v>
       </c>
       <c r="E30" s="182"/>
     </row>
     <row r="31" spans="1:5" ht="48.75">
       <c r="A31" s="256" t="s">
-        <v>3758</v>
+        <v>3762</v>
       </c>
       <c r="B31" s="126" t="s">
-        <v>3759</v>
+        <v>3763</v>
       </c>
       <c r="C31" s="182"/>
       <c r="D31" s="126" t="s">
-        <v>3757</v>
+        <v>3761</v>
       </c>
       <c r="E31" s="182"/>
     </row>
     <row r="32" spans="1:5" ht="48.75">
       <c r="A32" s="256" t="s">
-        <v>3760</v>
+        <v>3764</v>
       </c>
       <c r="B32" s="126" t="s">
-        <v>3761</v>
+        <v>3765</v>
       </c>
       <c r="C32" s="182"/>
       <c r="D32" s="126"/>
@@ -21237,10 +21243,10 @@
         <v>2240</v>
       </c>
       <c r="B33" s="126" t="s">
-        <v>3762</v>
+        <v>3766</v>
       </c>
       <c r="C33" s="183" t="s">
-        <v>3763</v>
+        <v>3767</v>
       </c>
       <c r="D33" s="126"/>
       <c r="E33" s="182"/>
@@ -21250,40 +21256,40 @@
         <v>3010</v>
       </c>
       <c r="B34" s="274" t="s">
-        <v>3764</v>
+        <v>3768</v>
       </c>
       <c r="C34" s="183" t="s">
-        <v>3765</v>
+        <v>3769</v>
       </c>
       <c r="D34" t="s">
-        <v>3766</v>
+        <v>3770</v>
       </c>
       <c r="E34" s="182"/>
     </row>
     <row r="35" spans="1:5" ht="16.5">
       <c r="A35" s="256" t="s">
-        <v>3767</v>
+        <v>3771</v>
       </c>
       <c r="B35" s="274" t="s">
-        <v>3768</v>
+        <v>3772</v>
       </c>
       <c r="C35" s="183" t="s">
-        <v>3769</v>
+        <v>3773</v>
       </c>
       <c r="D35" s="126" t="s">
-        <v>3770</v>
+        <v>3774</v>
       </c>
       <c r="E35" s="182"/>
     </row>
     <row r="36" spans="1:5" ht="32.25">
       <c r="A36" s="256" t="s">
-        <v>3771</v>
+        <v>3775</v>
       </c>
       <c r="B36" s="126" t="s">
-        <v>3772</v>
+        <v>3776</v>
       </c>
       <c r="C36" s="183" t="s">
-        <v>3773</v>
+        <v>3777</v>
       </c>
       <c r="D36" s="126"/>
       <c r="E36" s="182"/>
@@ -21293,39 +21299,39 @@
         <v>2558</v>
       </c>
       <c r="B37" s="126" t="s">
-        <v>3774</v>
+        <v>3778</v>
       </c>
       <c r="C37" s="182"/>
       <c r="D37" s="126" t="s">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="E37" s="182"/>
     </row>
     <row r="38" spans="1:5" ht="48.75">
       <c r="A38" s="182" t="s">
-        <v>3776</v>
+        <v>3780</v>
       </c>
       <c r="B38" s="126" t="s">
-        <v>3777</v>
+        <v>3781</v>
       </c>
       <c r="C38" s="182"/>
       <c r="D38" s="126" t="s">
-        <v>3778</v>
+        <v>3782</v>
       </c>
       <c r="E38" s="182"/>
     </row>
     <row r="39" spans="1:5" ht="32.25">
       <c r="A39" s="256" t="s">
-        <v>3779</v>
+        <v>3783</v>
       </c>
       <c r="B39" s="126" t="s">
-        <v>3780</v>
+        <v>3784</v>
       </c>
       <c r="C39" s="183" t="s">
-        <v>3781</v>
+        <v>3785</v>
       </c>
       <c r="D39" s="126" t="s">
-        <v>3782</v>
+        <v>3786</v>
       </c>
       <c r="E39" s="182"/>
     </row>
@@ -21334,39 +21340,39 @@
         <v>2313</v>
       </c>
       <c r="B40" s="126" t="s">
-        <v>3783</v>
+        <v>3787</v>
       </c>
       <c r="C40" s="183" t="s">
-        <v>3784</v>
+        <v>3788</v>
       </c>
       <c r="D40" s="126"/>
       <c r="E40" s="182"/>
     </row>
     <row r="41" spans="1:5" ht="32.25">
       <c r="A41" s="256" t="s">
-        <v>3785</v>
+        <v>3789</v>
       </c>
       <c r="B41" s="126" t="s">
-        <v>3786</v>
+        <v>3790</v>
       </c>
       <c r="C41" s="182"/>
       <c r="D41" s="126" t="s">
-        <v>3787</v>
+        <v>3791</v>
       </c>
       <c r="E41" s="182"/>
     </row>
     <row r="42" spans="1:5" ht="32.25">
       <c r="A42" s="182" t="s">
-        <v>3788</v>
+        <v>3792</v>
       </c>
       <c r="B42" s="126" t="s">
-        <v>3789</v>
+        <v>3793</v>
       </c>
       <c r="C42" s="183" t="s">
-        <v>3790</v>
+        <v>3794</v>
       </c>
       <c r="D42" s="126" t="s">
-        <v>3791</v>
+        <v>3795</v>
       </c>
       <c r="E42" s="182"/>
     </row>
@@ -21375,20 +21381,20 @@
         <v>2866</v>
       </c>
       <c r="B43" s="126" t="s">
-        <v>3792</v>
+        <v>3796</v>
       </c>
       <c r="C43" s="182"/>
       <c r="D43" s="126" t="s">
-        <v>3793</v>
+        <v>3797</v>
       </c>
       <c r="E43" s="182"/>
     </row>
     <row r="44" spans="1:5" ht="32.25">
       <c r="A44" s="182" t="s">
-        <v>3794</v>
+        <v>3798</v>
       </c>
       <c r="B44" s="126" t="s">
-        <v>3795</v>
+        <v>3799</v>
       </c>
       <c r="C44" s="182"/>
       <c r="D44" s="126"/>
@@ -21396,38 +21402,38 @@
     </row>
     <row r="45" spans="1:5" ht="32.25">
       <c r="A45" s="256" t="s">
-        <v>3796</v>
+        <v>3800</v>
       </c>
       <c r="B45" s="126" t="s">
-        <v>3797</v>
+        <v>3801</v>
       </c>
       <c r="C45" s="183" t="s">
-        <v>3798</v>
+        <v>3802</v>
       </c>
       <c r="D45" s="126" t="s">
-        <v>3799</v>
+        <v>3803</v>
       </c>
       <c r="E45" s="182"/>
     </row>
     <row r="46" spans="1:5" ht="48.75">
       <c r="A46" s="182" t="s">
-        <v>3800</v>
+        <v>3804</v>
       </c>
       <c r="B46" s="126" t="s">
-        <v>3801</v>
+        <v>3805</v>
       </c>
       <c r="C46" s="182"/>
       <c r="D46" s="126" t="s">
-        <v>3802</v>
+        <v>3806</v>
       </c>
       <c r="E46" s="182"/>
     </row>
     <row r="47" spans="1:5" ht="32.25">
       <c r="A47" s="256" t="s">
-        <v>3803</v>
+        <v>3807</v>
       </c>
       <c r="B47" s="126" t="s">
-        <v>3804</v>
+        <v>3808</v>
       </c>
       <c r="C47" s="182"/>
       <c r="D47" s="126"/>
@@ -21438,11 +21444,11 @@
         <v>2400</v>
       </c>
       <c r="B48" s="126" t="s">
-        <v>3805</v>
+        <v>3809</v>
       </c>
       <c r="C48" s="182"/>
       <c r="D48" s="126" t="s">
-        <v>3806</v>
+        <v>3810</v>
       </c>
       <c r="E48" s="182"/>
     </row>
@@ -21451,26 +21457,26 @@
         <v>2464</v>
       </c>
       <c r="B49" s="126" t="s">
-        <v>3807</v>
+        <v>3811</v>
       </c>
       <c r="C49" s="182"/>
       <c r="D49" s="126" t="s">
-        <v>3808</v>
+        <v>3812</v>
       </c>
       <c r="E49" s="182"/>
     </row>
     <row r="50" spans="1:5" ht="32.25">
       <c r="A50" s="182" t="s">
-        <v>3809</v>
+        <v>3813</v>
       </c>
       <c r="B50" s="126" t="s">
-        <v>3810</v>
+        <v>3814</v>
       </c>
       <c r="C50" s="183" t="s">
-        <v>3811</v>
+        <v>3815</v>
       </c>
       <c r="D50" s="126" t="s">
-        <v>3812</v>
+        <v>3816</v>
       </c>
       <c r="E50" s="182"/>
     </row>
@@ -21479,7 +21485,7 @@
         <v>2555</v>
       </c>
       <c r="B51" s="126" t="s">
-        <v>3813</v>
+        <v>3817</v>
       </c>
       <c r="C51" s="182"/>
       <c r="D51" s="126"/>
@@ -21487,23 +21493,23 @@
     </row>
     <row r="52" spans="1:5" ht="81">
       <c r="A52" s="182" t="s">
-        <v>3814</v>
+        <v>3818</v>
       </c>
       <c r="B52" s="126" t="s">
-        <v>3815</v>
+        <v>3819</v>
       </c>
       <c r="C52" s="183" t="s">
-        <v>3816</v>
+        <v>3820</v>
       </c>
       <c r="D52" s="126"/>
       <c r="E52" s="182"/>
     </row>
     <row r="53" spans="1:5" ht="16.5">
       <c r="A53" s="182" t="s">
-        <v>3817</v>
+        <v>3821</v>
       </c>
       <c r="B53" s="126" t="s">
-        <v>3818</v>
+        <v>3822</v>
       </c>
       <c r="C53" s="182"/>
       <c r="D53" s="126"/>
@@ -21511,23 +21517,23 @@
     </row>
     <row r="54" spans="1:5" ht="48.75">
       <c r="A54" s="182" t="s">
-        <v>3819</v>
+        <v>3823</v>
       </c>
       <c r="B54" s="126" t="s">
-        <v>3820</v>
+        <v>3824</v>
       </c>
       <c r="C54" s="182"/>
       <c r="D54" s="126" t="s">
-        <v>3821</v>
+        <v>3825</v>
       </c>
       <c r="E54" s="182"/>
     </row>
     <row r="55" spans="1:5" ht="48.75">
       <c r="A55" s="256" t="s">
-        <v>3822</v>
+        <v>3826</v>
       </c>
       <c r="B55" s="126" t="s">
-        <v>3823</v>
+        <v>3827</v>
       </c>
       <c r="C55" s="182"/>
       <c r="D55" s="126"/>
@@ -21535,33 +21541,33 @@
     </row>
     <row r="56" spans="1:5" ht="48.75">
       <c r="A56" s="182" t="s">
-        <v>3824</v>
+        <v>3828</v>
       </c>
       <c r="B56" s="126" t="s">
-        <v>3825</v>
+        <v>3829</v>
       </c>
       <c r="C56" s="182"/>
       <c r="D56" s="126" t="s">
-        <v>3826</v>
+        <v>3830</v>
       </c>
       <c r="E56" s="182"/>
     </row>
     <row r="57" spans="1:5" ht="32.25">
       <c r="A57" s="182" t="s">
-        <v>3827</v>
+        <v>3831</v>
       </c>
       <c r="B57" s="126" t="s">
-        <v>3828</v>
+        <v>3832</v>
       </c>
       <c r="C57" s="183" t="s">
-        <v>3829</v>
+        <v>3833</v>
       </c>
       <c r="D57" s="126"/>
       <c r="E57" s="182"/>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="182" t="s">
-        <v>3830</v>
+        <v>3834</v>
       </c>
       <c r="B58" s="126"/>
       <c r="C58" s="182"/>
@@ -21570,7 +21576,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="256" t="s">
-        <v>3831</v>
+        <v>3835</v>
       </c>
       <c r="B59" s="126"/>
       <c r="C59" s="182"/>
@@ -21638,19 +21644,19 @@
   <sheetData>
     <row r="1" spans="1:5" ht="29.25" customHeight="1">
       <c r="A1" s="118" t="s">
-        <v>3674</v>
+        <v>3678</v>
       </c>
       <c r="B1" s="118" t="s">
-        <v>3832</v>
+        <v>3836</v>
       </c>
       <c r="C1" s="118" t="s">
-        <v>3833</v>
+        <v>3837</v>
       </c>
       <c r="D1" s="120" t="s">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1" s="118" t="s">
-        <v>3835</v>
+        <v>3839</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5">
@@ -21658,13 +21664,13 @@
         <v>3244</v>
       </c>
       <c r="B2" s="164" t="s">
-        <v>3836</v>
+        <v>3840</v>
       </c>
       <c r="C2" s="185" t="s">
-        <v>3837</v>
+        <v>3841</v>
       </c>
       <c r="D2" s="186" t="s">
-        <v>3838</v>
+        <v>3842</v>
       </c>
       <c r="E2" s="185"/>
     </row>
@@ -21673,24 +21679,24 @@
         <v>3257</v>
       </c>
       <c r="B3" s="181" t="s">
-        <v>3839</v>
+        <v>3843</v>
       </c>
       <c r="C3" s="185"/>
       <c r="D3" s="186" t="s">
-        <v>3840</v>
+        <v>3844</v>
       </c>
       <c r="E3" s="185"/>
     </row>
     <row r="4" spans="1:5" ht="32.25">
       <c r="A4" s="185" t="s">
-        <v>3841</v>
+        <v>3845</v>
       </c>
       <c r="B4" s="126" t="s">
-        <v>3842</v>
+        <v>3846</v>
       </c>
       <c r="C4" s="185"/>
       <c r="D4" s="186" t="s">
-        <v>3843</v>
+        <v>3847</v>
       </c>
       <c r="E4" s="185"/>
     </row>
@@ -21699,11 +21705,11 @@
         <v>3265</v>
       </c>
       <c r="B5" s="179" t="s">
-        <v>3844</v>
+        <v>3848</v>
       </c>
       <c r="C5" s="185"/>
       <c r="D5" s="186" t="s">
-        <v>3845</v>
+        <v>3849</v>
       </c>
       <c r="E5" s="185"/>
     </row>
@@ -21712,11 +21718,11 @@
         <v>3317</v>
       </c>
       <c r="B6" t="s">
-        <v>3846</v>
+        <v>3850</v>
       </c>
       <c r="C6" s="185"/>
       <c r="D6" s="186" t="s">
-        <v>3847</v>
+        <v>3851</v>
       </c>
       <c r="E6" s="185"/>
     </row>
@@ -21725,22 +21731,22 @@
         <v>3400</v>
       </c>
       <c r="B7" s="185" t="s">
-        <v>3848</v>
+        <v>3852</v>
       </c>
       <c r="C7" s="185" t="s">
-        <v>3849</v>
+        <v>3853</v>
       </c>
       <c r="D7" s="186" t="s">
-        <v>3850</v>
+        <v>3854</v>
       </c>
       <c r="E7" s="185"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="185" t="s">
-        <v>3851</v>
+        <v>3855</v>
       </c>
       <c r="B8" s="185" t="s">
-        <v>3852</v>
+        <v>3856</v>
       </c>
       <c r="C8" s="185"/>
       <c r="D8" s="186"/>
@@ -21751,12 +21757,12 @@
         <v>3445</v>
       </c>
       <c r="B9" s="126" t="s">
-        <v>3853</v>
+        <v>3857</v>
       </c>
       <c r="C9" s="185"/>
       <c r="D9" s="186"/>
       <c r="E9" s="185" t="s">
-        <v>3854</v>
+        <v>3858</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -21764,13 +21770,13 @@
         <v>3476</v>
       </c>
       <c r="B10" s="185" t="s">
-        <v>3855</v>
+        <v>3859</v>
       </c>
       <c r="C10" s="185" t="s">
-        <v>3856</v>
+        <v>3860</v>
       </c>
       <c r="D10" s="186" t="s">
-        <v>3857</v>
+        <v>3861</v>
       </c>
       <c r="E10" s="185"/>
     </row>
@@ -21779,10 +21785,10 @@
         <v>3558</v>
       </c>
       <c r="B11" s="185" t="s">
-        <v>3858</v>
+        <v>3862</v>
       </c>
       <c r="C11" s="185" t="s">
-        <v>3859</v>
+        <v>3863</v>
       </c>
       <c r="D11" s="186"/>
       <c r="E11" s="185"/>
@@ -21792,7 +21798,7 @@
         <v>3269</v>
       </c>
       <c r="B12" t="s">
-        <v>3860</v>
+        <v>3864</v>
       </c>
       <c r="C12" s="185"/>
       <c r="D12" s="186"/>
@@ -21800,7 +21806,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="185" t="s">
-        <v>3861</v>
+        <v>3865</v>
       </c>
       <c r="B13" s="185"/>
       <c r="C13" s="185"/>
@@ -21809,7 +21815,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="185" t="s">
-        <v>3862</v>
+        <v>3866</v>
       </c>
       <c r="B14" s="185"/>
       <c r="C14" s="185"/>
@@ -21818,7 +21824,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="185" t="s">
-        <v>3863</v>
+        <v>3867</v>
       </c>
       <c r="B15" s="185"/>
       <c r="C15" s="185"/>
@@ -21827,7 +21833,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="185" t="s">
-        <v>3864</v>
+        <v>3868</v>
       </c>
       <c r="B16" s="185"/>
       <c r="C16" s="185"/>
@@ -21836,7 +21842,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="185" t="s">
-        <v>3865</v>
+        <v>3869</v>
       </c>
       <c r="B17" s="185"/>
       <c r="C17" s="185"/>
@@ -21877,32 +21883,32 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16.5">
       <c r="A1" s="82" t="s">
-        <v>3866</v>
+        <v>3870</v>
       </c>
       <c r="B1" s="94" t="s">
-        <v>3867</v>
+        <v>3871</v>
       </c>
       <c r="C1" s="83" t="s">
-        <v>3868</v>
+        <v>3872</v>
       </c>
       <c r="D1" s="83" t="s">
-        <v>3869</v>
+        <v>3873</v>
       </c>
       <c r="E1" s="84" t="s">
-        <v>3870</v>
+        <v>3874</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="162">
       <c r="A2" s="85"/>
       <c r="B2" s="95"/>
       <c r="C2" s="86" t="s">
-        <v>3871</v>
+        <v>3875</v>
       </c>
       <c r="D2" s="86" t="s">
-        <v>3871</v>
+        <v>3875</v>
       </c>
       <c r="E2" s="87" t="s">
-        <v>3872</v>
+        <v>3876</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="48.75">
@@ -21913,13 +21919,13 @@
         <v>300008347</v>
       </c>
       <c r="C3" s="89" t="s">
-        <v>3873</v>
+        <v>3877</v>
       </c>
       <c r="D3" s="89" t="s">
-        <v>3874</v>
+        <v>3878</v>
       </c>
       <c r="E3" s="90" t="s">
-        <v>3875</v>
+        <v>3879</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="32.25">
@@ -21930,13 +21936,13 @@
         <v>300008389</v>
       </c>
       <c r="C4" s="88" t="s">
-        <v>3876</v>
+        <v>3880</v>
       </c>
       <c r="D4" s="88" t="s">
-        <v>3877</v>
+        <v>3881</v>
       </c>
       <c r="E4" s="90" t="s">
-        <v>3878</v>
+        <v>3882</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="32.25">
@@ -21947,13 +21953,13 @@
         <v>300008375</v>
       </c>
       <c r="C5" s="88" t="s">
-        <v>3879</v>
+        <v>3883</v>
       </c>
       <c r="D5" s="88" t="s">
-        <v>3880</v>
+        <v>3884</v>
       </c>
       <c r="E5" s="90" t="s">
-        <v>3881</v>
+        <v>3885</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="32.25">
@@ -21964,13 +21970,13 @@
         <v>300008372</v>
       </c>
       <c r="C6" s="88" t="s">
-        <v>3882</v>
+        <v>3886</v>
       </c>
       <c r="D6" s="88" t="s">
-        <v>3883</v>
+        <v>3887</v>
       </c>
       <c r="E6" s="90" t="s">
-        <v>3884</v>
+        <v>3888</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="32.25">
@@ -21981,13 +21987,13 @@
         <v>300120599</v>
       </c>
       <c r="C7" s="88" t="s">
-        <v>3885</v>
+        <v>3889</v>
       </c>
       <c r="D7" s="88" t="s">
-        <v>3886</v>
+        <v>3890</v>
       </c>
       <c r="E7" s="90" t="s">
-        <v>3887</v>
+        <v>3891</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16.5">
@@ -21998,13 +22004,13 @@
         <v>300387272</v>
       </c>
       <c r="C8" s="88" t="s">
-        <v>3888</v>
+        <v>3892</v>
       </c>
       <c r="D8" s="88" t="s">
-        <v>3889</v>
+        <v>3893</v>
       </c>
       <c r="E8" s="90" t="s">
-        <v>3890</v>
+        <v>3894</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="32.25">
@@ -22015,13 +22021,13 @@
         <v>300008537</v>
       </c>
       <c r="C9" s="88" t="s">
-        <v>3891</v>
+        <v>3895</v>
       </c>
       <c r="D9" s="88" t="s">
-        <v>3892</v>
+        <v>3896</v>
       </c>
       <c r="E9" s="90" t="s">
-        <v>3893</v>
+        <v>3897</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="16.5">
@@ -22032,13 +22038,13 @@
         <v>300387216</v>
       </c>
       <c r="C10" s="88" t="s">
-        <v>3894</v>
+        <v>3898</v>
       </c>
       <c r="D10" s="88" t="s">
-        <v>3895</v>
+        <v>3899</v>
       </c>
       <c r="E10" s="90" t="s">
-        <v>3896</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="16.5">
@@ -22049,13 +22055,13 @@
         <v>300008542</v>
       </c>
       <c r="C11" s="88" t="s">
-        <v>3897</v>
+        <v>3901</v>
       </c>
       <c r="D11" s="88" t="s">
-        <v>3898</v>
+        <v>3902</v>
       </c>
       <c r="E11" s="90" t="s">
-        <v>3896</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="16.5">
@@ -22066,13 +22072,13 @@
         <v>300167671</v>
       </c>
       <c r="C12" s="88" t="s">
-        <v>3899</v>
+        <v>3903</v>
       </c>
       <c r="D12" s="88" t="s">
-        <v>3900</v>
+        <v>3904</v>
       </c>
       <c r="E12" s="90" t="s">
-        <v>3901</v>
+        <v>3905</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="48.75">
@@ -22083,13 +22089,13 @@
         <v>300387318</v>
       </c>
       <c r="C13" s="88" t="s">
-        <v>3902</v>
+        <v>3906</v>
       </c>
       <c r="D13" s="88" t="s">
-        <v>3903</v>
+        <v>3907</v>
       </c>
       <c r="E13" s="90" t="s">
-        <v>3904</v>
+        <v>3908</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="16.5">
@@ -22100,13 +22106,13 @@
         <v>300387326</v>
       </c>
       <c r="C14" s="88" t="s">
-        <v>3905</v>
+        <v>3909</v>
       </c>
       <c r="D14" s="88" t="s">
-        <v>3906</v>
+        <v>3910</v>
       </c>
       <c r="E14" s="90" t="s">
-        <v>3907</v>
+        <v>3911</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="32.25">
@@ -22117,13 +22123,13 @@
         <v>300387203</v>
       </c>
       <c r="C15" s="88" t="s">
-        <v>3908</v>
+        <v>3912</v>
       </c>
       <c r="D15" s="88" t="s">
-        <v>3909</v>
+        <v>3913</v>
       </c>
       <c r="E15" s="90" t="s">
-        <v>3910</v>
+        <v>3914</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="16.5">
@@ -22134,26 +22140,26 @@
         <v>300387323</v>
       </c>
       <c r="C16" s="88" t="s">
-        <v>3911</v>
+        <v>3915</v>
       </c>
       <c r="D16" s="88" t="s">
-        <v>3912</v>
+        <v>3916</v>
       </c>
       <c r="E16" s="90" t="s">
-        <v>3913</v>
+        <v>3917</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="32.25">
       <c r="A17" s="85"/>
       <c r="B17" s="95"/>
       <c r="C17" s="89" t="s">
-        <v>3914</v>
+        <v>3918</v>
       </c>
       <c r="D17" s="89" t="s">
-        <v>3914</v>
+        <v>3918</v>
       </c>
       <c r="E17" s="90" t="s">
-        <v>3915</v>
+        <v>3919</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="48.75">
@@ -22164,13 +22170,13 @@
         <v>300182722</v>
       </c>
       <c r="C18" s="91" t="s">
-        <v>3916</v>
+        <v>3920</v>
       </c>
       <c r="D18" s="91" t="s">
-        <v>3917</v>
+        <v>3921</v>
       </c>
       <c r="E18" s="90" t="s">
-        <v>3918</v>
+        <v>3922</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="32.25">
@@ -22181,13 +22187,13 @@
         <v>300387178</v>
       </c>
       <c r="C19" s="88" t="s">
-        <v>3919</v>
+        <v>3923</v>
       </c>
       <c r="D19" s="88" t="s">
-        <v>3920</v>
+        <v>3924</v>
       </c>
       <c r="E19" s="90" t="s">
-        <v>3921</v>
+        <v>3925</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="16.5">
@@ -22198,26 +22204,26 @@
         <v>300387347</v>
       </c>
       <c r="C20" s="88" t="s">
-        <v>3922</v>
+        <v>3926</v>
       </c>
       <c r="D20" s="88" t="s">
-        <v>3923</v>
+        <v>3927</v>
       </c>
       <c r="E20" s="90" t="s">
-        <v>3924</v>
+        <v>3928</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="16.5">
       <c r="A21" s="85"/>
       <c r="B21" s="95"/>
       <c r="C21" s="89" t="s">
-        <v>3925</v>
+        <v>3929</v>
       </c>
       <c r="D21" s="89" t="s">
-        <v>3925</v>
+        <v>3929</v>
       </c>
       <c r="E21" s="90" t="s">
-        <v>3926</v>
+        <v>3930</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="32.25">
@@ -22228,13 +22234,13 @@
         <v>300387616</v>
       </c>
       <c r="C22" s="88" t="s">
-        <v>3927</v>
+        <v>3931</v>
       </c>
       <c r="D22" s="88" t="s">
-        <v>3928</v>
+        <v>3932</v>
       </c>
       <c r="E22" s="90" t="s">
-        <v>3929</v>
+        <v>3933</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="32.25">
@@ -22245,13 +22251,13 @@
         <v>300386114</v>
       </c>
       <c r="C23" s="88" t="s">
-        <v>3930</v>
+        <v>3934</v>
       </c>
       <c r="D23" s="88" t="s">
-        <v>3931</v>
+        <v>3935</v>
       </c>
       <c r="E23" s="90" t="s">
-        <v>3932</v>
+        <v>3936</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="32.25">
@@ -22260,13 +22266,13 @@
         <v>300261086</v>
       </c>
       <c r="C24" s="89" t="s">
-        <v>3933</v>
+        <v>3937</v>
       </c>
       <c r="D24" s="89" t="s">
-        <v>3934</v>
+        <v>3938</v>
       </c>
       <c r="E24" s="90" t="s">
-        <v>3935</v>
+        <v>3939</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="16.5">
@@ -22277,13 +22283,13 @@
         <v>300232420</v>
       </c>
       <c r="C25" s="91" t="s">
-        <v>3936</v>
+        <v>3940</v>
       </c>
       <c r="D25" s="91" t="s">
-        <v>3937</v>
+        <v>3941</v>
       </c>
       <c r="E25" s="90" t="s">
-        <v>3938</v>
+        <v>3942</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="32.25">
@@ -22294,13 +22300,13 @@
         <v>300128207</v>
       </c>
       <c r="C26" s="88" t="s">
-        <v>3939</v>
+        <v>3943</v>
       </c>
       <c r="D26" s="88" t="s">
-        <v>3940</v>
+        <v>3944</v>
       </c>
       <c r="E26" s="90" t="s">
-        <v>3941</v>
+        <v>3945</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="16.5">
@@ -22311,13 +22317,13 @@
         <v>300403959</v>
       </c>
       <c r="C27" s="88" t="s">
-        <v>3942</v>
+        <v>3946</v>
       </c>
       <c r="D27" s="88" t="s">
-        <v>3943</v>
+        <v>3947</v>
       </c>
       <c r="E27" s="90" t="s">
-        <v>3944</v>
+        <v>3948</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="16.5">
@@ -22328,13 +22334,13 @@
         <v>300387062</v>
       </c>
       <c r="C28" s="88" t="s">
-        <v>3942</v>
+        <v>3946</v>
       </c>
       <c r="D28" s="88" t="s">
-        <v>3945</v>
+        <v>3949</v>
       </c>
       <c r="E28" s="90" t="s">
-        <v>3946</v>
+        <v>3950</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="32.25">
@@ -22345,13 +22351,13 @@
         <v>300387506</v>
       </c>
       <c r="C29" s="88" t="s">
-        <v>3947</v>
+        <v>3951</v>
       </c>
       <c r="D29" s="88" t="s">
-        <v>3948</v>
+        <v>3952</v>
       </c>
       <c r="E29" s="90" t="s">
-        <v>3949</v>
+        <v>3953</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="32.25">
@@ -22362,13 +22368,13 @@
         <v>300128214</v>
       </c>
       <c r="C30" s="88" t="s">
-        <v>3950</v>
+        <v>3954</v>
       </c>
       <c r="D30" s="88" t="s">
-        <v>3951</v>
+        <v>3955</v>
       </c>
       <c r="E30" s="90" t="s">
-        <v>3952</v>
+        <v>3956</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="16.5">
@@ -22379,13 +22385,13 @@
         <v>300417385</v>
       </c>
       <c r="C31" s="88" t="s">
-        <v>3953</v>
+        <v>3957</v>
       </c>
       <c r="D31" s="88" t="s">
-        <v>3954</v>
+        <v>3958</v>
       </c>
       <c r="E31" s="90" t="s">
-        <v>3955</v>
+        <v>3959</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="32.25">
@@ -22396,13 +22402,13 @@
         <v>300235114</v>
       </c>
       <c r="C32" s="91" t="s">
-        <v>3956</v>
+        <v>3960</v>
       </c>
       <c r="D32" s="91" t="s">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E32" s="90" t="s">
-        <v>3958</v>
+        <v>3962</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="32.25">
@@ -22413,13 +22419,13 @@
         <v>300387137</v>
       </c>
       <c r="C33" s="88" t="s">
-        <v>3959</v>
+        <v>3963</v>
       </c>
       <c r="D33" s="88" t="s">
-        <v>3960</v>
+        <v>3964</v>
       </c>
       <c r="E33" s="90" t="s">
-        <v>3961</v>
+        <v>3965</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="16.5">
@@ -22430,13 +22436,13 @@
         <v>300235118</v>
       </c>
       <c r="C34" s="88" t="s">
-        <v>3962</v>
+        <v>3966</v>
       </c>
       <c r="D34" s="88" t="s">
-        <v>3963</v>
+        <v>3967</v>
       </c>
       <c r="E34" s="90" t="s">
-        <v>3964</v>
+        <v>3968</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="32.25">
@@ -22447,13 +22453,13 @@
         <v>300235115</v>
       </c>
       <c r="C35" s="88" t="s">
-        <v>3965</v>
+        <v>3969</v>
       </c>
       <c r="D35" s="88" t="s">
-        <v>3966</v>
+        <v>3970</v>
       </c>
       <c r="E35" s="90" t="s">
-        <v>3967</v>
+        <v>3971</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="16.5">
@@ -22464,13 +22470,13 @@
         <v>300412029</v>
       </c>
       <c r="C36" s="88" t="s">
-        <v>3968</v>
+        <v>3972</v>
       </c>
       <c r="D36" s="88" t="s">
-        <v>3969</v>
+        <v>3973</v>
       </c>
       <c r="E36" s="90" t="s">
-        <v>3970</v>
+        <v>3974</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="32.25">
@@ -22481,13 +22487,13 @@
         <v>300232418</v>
       </c>
       <c r="C37" s="91" t="s">
-        <v>3971</v>
+        <v>3975</v>
       </c>
       <c r="D37" s="91" t="s">
-        <v>3972</v>
+        <v>3976</v>
       </c>
       <c r="E37" s="90" t="s">
-        <v>3973</v>
+        <v>3977</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="16.5">
@@ -22498,13 +22504,13 @@
         <v>300236157</v>
       </c>
       <c r="C38" s="91" t="s">
-        <v>3974</v>
+        <v>3978</v>
       </c>
       <c r="D38" s="91" t="s">
-        <v>3975</v>
+        <v>3979</v>
       </c>
       <c r="E38" s="90" t="s">
-        <v>3976</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="32.25">
@@ -22515,13 +22521,13 @@
         <v>300000774</v>
       </c>
       <c r="C39" s="88" t="s">
-        <v>3977</v>
+        <v>3981</v>
       </c>
       <c r="D39" s="88" t="s">
-        <v>3978</v>
+        <v>3982</v>
       </c>
       <c r="E39" s="90" t="s">
-        <v>3979</v>
+        <v>3983</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="64.5">
@@ -22532,13 +22538,13 @@
         <v>300000771</v>
       </c>
       <c r="C40" s="88" t="s">
-        <v>3980</v>
+        <v>3984</v>
       </c>
       <c r="D40" s="88" t="s">
-        <v>3981</v>
+        <v>3985</v>
       </c>
       <c r="E40" s="90" t="s">
-        <v>3982</v>
+        <v>3986</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="32.25">
@@ -22549,13 +22555,13 @@
         <v>300000776</v>
       </c>
       <c r="C41" s="88" t="s">
-        <v>3983</v>
+        <v>3987</v>
       </c>
       <c r="D41" s="88" t="s">
-        <v>3984</v>
+        <v>3988</v>
       </c>
       <c r="E41" s="90" t="s">
-        <v>3985</v>
+        <v>3989</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="32.25">
@@ -22566,13 +22572,13 @@
         <v>300135982</v>
       </c>
       <c r="C42" s="88" t="s">
-        <v>3986</v>
+        <v>3990</v>
       </c>
       <c r="D42" s="88" t="s">
-        <v>3987</v>
+        <v>3991</v>
       </c>
       <c r="E42" s="90" t="s">
-        <v>3988</v>
+        <v>3992</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="64.5">
@@ -22583,13 +22589,13 @@
         <v>300387107</v>
       </c>
       <c r="C43" s="88" t="s">
-        <v>3989</v>
+        <v>3993</v>
       </c>
       <c r="D43" s="88" t="s">
-        <v>3990</v>
+        <v>3994</v>
       </c>
       <c r="E43" s="90" t="s">
-        <v>3991</v>
+        <v>3995</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="64.5">
@@ -22600,13 +22606,13 @@
         <v>300387130</v>
       </c>
       <c r="C44" s="88" t="s">
-        <v>3992</v>
+        <v>3996</v>
       </c>
       <c r="D44" s="88" t="s">
-        <v>3993</v>
+        <v>3997</v>
       </c>
       <c r="E44" s="90" t="s">
-        <v>3994</v>
+        <v>3998</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="16.5">
@@ -22617,13 +22623,13 @@
         <v>300236153</v>
       </c>
       <c r="C45" s="88" t="s">
-        <v>3995</v>
+        <v>3999</v>
       </c>
       <c r="D45" s="88" t="s">
-        <v>3996</v>
+        <v>4000</v>
       </c>
       <c r="E45" s="90" t="s">
-        <v>3997</v>
+        <v>4001</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="16.5">
@@ -22634,13 +22640,13 @@
         <v>300235087</v>
       </c>
       <c r="C46" s="88" t="s">
-        <v>3998</v>
+        <v>4002</v>
       </c>
       <c r="D46" s="88" t="s">
-        <v>3999</v>
+        <v>4003</v>
       </c>
       <c r="E46" s="90" t="s">
-        <v>4000</v>
+        <v>4004</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="16.5">
@@ -22651,13 +22657,13 @@
         <v>300264084</v>
       </c>
       <c r="C47" s="88" t="s">
-        <v>4001</v>
+        <v>4005</v>
       </c>
       <c r="D47" s="88" t="s">
-        <v>4002</v>
+        <v>4006</v>
       </c>
       <c r="E47" s="90" t="s">
-        <v>4003</v>
+        <v>4007</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="64.5">
@@ -22668,13 +22674,13 @@
         <v>300264389</v>
       </c>
       <c r="C48" s="88" t="s">
-        <v>4004</v>
+        <v>4008</v>
       </c>
       <c r="D48" s="88" t="s">
-        <v>4005</v>
+        <v>4009</v>
       </c>
       <c r="E48" s="90" t="s">
-        <v>4006</v>
+        <v>4010</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="16.5">
@@ -22685,13 +22691,13 @@
         <v>300374944</v>
       </c>
       <c r="C49" s="88" t="s">
-        <v>4007</v>
+        <v>4011</v>
       </c>
       <c r="D49" s="88" t="s">
-        <v>4008</v>
+        <v>4012</v>
       </c>
       <c r="E49" s="90" t="s">
-        <v>4009</v>
+        <v>4013</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="16.5">
@@ -22702,13 +22708,13 @@
         <v>300235088</v>
       </c>
       <c r="C50" s="88" t="s">
-        <v>4010</v>
+        <v>4014</v>
       </c>
       <c r="D50" s="88" t="s">
-        <v>4011</v>
+        <v>4015</v>
       </c>
       <c r="E50" s="90" t="s">
-        <v>4012</v>
+        <v>4016</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="16.5">
@@ -22719,13 +22725,13 @@
         <v>300387184</v>
       </c>
       <c r="C51" s="88" t="s">
-        <v>4013</v>
+        <v>4017</v>
       </c>
       <c r="D51" s="88" t="s">
-        <v>4014</v>
+        <v>4018</v>
       </c>
       <c r="E51" s="90" t="s">
-        <v>4015</v>
+        <v>4019</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="16.5">
@@ -22736,13 +22742,13 @@
         <v>300235095</v>
       </c>
       <c r="C52" s="88" t="s">
-        <v>4016</v>
+        <v>4020</v>
       </c>
       <c r="D52" s="88" t="s">
-        <v>4017</v>
+        <v>4021</v>
       </c>
       <c r="E52" s="90" t="s">
-        <v>4018</v>
+        <v>4022</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="16.5">
@@ -22753,13 +22759,13 @@
         <v>300235096</v>
       </c>
       <c r="C53" s="88" t="s">
-        <v>4019</v>
+        <v>4023</v>
       </c>
       <c r="D53" s="88" t="s">
-        <v>4020</v>
+        <v>4024</v>
       </c>
       <c r="E53" s="90" t="s">
-        <v>4021</v>
+        <v>4025</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="16.5">
@@ -22770,13 +22776,13 @@
         <v>300235101</v>
       </c>
       <c r="C54" s="88" t="s">
-        <v>4022</v>
+        <v>4026</v>
       </c>
       <c r="D54" s="88" t="s">
-        <v>4023</v>
+        <v>4027</v>
       </c>
       <c r="E54" s="90" t="s">
-        <v>4024</v>
+        <v>4028</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="16.5">
@@ -22787,13 +22793,13 @@
         <v>300235105</v>
       </c>
       <c r="C55" s="88" t="s">
-        <v>4025</v>
+        <v>4029</v>
       </c>
       <c r="D55" s="88" t="s">
-        <v>4026</v>
+        <v>4030</v>
       </c>
       <c r="E55" s="90" t="s">
-        <v>4027</v>
+        <v>4031</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="16.5">
@@ -22804,13 +22810,13 @@
         <v>300235106</v>
       </c>
       <c r="C56" s="88" t="s">
-        <v>4028</v>
+        <v>4032</v>
       </c>
       <c r="D56" s="88" t="s">
-        <v>4029</v>
+        <v>4033</v>
       </c>
       <c r="E56" s="90" t="s">
-        <v>4030</v>
+        <v>4034</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="16.5">
@@ -22821,13 +22827,13 @@
         <v>300235099</v>
       </c>
       <c r="C57" s="88" t="s">
-        <v>4031</v>
+        <v>4035</v>
       </c>
       <c r="D57" s="88" t="s">
-        <v>4032</v>
+        <v>4036</v>
       </c>
       <c r="E57" s="90" t="s">
-        <v>4033</v>
+        <v>4037</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="16.5">
@@ -22838,13 +22844,13 @@
         <v>300192630</v>
       </c>
       <c r="C58" s="89" t="s">
-        <v>4034</v>
+        <v>4038</v>
       </c>
       <c r="D58" s="89" t="s">
-        <v>4035</v>
+        <v>4039</v>
       </c>
       <c r="E58" s="90" t="s">
-        <v>4036</v>
+        <v>4040</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="32.25">
@@ -22855,13 +22861,13 @@
         <v>300387171</v>
       </c>
       <c r="C59" s="88" t="s">
-        <v>4037</v>
+        <v>4041</v>
       </c>
       <c r="D59" s="88" t="s">
-        <v>4038</v>
+        <v>4042</v>
       </c>
       <c r="E59" s="90" t="s">
-        <v>4039</v>
+        <v>4043</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="32.25">
@@ -22872,26 +22878,26 @@
         <v>300386176</v>
       </c>
       <c r="C60" s="88" t="s">
-        <v>4040</v>
+        <v>4044</v>
       </c>
       <c r="D60" s="88" t="s">
-        <v>4041</v>
+        <v>4045</v>
       </c>
       <c r="E60" s="90" t="s">
-        <v>4042</v>
+        <v>4046</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="243">
       <c r="A61" s="85"/>
       <c r="B61" s="95"/>
       <c r="C61" s="92" t="s">
-        <v>4043</v>
+        <v>4047</v>
       </c>
       <c r="D61" s="92" t="s">
-        <v>4043</v>
+        <v>4047</v>
       </c>
       <c r="E61" s="90" t="s">
-        <v>4044</v>
+        <v>4048</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="32.25">
@@ -22902,13 +22908,13 @@
         <v>300000202</v>
       </c>
       <c r="C62" s="92" t="s">
-        <v>4045</v>
+        <v>4049</v>
       </c>
       <c r="D62" s="92" t="s">
-        <v>4045</v>
+        <v>4049</v>
       </c>
       <c r="E62" s="90" t="s">
-        <v>4046</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="32.25">
@@ -22919,13 +22925,13 @@
         <v>300000809</v>
       </c>
       <c r="C63" s="89" t="s">
-        <v>4047</v>
+        <v>4051</v>
       </c>
       <c r="D63" s="89" t="s">
-        <v>4048</v>
+        <v>4052</v>
       </c>
       <c r="E63" s="90" t="s">
-        <v>4049</v>
+        <v>4053</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="64.5">
@@ -22936,13 +22942,13 @@
         <v>300000810</v>
       </c>
       <c r="C64" s="88" t="s">
-        <v>4050</v>
+        <v>4054</v>
       </c>
       <c r="D64" s="88" t="s">
-        <v>4051</v>
+        <v>4055</v>
       </c>
       <c r="E64" s="90" t="s">
-        <v>4052</v>
+        <v>4056</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="16.5">
@@ -22953,13 +22959,13 @@
         <v>300387006</v>
       </c>
       <c r="C65" s="88" t="s">
-        <v>4053</v>
+        <v>4057</v>
       </c>
       <c r="D65" s="88" t="s">
-        <v>4054</v>
+        <v>4058</v>
       </c>
       <c r="E65" s="90" t="s">
-        <v>4055</v>
+        <v>4059</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="16.5">
@@ -22970,13 +22976,13 @@
         <v>300387007</v>
       </c>
       <c r="C66" s="88" t="s">
-        <v>4056</v>
+        <v>4060</v>
       </c>
       <c r="D66" s="88" t="s">
-        <v>4057</v>
+        <v>4061</v>
       </c>
       <c r="E66" s="90" t="s">
-        <v>4058</v>
+        <v>4062</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="16.5">
@@ -22987,13 +22993,13 @@
         <v>300387000</v>
       </c>
       <c r="C67" s="88" t="s">
-        <v>4059</v>
+        <v>4063</v>
       </c>
       <c r="D67" s="88" t="s">
-        <v>4060</v>
+        <v>4064</v>
       </c>
       <c r="E67" s="90" t="s">
-        <v>4061</v>
+        <v>4065</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="16.5">
@@ -23004,13 +23010,13 @@
         <v>300000835</v>
       </c>
       <c r="C68" s="88" t="s">
-        <v>4062</v>
+        <v>4066</v>
       </c>
       <c r="D68" s="88" t="s">
-        <v>4063</v>
+        <v>4067</v>
       </c>
       <c r="E68" s="90" t="s">
-        <v>4064</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="32.25">
@@ -23021,13 +23027,13 @@
         <v>300386998</v>
       </c>
       <c r="C69" s="88" t="s">
-        <v>4065</v>
+        <v>4069</v>
       </c>
       <c r="D69" s="88" t="s">
-        <v>4066</v>
+        <v>4070</v>
       </c>
       <c r="E69" s="90" t="s">
-        <v>4067</v>
+        <v>4071</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="32.25">
@@ -23038,13 +23044,13 @@
         <v>300263063</v>
       </c>
       <c r="C70" s="88" t="s">
-        <v>4068</v>
+        <v>4072</v>
       </c>
       <c r="D70" s="88" t="s">
-        <v>4069</v>
+        <v>4073</v>
       </c>
       <c r="E70" s="90" t="s">
-        <v>4070</v>
+        <v>4074</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="16.5">
@@ -23055,13 +23061,13 @@
         <v>300387268</v>
       </c>
       <c r="C71" s="88" t="s">
-        <v>4071</v>
+        <v>4075</v>
       </c>
       <c r="D71" s="88" t="s">
-        <v>4072</v>
+        <v>4076</v>
       </c>
       <c r="E71" s="90" t="s">
-        <v>4073</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="16.5">
@@ -23072,13 +23078,13 @@
         <v>300387004</v>
       </c>
       <c r="C72" s="88" t="s">
-        <v>4074</v>
+        <v>4078</v>
       </c>
       <c r="D72" s="88" t="s">
-        <v>4075</v>
+        <v>4079</v>
       </c>
       <c r="E72" s="90" t="s">
-        <v>4076</v>
+        <v>4080</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="48.75">
@@ -23089,13 +23095,13 @@
         <v>300266755</v>
       </c>
       <c r="C73" s="88" t="s">
-        <v>4077</v>
+        <v>4081</v>
       </c>
       <c r="D73" s="88" t="s">
-        <v>4078</v>
+        <v>4082</v>
       </c>
       <c r="E73" s="90" t="s">
-        <v>4079</v>
+        <v>4083</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="48.75">
@@ -23106,13 +23112,13 @@
         <v>300000277</v>
       </c>
       <c r="C74" s="88" t="s">
-        <v>4080</v>
+        <v>4084</v>
       </c>
       <c r="D74" s="88" t="s">
-        <v>4081</v>
+        <v>4085</v>
       </c>
       <c r="E74" s="90" t="s">
-        <v>4082</v>
+        <v>4086</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="16.5">
@@ -23123,13 +23129,13 @@
         <v>300164060</v>
       </c>
       <c r="C75" s="88" t="s">
-        <v>4083</v>
+        <v>4087</v>
       </c>
       <c r="D75" s="88" t="s">
-        <v>4084</v>
+        <v>4088</v>
       </c>
       <c r="E75" s="90" t="s">
-        <v>4085</v>
+        <v>4089</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="32.25">
@@ -23140,13 +23146,13 @@
         <v>300000455</v>
       </c>
       <c r="C76" s="88" t="s">
-        <v>4086</v>
+        <v>4090</v>
       </c>
       <c r="D76" s="88" t="s">
-        <v>4087</v>
+        <v>4091</v>
       </c>
       <c r="E76" s="90" t="s">
-        <v>4088</v>
+        <v>4092</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="16.5">
@@ -23157,13 +23163,13 @@
         <v>300008439</v>
       </c>
       <c r="C77" s="88" t="s">
-        <v>4089</v>
+        <v>4093</v>
       </c>
       <c r="D77" s="88" t="s">
-        <v>4090</v>
+        <v>4094</v>
       </c>
       <c r="E77" s="90" t="s">
-        <v>4091</v>
+        <v>4095</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="32.25">
@@ -23174,13 +23180,13 @@
         <v>300410262</v>
       </c>
       <c r="C78" s="88" t="s">
-        <v>4092</v>
+        <v>4096</v>
       </c>
       <c r="D78" s="88" t="s">
-        <v>4093</v>
+        <v>4097</v>
       </c>
       <c r="E78" s="90" t="s">
-        <v>4094</v>
+        <v>4098</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="16.5">
@@ -23191,13 +23197,13 @@
         <v>300417317</v>
       </c>
       <c r="C79" s="88" t="s">
-        <v>4095</v>
+        <v>4099</v>
       </c>
       <c r="D79" s="88" t="s">
-        <v>4096</v>
+        <v>4100</v>
       </c>
       <c r="E79" s="90" t="s">
-        <v>4097</v>
+        <v>4101</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="16.5">
@@ -23208,13 +23214,13 @@
         <v>300263741</v>
       </c>
       <c r="C80" s="88" t="s">
-        <v>4098</v>
+        <v>4102</v>
       </c>
       <c r="D80" s="88" t="s">
-        <v>4099</v>
+        <v>4103</v>
       </c>
       <c r="E80" s="90" t="s">
-        <v>4100</v>
+        <v>4104</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="16.5">
@@ -23225,13 +23231,13 @@
         <v>300000678</v>
       </c>
       <c r="C81" s="88" t="s">
-        <v>4101</v>
+        <v>4105</v>
       </c>
       <c r="D81" s="88" t="s">
-        <v>4102</v>
+        <v>4106</v>
       </c>
       <c r="E81" s="90" t="s">
-        <v>4103</v>
+        <v>4107</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="48.75">
@@ -23242,13 +23248,13 @@
         <v>300000681</v>
       </c>
       <c r="C82" s="88" t="s">
-        <v>4104</v>
+        <v>4108</v>
       </c>
       <c r="D82" s="88" t="s">
-        <v>4105</v>
+        <v>4109</v>
       </c>
       <c r="E82" s="90" t="s">
-        <v>4106</v>
+        <v>4110</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="16.5">
@@ -23259,13 +23265,13 @@
         <v>300125766</v>
       </c>
       <c r="C83" s="88" t="s">
-        <v>4107</v>
+        <v>4111</v>
       </c>
       <c r="D83" s="88" t="s">
-        <v>4108</v>
+        <v>4112</v>
       </c>
       <c r="E83" s="90" t="s">
-        <v>4109</v>
+        <v>4113</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="32.25">
@@ -23276,13 +23282,13 @@
         <v>300000401</v>
       </c>
       <c r="C84" s="88" t="s">
-        <v>4110</v>
+        <v>4114</v>
       </c>
       <c r="D84" s="88" t="s">
-        <v>4111</v>
+        <v>4115</v>
       </c>
       <c r="E84" s="90" t="s">
-        <v>4112</v>
+        <v>4116</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="32.25">
@@ -23293,13 +23299,13 @@
         <v>300000390</v>
       </c>
       <c r="C85" s="88" t="s">
-        <v>4113</v>
+        <v>4117</v>
       </c>
       <c r="D85" s="88" t="s">
-        <v>4114</v>
+        <v>4118</v>
       </c>
       <c r="E85" s="90" t="s">
-        <v>4115</v>
+        <v>4119</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="16.5">
@@ -23310,13 +23316,13 @@
         <v>300132656</v>
       </c>
       <c r="C86" s="88" t="s">
-        <v>4116</v>
+        <v>4120</v>
       </c>
       <c r="D86" s="88" t="s">
-        <v>4117</v>
+        <v>4121</v>
       </c>
       <c r="E86" s="90" t="s">
-        <v>4118</v>
+        <v>4122</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="32.25">
@@ -23327,13 +23333,13 @@
         <v>300257640</v>
       </c>
       <c r="C87" s="88" t="s">
-        <v>4119</v>
+        <v>4123</v>
       </c>
       <c r="D87" s="88" t="s">
-        <v>4120</v>
+        <v>4124</v>
       </c>
       <c r="E87" s="90" t="s">
-        <v>4121</v>
+        <v>4125</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="16.5">
@@ -23344,13 +23350,13 @@
         <v>300000705</v>
       </c>
       <c r="C88" s="89" t="s">
-        <v>4122</v>
+        <v>4126</v>
       </c>
       <c r="D88" s="89" t="s">
-        <v>4123</v>
+        <v>4127</v>
       </c>
       <c r="E88" s="90" t="s">
-        <v>4124</v>
+        <v>4128</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="16.5">
@@ -23361,13 +23367,13 @@
         <v>300000742</v>
       </c>
       <c r="C89" s="88" t="s">
-        <v>4125</v>
+        <v>4129</v>
       </c>
       <c r="D89" s="88" t="s">
-        <v>4126</v>
+        <v>4130</v>
       </c>
       <c r="E89" s="90" t="s">
-        <v>4127</v>
+        <v>4131</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="32.25">
@@ -23378,13 +23384,13 @@
         <v>300000745</v>
       </c>
       <c r="C90" s="88" t="s">
-        <v>4128</v>
+        <v>4132</v>
       </c>
       <c r="D90" s="88" t="s">
-        <v>4129</v>
+        <v>4133</v>
       </c>
       <c r="E90" s="90" t="s">
-        <v>4130</v>
+        <v>4134</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="16.5">
@@ -23395,13 +23401,13 @@
         <v>300000750</v>
       </c>
       <c r="C91" s="88" t="s">
-        <v>4131</v>
+        <v>4135</v>
       </c>
       <c r="D91" s="88" t="s">
-        <v>4132</v>
+        <v>4136</v>
       </c>
       <c r="E91" s="90" t="s">
-        <v>4133</v>
+        <v>4137</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="16.5">
@@ -23412,13 +23418,13 @@
         <v>300387143</v>
       </c>
       <c r="C92" s="88" t="s">
-        <v>4134</v>
+        <v>4138</v>
       </c>
       <c r="D92" s="88" t="s">
-        <v>4135</v>
+        <v>4139</v>
       </c>
       <c r="E92" s="90" t="s">
-        <v>4136</v>
+        <v>4140</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="16.5">
@@ -23427,13 +23433,13 @@
         <v>300004790</v>
       </c>
       <c r="C93" s="89" t="s">
-        <v>4137</v>
+        <v>4141</v>
       </c>
       <c r="D93" s="89" t="s">
-        <v>4138</v>
+        <v>4142</v>
       </c>
       <c r="E93" s="90" t="s">
-        <v>4139</v>
+        <v>4143</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="16.5">
@@ -23444,13 +23450,13 @@
         <v>300007836</v>
       </c>
       <c r="C94" s="88" t="s">
-        <v>4140</v>
+        <v>4144</v>
       </c>
       <c r="D94" s="88" t="s">
-        <v>4141</v>
+        <v>4145</v>
       </c>
       <c r="E94" s="90" t="s">
-        <v>4142</v>
+        <v>4146</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="16.5">
@@ -23461,13 +23467,13 @@
         <v>300008057</v>
       </c>
       <c r="C95" s="88" t="s">
-        <v>4143</v>
+        <v>4147</v>
       </c>
       <c r="D95" s="88" t="s">
-        <v>4144</v>
+        <v>4148</v>
       </c>
       <c r="E95" s="90" t="s">
-        <v>4145</v>
+        <v>4149</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="48.75">
@@ -23478,13 +23484,13 @@
         <v>300008063</v>
       </c>
       <c r="C96" s="88" t="s">
-        <v>4146</v>
+        <v>4150</v>
       </c>
       <c r="D96" s="88" t="s">
-        <v>4147</v>
+        <v>4151</v>
       </c>
       <c r="E96" s="90" t="s">
-        <v>4148</v>
+        <v>4152</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="16.5">
@@ -23495,13 +23501,13 @@
         <v>300006073</v>
       </c>
       <c r="C97" s="88" t="s">
-        <v>4149</v>
+        <v>4153</v>
       </c>
       <c r="D97" s="88" t="s">
-        <v>4150</v>
+        <v>4154</v>
       </c>
       <c r="E97" s="90" t="s">
-        <v>4151</v>
+        <v>4155</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="16.5">
@@ -23512,13 +23518,13 @@
         <v>300006075</v>
       </c>
       <c r="C98" s="88" t="s">
-        <v>4152</v>
+        <v>4156</v>
       </c>
       <c r="D98" s="88" t="s">
-        <v>4153</v>
+        <v>4157</v>
       </c>
       <c r="E98" s="90" t="s">
-        <v>4154</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="16.5">
@@ -23529,13 +23535,13 @@
         <v>300006084</v>
       </c>
       <c r="C99" s="88" t="s">
-        <v>4155</v>
+        <v>4159</v>
       </c>
       <c r="D99" s="88" t="s">
-        <v>4156</v>
+        <v>4160</v>
       </c>
       <c r="E99" s="90" t="s">
-        <v>4157</v>
+        <v>4161</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="64.5">
@@ -23546,13 +23552,13 @@
         <v>300006084</v>
       </c>
       <c r="C100" s="88" t="s">
-        <v>4158</v>
+        <v>4162</v>
       </c>
       <c r="D100" s="88" t="s">
-        <v>4159</v>
+        <v>4163</v>
       </c>
       <c r="E100" s="90" t="s">
-        <v>4160</v>
+        <v>4164</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="16.5">
@@ -23563,13 +23569,13 @@
         <v>300006191</v>
       </c>
       <c r="C101" s="88" t="s">
-        <v>4161</v>
+        <v>4165</v>
       </c>
       <c r="D101" s="88" t="s">
-        <v>4162</v>
+        <v>4166</v>
       </c>
       <c r="E101" s="90" t="s">
-        <v>4163</v>
+        <v>4167</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="32.25">
@@ -23580,13 +23586,13 @@
         <v>300006207</v>
       </c>
       <c r="C102" s="88" t="s">
-        <v>4164</v>
+        <v>4168</v>
       </c>
       <c r="D102" s="88" t="s">
-        <v>4165</v>
+        <v>4169</v>
       </c>
       <c r="E102" s="90" t="s">
-        <v>4166</v>
+        <v>4170</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="16.5">
@@ -23597,13 +23603,13 @@
         <v>300263489</v>
       </c>
       <c r="C103" s="88" t="s">
-        <v>4167</v>
+        <v>4171</v>
       </c>
       <c r="D103" s="88" t="s">
-        <v>4168</v>
+        <v>4172</v>
       </c>
       <c r="E103" s="90" t="s">
-        <v>4169</v>
+        <v>4173</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="32.25">
@@ -23614,13 +23620,13 @@
         <v>300005903</v>
       </c>
       <c r="C104" s="88" t="s">
-        <v>4170</v>
+        <v>4174</v>
       </c>
       <c r="D104" s="88" t="s">
-        <v>4171</v>
+        <v>4175</v>
       </c>
       <c r="E104" s="90" t="s">
-        <v>4172</v>
+        <v>4176</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="16.5">
@@ -23631,13 +23637,13 @@
         <v>300120364</v>
       </c>
       <c r="C105" s="88" t="s">
-        <v>4173</v>
+        <v>4177</v>
       </c>
       <c r="D105" s="88" t="s">
-        <v>4174</v>
+        <v>4178</v>
       </c>
       <c r="E105" s="90" t="s">
-        <v>4175</v>
+        <v>4179</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="32.25">
@@ -23648,13 +23654,13 @@
         <v>300007486</v>
       </c>
       <c r="C106" s="88" t="s">
-        <v>4176</v>
+        <v>4180</v>
       </c>
       <c r="D106" s="88" t="s">
-        <v>4177</v>
+        <v>4181</v>
       </c>
       <c r="E106" s="90" t="s">
-        <v>4178</v>
+        <v>4182</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="32.25">
@@ -23665,13 +23671,13 @@
         <v>300007501</v>
       </c>
       <c r="C107" s="88" t="s">
-        <v>4179</v>
+        <v>4183</v>
       </c>
       <c r="D107" s="88" t="s">
-        <v>4180</v>
+        <v>4184</v>
       </c>
       <c r="E107" s="90" t="s">
-        <v>4181</v>
+        <v>4185</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="16.5">
@@ -23682,13 +23688,13 @@
         <v>300007544</v>
       </c>
       <c r="C108" s="88" t="s">
-        <v>4182</v>
+        <v>4186</v>
       </c>
       <c r="D108" s="88" t="s">
-        <v>4183</v>
+        <v>4187</v>
       </c>
       <c r="E108" s="90" t="s">
-        <v>4184</v>
+        <v>4188</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="32.25">
@@ -23699,13 +23705,13 @@
         <v>300007595</v>
       </c>
       <c r="C109" s="88" t="s">
-        <v>4185</v>
+        <v>4189</v>
       </c>
       <c r="D109" s="88" t="s">
-        <v>4186</v>
+        <v>4190</v>
       </c>
       <c r="E109" s="90" t="s">
-        <v>4187</v>
+        <v>4191</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="32.25">
@@ -23716,13 +23722,13 @@
         <v>300004829</v>
       </c>
       <c r="C110" s="88" t="s">
-        <v>4188</v>
+        <v>4192</v>
       </c>
       <c r="D110" s="88" t="s">
-        <v>4189</v>
+        <v>4193</v>
       </c>
       <c r="E110" s="90" t="s">
-        <v>4190</v>
+        <v>4194</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="16.5">
@@ -23733,13 +23739,13 @@
         <v>300007590</v>
       </c>
       <c r="C111" s="88" t="s">
-        <v>4191</v>
+        <v>4195</v>
       </c>
       <c r="D111" s="88" t="s">
-        <v>4192</v>
+        <v>4196</v>
       </c>
       <c r="E111" s="90" t="s">
-        <v>4193</v>
+        <v>4197</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="32.25">
@@ -23750,13 +23756,13 @@
         <v>300005734</v>
       </c>
       <c r="C112" s="88" t="s">
-        <v>4194</v>
+        <v>4198</v>
       </c>
       <c r="D112" s="88" t="s">
-        <v>4195</v>
+        <v>4199</v>
       </c>
       <c r="E112" s="90" t="s">
-        <v>4196</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="16.5">
@@ -23767,13 +23773,13 @@
         <v>300387025</v>
       </c>
       <c r="C113" s="88" t="s">
-        <v>4197</v>
+        <v>4201</v>
       </c>
       <c r="D113" s="88" t="s">
-        <v>4198</v>
+        <v>4202</v>
       </c>
       <c r="E113" s="90" t="s">
-        <v>4199</v>
+        <v>4203</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="16.5">
@@ -23784,13 +23790,13 @@
         <v>300006888</v>
       </c>
       <c r="C114" s="88" t="s">
-        <v>4200</v>
+        <v>4204</v>
       </c>
       <c r="D114" s="88" t="s">
-        <v>4201</v>
+        <v>4205</v>
       </c>
       <c r="E114" s="90" t="s">
-        <v>4202</v>
+        <v>4206</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="16.5">
@@ -23801,13 +23807,13 @@
         <v>300006891</v>
       </c>
       <c r="C115" s="88" t="s">
-        <v>4203</v>
+        <v>4207</v>
       </c>
       <c r="D115" s="88" t="s">
-        <v>4204</v>
+        <v>4208</v>
       </c>
       <c r="E115" s="90" t="s">
-        <v>4205</v>
+        <v>4209</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="16.5">
@@ -23818,13 +23824,13 @@
         <v>300005072</v>
       </c>
       <c r="C116" s="88" t="s">
-        <v>4206</v>
+        <v>4210</v>
       </c>
       <c r="D116" s="88" t="s">
-        <v>4207</v>
+        <v>4211</v>
       </c>
       <c r="E116" s="90" t="s">
-        <v>4208</v>
+        <v>4212</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="32.25">
@@ -23835,13 +23841,13 @@
         <v>300006617</v>
       </c>
       <c r="C117" s="88" t="s">
-        <v>4209</v>
+        <v>4213</v>
       </c>
       <c r="D117" s="88" t="s">
-        <v>4210</v>
+        <v>4214</v>
       </c>
       <c r="E117" s="90" t="s">
-        <v>4211</v>
+        <v>4215</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="16.5">
@@ -23850,13 +23856,13 @@
         <v>300155846</v>
       </c>
       <c r="C118" s="89" t="s">
-        <v>4212</v>
+        <v>4216</v>
       </c>
       <c r="D118" s="89" t="s">
-        <v>4213</v>
+        <v>4217</v>
       </c>
       <c r="E118" s="90" t="s">
-        <v>4214</v>
+        <v>4218</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="32.25">
@@ -23867,13 +23873,13 @@
         <v>300008591</v>
       </c>
       <c r="C119" s="88" t="s">
-        <v>4215</v>
+        <v>4219</v>
       </c>
       <c r="D119" s="88" t="s">
-        <v>4216</v>
+        <v>4220</v>
       </c>
       <c r="E119" s="90" t="s">
-        <v>4217</v>
+        <v>4221</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="48.75">
@@ -23882,13 +23888,13 @@
         <v>300008072</v>
       </c>
       <c r="C120" s="92" t="s">
-        <v>4218</v>
+        <v>4222</v>
       </c>
       <c r="D120" s="92" t="s">
-        <v>4219</v>
+        <v>4223</v>
       </c>
       <c r="E120" s="90" t="s">
-        <v>4220</v>
+        <v>4224</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="16.5">
@@ -23899,13 +23905,13 @@
         <v>300008304</v>
       </c>
       <c r="C121" s="88" t="s">
-        <v>4221</v>
+        <v>4225</v>
       </c>
       <c r="D121" s="88" t="s">
-        <v>4222</v>
+        <v>4226</v>
       </c>
       <c r="E121" s="90" t="s">
-        <v>4223</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="16.5">
@@ -23916,13 +23922,13 @@
         <v>300008187</v>
       </c>
       <c r="C122" s="88" t="s">
-        <v>4224</v>
+        <v>4228</v>
       </c>
       <c r="D122" s="88" t="s">
-        <v>4225</v>
+        <v>4229</v>
       </c>
       <c r="E122" s="90" t="s">
-        <v>4226</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="16.5">
@@ -23933,13 +23939,13 @@
         <v>300122438</v>
       </c>
       <c r="C123" s="88" t="s">
-        <v>4227</v>
+        <v>4231</v>
       </c>
       <c r="D123" s="88" t="s">
-        <v>4228</v>
+        <v>4232</v>
       </c>
       <c r="E123" s="90" t="s">
-        <v>4229</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="32.25">
@@ -23950,13 +23956,13 @@
         <v>300008217</v>
       </c>
       <c r="C124" s="88" t="s">
-        <v>4230</v>
+        <v>4234</v>
       </c>
       <c r="D124" s="88" t="s">
-        <v>4231</v>
+        <v>4235</v>
       </c>
       <c r="E124" s="90" t="s">
-        <v>4232</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="16.5">
@@ -23967,13 +23973,13 @@
         <v>300265365</v>
       </c>
       <c r="C125" s="88" t="s">
-        <v>4233</v>
+        <v>4237</v>
       </c>
       <c r="D125" s="88" t="s">
-        <v>4234</v>
+        <v>4238</v>
       </c>
       <c r="E125" s="90" t="s">
-        <v>4235</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="32.25">
@@ -23984,13 +23990,13 @@
         <v>300386595</v>
       </c>
       <c r="C126" s="88" t="s">
-        <v>4236</v>
+        <v>4240</v>
       </c>
       <c r="D126" s="88" t="s">
-        <v>4237</v>
+        <v>4241</v>
       </c>
       <c r="E126" s="90" t="s">
-        <v>4238</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="16.5">
@@ -24001,13 +24007,13 @@
         <v>300265367</v>
       </c>
       <c r="C127" s="88" t="s">
-        <v>4239</v>
+        <v>4243</v>
       </c>
       <c r="D127" s="88" t="s">
-        <v>4240</v>
+        <v>4244</v>
       </c>
       <c r="E127" s="90" t="s">
-        <v>4241</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="16.5">
@@ -24018,13 +24024,13 @@
         <v>300265366</v>
       </c>
       <c r="C128" s="88" t="s">
-        <v>4242</v>
+        <v>4246</v>
       </c>
       <c r="D128" s="88" t="s">
-        <v>4243</v>
+        <v>4247</v>
       </c>
       <c r="E128" s="90" t="s">
-        <v>4244</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="32.25">
@@ -24035,13 +24041,13 @@
         <v>300008312</v>
       </c>
       <c r="C129" s="88" t="s">
-        <v>4245</v>
+        <v>4249</v>
       </c>
       <c r="D129" s="88" t="s">
-        <v>4246</v>
+        <v>4250</v>
       </c>
       <c r="E129" s="90" t="s">
-        <v>4247</v>
+        <v>4251</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="16.5">
@@ -24052,13 +24058,13 @@
         <v>300008321</v>
       </c>
       <c r="C130" s="88" t="s">
-        <v>4248</v>
+        <v>4252</v>
       </c>
       <c r="D130" s="88" t="s">
-        <v>4249</v>
+        <v>4253</v>
       </c>
       <c r="E130" s="90" t="s">
-        <v>4250</v>
+        <v>4254</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="32.25">
@@ -24069,13 +24075,13 @@
         <v>300132294</v>
       </c>
       <c r="C131" s="86" t="s">
-        <v>4251</v>
+        <v>4255</v>
       </c>
       <c r="D131" s="86" t="s">
-        <v>4252</v>
+        <v>4256</v>
       </c>
       <c r="E131" s="90" t="s">
-        <v>4253</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="48.75">
@@ -24086,13 +24092,13 @@
         <v>300266060</v>
       </c>
       <c r="C132" s="89" t="s">
-        <v>4254</v>
+        <v>4258</v>
       </c>
       <c r="D132" s="89" t="s">
-        <v>4255</v>
+        <v>4259</v>
       </c>
       <c r="E132" s="90" t="s">
-        <v>4256</v>
+        <v>4260</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="16.5">
@@ -24103,13 +24109,13 @@
         <v>300386845</v>
       </c>
       <c r="C133" s="88" t="s">
-        <v>4257</v>
+        <v>4261</v>
       </c>
       <c r="D133" s="88" t="s">
-        <v>4258</v>
+        <v>4262</v>
       </c>
       <c r="E133" s="90" t="s">
-        <v>4259</v>
+        <v>4263</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="16.5">
@@ -24120,13 +24126,13 @@
         <v>300008850</v>
       </c>
       <c r="C134" s="88" t="s">
-        <v>4260</v>
+        <v>4264</v>
       </c>
       <c r="D134" s="88" t="s">
-        <v>4261</v>
+        <v>4265</v>
       </c>
       <c r="E134" s="90" t="s">
-        <v>4262</v>
+        <v>4266</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="16.5">
@@ -24137,13 +24143,13 @@
         <v>300386846</v>
       </c>
       <c r="C135" s="88" t="s">
-        <v>4263</v>
+        <v>4267</v>
       </c>
       <c r="D135" s="88" t="s">
-        <v>4264</v>
+        <v>4268</v>
       </c>
       <c r="E135" s="90" t="s">
-        <v>4265</v>
+        <v>4269</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="16.5">
@@ -24154,13 +24160,13 @@
         <v>300008804</v>
       </c>
       <c r="C136" s="88" t="s">
-        <v>4266</v>
+        <v>4270</v>
       </c>
       <c r="D136" s="88" t="s">
-        <v>4267</v>
+        <v>4271</v>
       </c>
       <c r="E136" s="90" t="s">
-        <v>4268</v>
+        <v>4272</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="32.25">
@@ -24171,13 +24177,13 @@
         <v>300128176</v>
       </c>
       <c r="C137" s="88" t="s">
-        <v>4269</v>
+        <v>4273</v>
       </c>
       <c r="D137" s="88" t="s">
-        <v>4270</v>
+        <v>4274</v>
       </c>
       <c r="E137" s="90" t="s">
-        <v>4271</v>
+        <v>4275</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="32.25">
@@ -24188,13 +24194,13 @@
         <v>300008760</v>
       </c>
       <c r="C138" s="88" t="s">
-        <v>4272</v>
+        <v>4276</v>
       </c>
       <c r="D138" s="88" t="s">
-        <v>4273</v>
+        <v>4277</v>
       </c>
       <c r="E138" s="90" t="s">
-        <v>4274</v>
+        <v>4278</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="16.5">
@@ -24205,13 +24211,13 @@
         <v>300386860</v>
       </c>
       <c r="C139" s="88" t="s">
-        <v>4275</v>
+        <v>4279</v>
       </c>
       <c r="D139" s="88" t="s">
-        <v>4276</v>
+        <v>4280</v>
       </c>
       <c r="E139" s="90" t="s">
-        <v>4277</v>
+        <v>4281</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="16.5">
@@ -24222,13 +24228,13 @@
         <v>300008916</v>
       </c>
       <c r="C140" s="88" t="s">
-        <v>4278</v>
+        <v>4282</v>
       </c>
       <c r="D140" s="88" t="s">
-        <v>4279</v>
+        <v>4283</v>
       </c>
       <c r="E140" s="90" t="s">
-        <v>4280</v>
+        <v>4284</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="32.25">
@@ -24239,13 +24245,13 @@
         <v>300387498</v>
       </c>
       <c r="C141" s="88" t="s">
-        <v>4281</v>
+        <v>4285</v>
       </c>
       <c r="D141" s="88" t="s">
-        <v>4282</v>
+        <v>4286</v>
       </c>
       <c r="E141" s="90" t="s">
-        <v>4283</v>
+        <v>4287</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="32.25">
@@ -24256,13 +24262,13 @@
         <v>300387499</v>
       </c>
       <c r="C142" s="88" t="s">
-        <v>4284</v>
+        <v>4288</v>
       </c>
       <c r="D142" s="88" t="s">
-        <v>4285</v>
+        <v>4289</v>
       </c>
       <c r="E142" s="90" t="s">
-        <v>4286</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="16.5">
@@ -24273,13 +24279,13 @@
         <v>300008777</v>
       </c>
       <c r="C143" s="88" t="s">
-        <v>4287</v>
+        <v>4291</v>
       </c>
       <c r="D143" s="88" t="s">
-        <v>4288</v>
+        <v>4292</v>
       </c>
       <c r="E143" s="90" t="s">
-        <v>4289</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="16.5">
@@ -24290,13 +24296,13 @@
         <v>300008791</v>
       </c>
       <c r="C144" s="88" t="s">
-        <v>4290</v>
+        <v>4294</v>
       </c>
       <c r="D144" s="88" t="s">
-        <v>4291</v>
+        <v>4295</v>
       </c>
       <c r="E144" s="90" t="s">
-        <v>4292</v>
+        <v>4296</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="16.5">
@@ -24307,13 +24313,13 @@
         <v>300386853</v>
       </c>
       <c r="C145" s="88" t="s">
-        <v>4293</v>
+        <v>4297</v>
       </c>
       <c r="D145" s="88" t="s">
-        <v>4294</v>
+        <v>4298</v>
       </c>
       <c r="E145" s="90" t="s">
-        <v>4295</v>
+        <v>4299</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="16.5">
@@ -24324,13 +24330,13 @@
         <v>300386831</v>
       </c>
       <c r="C146" s="88" t="s">
-        <v>4296</v>
+        <v>4300</v>
       </c>
       <c r="D146" s="88" t="s">
-        <v>4297</v>
+        <v>4301</v>
       </c>
       <c r="E146" s="90" t="s">
-        <v>4298</v>
+        <v>4302</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="32.25">
@@ -24341,13 +24347,13 @@
         <v>300008795</v>
       </c>
       <c r="C147" s="88" t="s">
-        <v>4299</v>
+        <v>4303</v>
       </c>
       <c r="D147" s="88" t="s">
-        <v>4300</v>
+        <v>4304</v>
       </c>
       <c r="E147" s="90" t="s">
-        <v>4301</v>
+        <v>4305</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="16.5">
@@ -24358,13 +24364,13 @@
         <v>300008686</v>
       </c>
       <c r="C148" s="88" t="s">
-        <v>4302</v>
+        <v>4306</v>
       </c>
       <c r="D148" s="88" t="s">
-        <v>4303</v>
+        <v>4307</v>
       </c>
       <c r="E148" s="90" t="s">
-        <v>4304</v>
+        <v>4308</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="16.5">
@@ -24375,13 +24381,13 @@
         <v>300259572</v>
       </c>
       <c r="C149" s="88" t="s">
-        <v>4305</v>
+        <v>4309</v>
       </c>
       <c r="D149" s="88" t="s">
-        <v>4306</v>
+        <v>4310</v>
       </c>
       <c r="E149" s="93" t="s">
-        <v>4307</v>
+        <v>4311</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="16.5">
@@ -24392,13 +24398,13 @@
         <v>300008805</v>
       </c>
       <c r="C150" s="88" t="s">
-        <v>4308</v>
+        <v>4312</v>
       </c>
       <c r="D150" s="88" t="s">
-        <v>4309</v>
+        <v>4313</v>
       </c>
       <c r="E150" s="90" t="s">
-        <v>4310</v>
+        <v>4314</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="16.5">
@@ -24409,13 +24415,13 @@
         <v>300132339</v>
       </c>
       <c r="C151" s="85" t="s">
-        <v>4311</v>
+        <v>4315</v>
       </c>
       <c r="D151" s="85" t="s">
-        <v>4312</v>
+        <v>4316</v>
       </c>
       <c r="E151" s="90" t="s">
-        <v>4313</v>
+        <v>4317</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="16.5">
@@ -24426,13 +24432,13 @@
         <v>300008761</v>
       </c>
       <c r="C152" s="88" t="s">
-        <v>4314</v>
+        <v>4318</v>
       </c>
       <c r="D152" s="88" t="s">
-        <v>4315</v>
+        <v>4319</v>
       </c>
       <c r="E152" s="90" t="s">
-        <v>4316</v>
+        <v>4320</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="16.5">
@@ -24443,13 +24449,13 @@
         <v>300129031</v>
       </c>
       <c r="C153" s="88" t="s">
-        <v>4317</v>
+        <v>4321</v>
       </c>
       <c r="D153" s="88" t="s">
-        <v>4318</v>
+        <v>4322</v>
       </c>
       <c r="E153" s="90" t="s">
-        <v>4319</v>
+        <v>4323</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="32.25">
@@ -24460,13 +24466,13 @@
         <v>300008746</v>
       </c>
       <c r="C154" s="88" t="s">
-        <v>4320</v>
+        <v>4324</v>
       </c>
       <c r="D154" s="88" t="s">
-        <v>4321</v>
+        <v>4325</v>
       </c>
       <c r="E154" s="90" t="s">
-        <v>4322</v>
+        <v>4326</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="16.5">
@@ -24477,13 +24483,13 @@
         <v>300379998</v>
       </c>
       <c r="C155" s="88" t="s">
-        <v>4323</v>
+        <v>4327</v>
       </c>
       <c r="D155" s="88" t="s">
-        <v>4324</v>
+        <v>4328</v>
       </c>
       <c r="E155" s="90" t="s">
-        <v>4325</v>
+        <v>4329</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="16.5">
@@ -24494,13 +24500,13 @@
         <v>300386857</v>
       </c>
       <c r="C156" s="88" t="s">
-        <v>4326</v>
+        <v>4330</v>
       </c>
       <c r="D156" s="88" t="s">
-        <v>4326</v>
+        <v>4330</v>
       </c>
       <c r="E156" s="90" t="s">
-        <v>4327</v>
+        <v>4331</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="162">
@@ -24511,13 +24517,13 @@
         <v>300266059</v>
       </c>
       <c r="C157" s="89" t="s">
-        <v>4328</v>
+        <v>4332</v>
       </c>
       <c r="D157" s="89" t="s">
-        <v>4329</v>
+        <v>4333</v>
       </c>
       <c r="E157" s="90" t="s">
-        <v>3872</v>
+        <v>3876</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="16.5">
@@ -24528,13 +24534,13 @@
         <v>300008678</v>
       </c>
       <c r="C158" s="88" t="s">
-        <v>4330</v>
+        <v>4334</v>
       </c>
       <c r="D158" s="88" t="s">
-        <v>4331</v>
+        <v>4335</v>
       </c>
       <c r="E158" s="90" t="s">
-        <v>4332</v>
+        <v>4336</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="16.5">
@@ -24545,13 +24551,13 @@
         <v>300132312</v>
       </c>
       <c r="C159" s="88" t="s">
-        <v>4333</v>
+        <v>4337</v>
       </c>
       <c r="D159" s="88" t="s">
-        <v>4333</v>
+        <v>4337</v>
       </c>
       <c r="E159" s="90" t="s">
-        <v>4334</v>
+        <v>4338</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="16.5">
@@ -24562,13 +24568,13 @@
         <v>300008707</v>
       </c>
       <c r="C160" s="88" t="s">
-        <v>4335</v>
+        <v>4339</v>
       </c>
       <c r="D160" s="88" t="s">
-        <v>4336</v>
+        <v>4340</v>
       </c>
       <c r="E160" s="90" t="s">
-        <v>4337</v>
+        <v>4341</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="32.25">
@@ -24579,13 +24585,13 @@
         <v>300008736</v>
       </c>
       <c r="C161" s="88" t="s">
-        <v>4338</v>
+        <v>4342</v>
       </c>
       <c r="D161" s="88" t="s">
-        <v>4339</v>
+        <v>4343</v>
       </c>
       <c r="E161" s="90" t="s">
-        <v>4340</v>
+        <v>4344</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="16.5">
@@ -24596,13 +24602,13 @@
         <v>300008697</v>
       </c>
       <c r="C162" s="88" t="s">
-        <v>4341</v>
+        <v>4345</v>
       </c>
       <c r="D162" s="88" t="s">
-        <v>4342</v>
+        <v>4346</v>
       </c>
       <c r="E162" s="90" t="s">
-        <v>4343</v>
+        <v>4347</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="32.25">
@@ -24613,13 +24619,13 @@
         <v>300008899</v>
       </c>
       <c r="C163" s="88" t="s">
-        <v>4344</v>
+        <v>4348</v>
       </c>
       <c r="D163" s="88" t="s">
-        <v>4345</v>
+        <v>4349</v>
       </c>
       <c r="E163" s="90" t="s">
-        <v>4346</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="16.5">
@@ -24630,13 +24636,13 @@
         <v>300132316</v>
       </c>
       <c r="C164" s="88" t="s">
-        <v>4347</v>
+        <v>4351</v>
       </c>
       <c r="D164" s="88" t="s">
-        <v>4348</v>
+        <v>4352</v>
       </c>
       <c r="E164" s="90" t="s">
-        <v>4349</v>
+        <v>4353</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="16.5">
@@ -24647,13 +24653,13 @@
         <v>300132315</v>
       </c>
       <c r="C165" s="88" t="s">
-        <v>4350</v>
+        <v>4354</v>
       </c>
       <c r="D165" s="88" t="s">
-        <v>4351</v>
+        <v>4355</v>
       </c>
       <c r="E165" s="90" t="s">
-        <v>4352</v>
+        <v>4356</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="16.5">
@@ -24664,13 +24670,13 @@
         <v>300008835</v>
       </c>
       <c r="C166" s="88" t="s">
-        <v>4353</v>
+        <v>4357</v>
       </c>
       <c r="D166" s="88" t="s">
-        <v>4354</v>
+        <v>4358</v>
       </c>
       <c r="E166" s="90" t="s">
-        <v>4355</v>
+        <v>4359</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="16.5">
@@ -24681,13 +24687,13 @@
         <v>300008676</v>
       </c>
       <c r="C167" s="88" t="s">
-        <v>4356</v>
+        <v>4360</v>
       </c>
       <c r="D167" s="88" t="s">
-        <v>4357</v>
+        <v>4361</v>
       </c>
       <c r="E167" s="90" t="s">
-        <v>4358</v>
+        <v>4362</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="16.5">
@@ -24698,13 +24704,13 @@
         <v>300008679</v>
       </c>
       <c r="C168" s="88" t="s">
-        <v>4359</v>
+        <v>4363</v>
       </c>
       <c r="D168" s="88" t="s">
-        <v>4360</v>
+        <v>4364</v>
       </c>
       <c r="E168" s="90" t="s">
-        <v>4361</v>
+        <v>4365</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="16.5">
@@ -24715,13 +24721,13 @@
         <v>300387217</v>
       </c>
       <c r="C169" s="88" t="s">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="D169" s="88" t="s">
-        <v>4363</v>
+        <v>4367</v>
       </c>
       <c r="E169" s="90" t="s">
-        <v>4364</v>
+        <v>4368</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="16.5">
@@ -24732,13 +24738,13 @@
         <v>300266556</v>
       </c>
       <c r="C170" s="88" t="s">
-        <v>4365</v>
+        <v>4369</v>
       </c>
       <c r="D170" s="88" t="s">
-        <v>4366</v>
+        <v>4370</v>
       </c>
       <c r="E170" s="90" t="s">
-        <v>4367</v>
+        <v>4371</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="16.5">
@@ -24749,13 +24755,13 @@
         <v>300266558</v>
       </c>
       <c r="C171" s="88" t="s">
-        <v>4368</v>
+        <v>4372</v>
       </c>
       <c r="D171" s="88" t="s">
-        <v>4369</v>
+        <v>4373</v>
       </c>
       <c r="E171" s="90" t="s">
-        <v>4370</v>
+        <v>4374</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="32.25">
@@ -24766,13 +24772,13 @@
         <v>300008687</v>
       </c>
       <c r="C172" s="88" t="s">
-        <v>4371</v>
+        <v>4375</v>
       </c>
       <c r="D172" s="88" t="s">
-        <v>4372</v>
+        <v>4376</v>
       </c>
       <c r="E172" s="90" t="s">
-        <v>4373</v>
+        <v>4377</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="32.25">
@@ -24783,13 +24789,13 @@
         <v>300008694</v>
       </c>
       <c r="C173" s="88" t="s">
-        <v>4374</v>
+        <v>4378</v>
       </c>
       <c r="D173" s="88" t="s">
-        <v>4375</v>
+        <v>4379</v>
       </c>
       <c r="E173" s="90" t="s">
-        <v>4376</v>
+        <v>4380</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="48.75">
@@ -24800,13 +24806,13 @@
         <v>300266571</v>
       </c>
       <c r="C174" s="88" t="s">
-        <v>4377</v>
+        <v>4381</v>
       </c>
       <c r="D174" s="88" t="s">
-        <v>4378</v>
+        <v>4382</v>
       </c>
       <c r="E174" s="90" t="s">
-        <v>4379</v>
+        <v>4383</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="16.5">
@@ -24817,13 +24823,13 @@
         <v>300008680</v>
       </c>
       <c r="C175" s="88" t="s">
-        <v>4380</v>
+        <v>4384</v>
       </c>
       <c r="D175" s="88" t="s">
-        <v>4381</v>
+        <v>4385</v>
       </c>
       <c r="E175" s="90" t="s">
-        <v>4382</v>
+        <v>4386</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="16.5">
@@ -24834,13 +24840,13 @@
         <v>300387029</v>
       </c>
       <c r="C176" s="88" t="s">
-        <v>4383</v>
+        <v>4387</v>
       </c>
       <c r="D176" s="88" t="s">
-        <v>4384</v>
+        <v>4388</v>
       </c>
       <c r="E176" s="90" t="s">
-        <v>4385</v>
+        <v>4389</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="16.5">
@@ -24851,13 +24857,13 @@
         <v>300185707</v>
       </c>
       <c r="C177" s="88" t="s">
-        <v>4386</v>
+        <v>4390</v>
       </c>
       <c r="D177" s="88" t="s">
-        <v>4387</v>
+        <v>4391</v>
       </c>
       <c r="E177" s="90" t="s">
-        <v>4388</v>
+        <v>4392</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="32.25">
@@ -24868,13 +24874,13 @@
         <v>300008932</v>
       </c>
       <c r="C178" s="89" t="s">
-        <v>4389</v>
+        <v>4393</v>
       </c>
       <c r="D178" s="89" t="s">
-        <v>4390</v>
+        <v>4394</v>
       </c>
       <c r="E178" s="90" t="s">
-        <v>4391</v>
+        <v>4395</v>
       </c>
     </row>
   </sheetData>
@@ -41524,64 +41530,64 @@
         <v>2371</v>
       </c>
       <c r="B62" s="193"/>
-      <c r="C62" s="292" t="s">
+      <c r="C62" s="159" t="s">
         <v>2372</v>
       </c>
-      <c r="D62" s="293"/>
+      <c r="D62" s="164"/>
       <c r="E62" s="164"/>
-      <c r="F62" s="294"/>
-      <c r="G62" s="294"/>
-      <c r="H62" s="294"/>
-      <c r="I62" s="294"/>
-      <c r="J62" s="294"/>
-      <c r="K62" s="294"/>
-      <c r="L62" s="294"/>
+      <c r="F62" s="165"/>
+      <c r="G62" s="165"/>
+      <c r="H62" s="165"/>
+      <c r="I62" s="165"/>
+      <c r="J62" s="165"/>
+      <c r="K62" s="165"/>
+      <c r="L62" s="165"/>
       <c r="M62" s="161"/>
-      <c r="N62" s="295"/>
+      <c r="N62" s="126"/>
       <c r="O62" s="162"/>
-      <c r="P62" s="295"/>
-      <c r="Q62" s="295"/>
-      <c r="R62" s="295"/>
-      <c r="S62" s="293"/>
-      <c r="T62" s="293"/>
+      <c r="P62" s="126"/>
+      <c r="Q62" s="126"/>
+      <c r="R62" s="126"/>
+      <c r="S62" s="164"/>
+      <c r="T62" s="164"/>
       <c r="U62" s="161"/>
       <c r="V62" s="161"/>
       <c r="W62" s="161"/>
       <c r="X62" s="161"/>
       <c r="Y62" s="161"/>
       <c r="Z62" s="127"/>
-      <c r="AA62" s="296" t="s">
+      <c r="AA62" s="160" t="s">
         <v>2373</v>
       </c>
       <c r="AB62" s="197"/>
-      <c r="AC62" s="296"/>
-      <c r="AD62" s="296"/>
+      <c r="AC62" s="160"/>
+      <c r="AD62" s="160"/>
       <c r="AE62" s="197"/>
-      <c r="AF62" s="296"/>
-      <c r="AG62" s="296" t="s">
+      <c r="AF62" s="160"/>
+      <c r="AG62" s="160" t="s">
         <v>2374</v>
       </c>
       <c r="AH62" s="197" t="s">
         <v>2375</v>
       </c>
-      <c r="AI62" s="296"/>
-      <c r="AJ62" s="296" t="s">
+      <c r="AI62" s="160"/>
+      <c r="AJ62" s="160" t="s">
         <v>2376</v>
       </c>
       <c r="AK62" s="197" t="s">
         <v>2375</v>
       </c>
-      <c r="AL62" s="296"/>
-      <c r="AM62" s="296" t="s">
+      <c r="AL62" s="160"/>
+      <c r="AM62" s="160" t="s">
         <v>2377</v>
       </c>
-      <c r="AN62" s="296"/>
-      <c r="AO62" s="296"/>
-      <c r="AP62" s="296"/>
-      <c r="AQ62" s="296"/>
-      <c r="AR62" s="296"/>
-      <c r="AS62" s="296"/>
-      <c r="AT62" s="296"/>
+      <c r="AN62" s="160"/>
+      <c r="AO62" s="160"/>
+      <c r="AP62" s="160"/>
+      <c r="AQ62" s="160"/>
+      <c r="AR62" s="160"/>
+      <c r="AS62" s="160"/>
+      <c r="AT62" s="160"/>
       <c r="AU62" s="133" t="s">
         <v>2378</v>
       </c>
@@ -41590,11 +41596,11 @@
       <c r="AX62" s="160" t="s">
         <v>2379</v>
       </c>
-      <c r="AY62" s="296"/>
-      <c r="AZ62" s="296"/>
-      <c r="BA62" s="296"/>
-      <c r="BB62" s="296"/>
-      <c r="BC62" s="296"/>
+      <c r="AY62" s="160"/>
+      <c r="AZ62" s="160"/>
+      <c r="BA62" s="160"/>
+      <c r="BB62" s="160"/>
+      <c r="BC62" s="160"/>
       <c r="BD62" s="205"/>
       <c r="BE62" s="132"/>
       <c r="BF62" s="132"/>
@@ -59616,19 +59622,23 @@
       <c r="M19" s="178"/>
       <c r="N19" s="178"/>
     </row>
-    <row r="20" spans="1:14" ht="16.5">
+    <row r="20" spans="1:14" ht="32.25">
       <c r="A20" s="178" t="s">
         <v>3624</v>
       </c>
-      <c r="B20" s="296" t="s">
+      <c r="B20" s="160" t="s">
         <v>2376</v>
       </c>
-      <c r="C20" s="178"/>
+      <c r="C20" s="178" t="s">
+        <v>3625</v>
+      </c>
       <c r="D20" s="178"/>
       <c r="E20" s="178"/>
       <c r="F20" s="178"/>
       <c r="G20" s="178"/>
-      <c r="H20" s="178"/>
+      <c r="H20" s="241" t="s">
+        <v>3626</v>
+      </c>
       <c r="I20" s="178"/>
       <c r="J20" s="178"/>
       <c r="K20" s="178"/>
@@ -59638,7 +59648,7 @@
     </row>
     <row r="21" spans="1:14" ht="16.5">
       <c r="A21" s="178" t="s">
-        <v>3625</v>
+        <v>3627</v>
       </c>
       <c r="B21" s="178"/>
       <c r="C21" s="178"/>
@@ -59669,7 +59679,7 @@
       <c r="F22" s="178"/>
       <c r="G22" s="178"/>
       <c r="H22" t="s">
-        <v>3626</v>
+        <v>3628</v>
       </c>
       <c r="I22" s="178"/>
       <c r="J22" s="178"/>
@@ -59680,10 +59690,10 @@
     </row>
     <row r="23" spans="1:14" ht="32.25">
       <c r="A23" s="178" t="s">
-        <v>3627</v>
+        <v>3629</v>
       </c>
       <c r="B23" s="178" t="s">
-        <v>3628</v>
+        <v>3630</v>
       </c>
       <c r="C23" s="178"/>
       <c r="D23" s="178" t="s">
@@ -59693,7 +59703,7 @@
       <c r="F23" s="178"/>
       <c r="G23" s="178"/>
       <c r="H23" s="266" t="s">
-        <v>3629</v>
+        <v>3631</v>
       </c>
       <c r="I23" s="178"/>
       <c r="J23" s="178"/>
@@ -59704,20 +59714,20 @@
     </row>
     <row r="24" spans="1:14" ht="32.25">
       <c r="A24" s="178" t="s">
-        <v>3630</v>
+        <v>3632</v>
       </c>
       <c r="B24" s="178" t="s">
-        <v>3631</v>
+        <v>3633</v>
       </c>
       <c r="C24" t="s">
-        <v>3632</v>
+        <v>3634</v>
       </c>
       <c r="D24" s="178"/>
       <c r="E24" s="178"/>
       <c r="F24" s="178"/>
       <c r="G24" s="178"/>
       <c r="H24" s="241" t="s">
-        <v>3633</v>
+        <v>3635</v>
       </c>
       <c r="I24" s="178"/>
       <c r="J24" s="178"/>
@@ -59728,7 +59738,7 @@
     </row>
     <row r="25" spans="1:14" ht="16.5">
       <c r="A25" s="178" t="s">
-        <v>3634</v>
+        <v>3636</v>
       </c>
       <c r="B25" s="178"/>
       <c r="C25" s="178"/>
@@ -59746,10 +59756,10 @@
     </row>
     <row r="26" spans="1:14" ht="16.5">
       <c r="A26" s="178" t="s">
-        <v>3635</v>
+        <v>3637</v>
       </c>
       <c r="B26" s="178" t="s">
-        <v>3636</v>
+        <v>3638</v>
       </c>
       <c r="C26" s="178"/>
       <c r="D26" s="178"/>
@@ -59766,10 +59776,10 @@
     </row>
     <row r="27" spans="1:14" ht="32.25">
       <c r="A27" s="178" t="s">
-        <v>3637</v>
+        <v>3639</v>
       </c>
       <c r="B27" s="178" t="s">
-        <v>3638</v>
+        <v>3640</v>
       </c>
       <c r="C27" s="178"/>
       <c r="D27" s="178"/>
@@ -59777,7 +59787,7 @@
       <c r="F27" s="178"/>
       <c r="G27" s="178"/>
       <c r="H27" s="241" t="s">
-        <v>3639</v>
+        <v>3641</v>
       </c>
       <c r="I27" s="178"/>
       <c r="J27" s="178"/>
@@ -59788,10 +59798,10 @@
     </row>
     <row r="28" spans="1:14" ht="32.25">
       <c r="A28" s="178" t="s">
-        <v>3640</v>
+        <v>3642</v>
       </c>
       <c r="B28" s="178" t="s">
-        <v>3641</v>
+        <v>3643</v>
       </c>
       <c r="C28" s="178"/>
       <c r="D28" s="178"/>
@@ -59799,7 +59809,7 @@
       <c r="F28" s="178"/>
       <c r="G28" s="178"/>
       <c r="H28" s="241" t="s">
-        <v>3642</v>
+        <v>3644</v>
       </c>
       <c r="I28" s="178"/>
       <c r="J28" s="178"/>
@@ -59810,10 +59820,10 @@
     </row>
     <row r="29" spans="1:14" ht="32.25">
       <c r="A29" s="178" t="s">
-        <v>3643</v>
+        <v>3645</v>
       </c>
       <c r="B29" s="178" t="s">
-        <v>3644</v>
+        <v>3646</v>
       </c>
       <c r="C29" s="178"/>
       <c r="D29" s="178"/>
@@ -59821,7 +59831,7 @@
       <c r="F29" s="178"/>
       <c r="G29" s="178"/>
       <c r="H29" s="241" t="s">
-        <v>3645</v>
+        <v>3647</v>
       </c>
       <c r="I29" s="178"/>
       <c r="J29" s="178"/>
@@ -59832,7 +59842,7 @@
     </row>
     <row r="30" spans="1:14" ht="32.25">
       <c r="A30" s="178" t="s">
-        <v>3646</v>
+        <v>3648</v>
       </c>
       <c r="B30" s="178" t="s">
         <v>1155</v>
@@ -59845,7 +59855,7 @@
       <c r="F30" s="178"/>
       <c r="G30" s="178"/>
       <c r="H30" s="266" t="s">
-        <v>3647</v>
+        <v>3649</v>
       </c>
       <c r="I30" s="178"/>
       <c r="J30" s="178"/>
@@ -59856,7 +59866,7 @@
     </row>
     <row r="31" spans="1:14" ht="32.25">
       <c r="A31" s="178" t="s">
-        <v>3648</v>
+        <v>3650</v>
       </c>
       <c r="B31" s="178" t="s">
         <v>174</v>
@@ -59869,7 +59879,7 @@
       <c r="F31" s="178"/>
       <c r="G31" s="178"/>
       <c r="H31" s="241" t="s">
-        <v>3649</v>
+        <v>3651</v>
       </c>
       <c r="I31" s="178"/>
       <c r="J31" s="178"/>
@@ -59896,7 +59906,7 @@
     </row>
     <row r="33" spans="1:14" ht="32.25">
       <c r="A33" s="178" t="s">
-        <v>3650</v>
+        <v>3652</v>
       </c>
       <c r="B33" s="178" t="s">
         <v>214</v>
@@ -59909,7 +59919,7 @@
       <c r="F33" s="178"/>
       <c r="G33" s="178"/>
       <c r="H33" s="266" t="s">
-        <v>3651</v>
+        <v>3653</v>
       </c>
       <c r="I33" s="178"/>
       <c r="J33" s="178"/>
@@ -59920,10 +59930,10 @@
     </row>
     <row r="34" spans="1:14" ht="32.25">
       <c r="A34" s="178" t="s">
-        <v>3652</v>
+        <v>3654</v>
       </c>
       <c r="B34" s="178" t="s">
-        <v>3653</v>
+        <v>3655</v>
       </c>
       <c r="C34" s="178"/>
       <c r="D34" s="178"/>
@@ -59931,7 +59941,7 @@
       <c r="F34" s="178"/>
       <c r="G34" s="178"/>
       <c r="H34" s="266" t="s">
-        <v>3654</v>
+        <v>3656</v>
       </c>
       <c r="I34" s="178"/>
       <c r="J34" s="178"/>
@@ -59940,19 +59950,21 @@
       <c r="M34" s="178"/>
       <c r="N34" s="178"/>
     </row>
-    <row r="35" spans="1:14" ht="16.5">
+    <row r="35" spans="1:14" ht="32.25">
       <c r="A35" s="178" t="s">
-        <v>3655</v>
+        <v>3657</v>
       </c>
       <c r="B35" s="178" t="s">
-        <v>3656</v>
+        <v>3658</v>
       </c>
       <c r="C35" s="178"/>
       <c r="D35" s="178"/>
       <c r="E35" s="178"/>
       <c r="F35" s="178"/>
       <c r="G35" s="178"/>
-      <c r="H35" s="266"/>
+      <c r="H35" s="292" t="s">
+        <v>3659</v>
+      </c>
       <c r="I35" s="178"/>
       <c r="J35" s="178"/>
       <c r="K35" s="178"/>
@@ -59962,13 +59974,13 @@
     </row>
     <row r="36" spans="1:14" ht="48.75">
       <c r="A36" s="178" t="s">
-        <v>3657</v>
+        <v>3660</v>
       </c>
       <c r="B36" s="178" t="s">
-        <v>3658</v>
+        <v>3661</v>
       </c>
       <c r="C36" s="178" t="s">
-        <v>3659</v>
+        <v>3662</v>
       </c>
       <c r="D36" s="178" t="s">
         <v>3180</v>
@@ -59977,7 +59989,7 @@
       <c r="F36" s="178"/>
       <c r="G36" s="178"/>
       <c r="H36" s="241" t="s">
-        <v>3660</v>
+        <v>3663</v>
       </c>
       <c r="I36" s="178"/>
       <c r="J36" s="178"/>
@@ -59988,20 +60000,20 @@
     </row>
     <row r="37" spans="1:14" ht="81">
       <c r="A37" s="178" t="s">
-        <v>3661</v>
+        <v>3664</v>
       </c>
       <c r="B37" s="178" t="s">
-        <v>3662</v>
+        <v>3665</v>
       </c>
       <c r="C37" s="178" t="s">
-        <v>3663</v>
+        <v>3666</v>
       </c>
       <c r="D37" s="178"/>
       <c r="E37" s="178"/>
       <c r="F37" s="178"/>
       <c r="G37" s="178"/>
       <c r="H37" s="266" t="s">
-        <v>3664</v>
+        <v>3667</v>
       </c>
       <c r="I37" s="178"/>
       <c r="J37" s="178"/>
@@ -60012,20 +60024,20 @@
     </row>
     <row r="38" spans="1:14" ht="32.25">
       <c r="A38" s="178" t="s">
-        <v>3665</v>
+        <v>3668</v>
       </c>
       <c r="B38" s="178" t="s">
-        <v>3666</v>
+        <v>3669</v>
       </c>
       <c r="C38" s="178" t="s">
-        <v>3667</v>
+        <v>3670</v>
       </c>
       <c r="D38" s="178"/>
       <c r="E38" s="178"/>
       <c r="F38" s="178"/>
       <c r="G38" s="178"/>
       <c r="H38" s="266" t="s">
-        <v>3668</v>
+        <v>3671</v>
       </c>
       <c r="I38" s="178"/>
       <c r="J38" s="178"/>
@@ -60036,10 +60048,10 @@
     </row>
     <row r="39" spans="1:14" ht="32.25">
       <c r="A39" s="178" t="s">
-        <v>3669</v>
+        <v>3672</v>
       </c>
       <c r="B39" s="178" t="s">
-        <v>3670</v>
+        <v>3673</v>
       </c>
       <c r="C39" s="178"/>
       <c r="D39" s="178"/>
@@ -60047,7 +60059,7 @@
       <c r="F39" s="178"/>
       <c r="G39" s="178"/>
       <c r="H39" s="266" t="s">
-        <v>3671</v>
+        <v>3674</v>
       </c>
       <c r="I39" s="178"/>
       <c r="J39" s="178"/>
@@ -60056,19 +60068,21 @@
       <c r="M39" s="178"/>
       <c r="N39" s="178"/>
     </row>
-    <row r="40" spans="1:14" ht="16.5">
+    <row r="40" spans="1:14" ht="32.25">
       <c r="A40" s="178" t="s">
-        <v>3672</v>
+        <v>3675</v>
       </c>
       <c r="B40" s="178" t="s">
-        <v>3673</v>
+        <v>3676</v>
       </c>
       <c r="C40" s="178"/>
       <c r="D40" s="178"/>
       <c r="E40" s="178"/>
       <c r="F40" s="178"/>
       <c r="G40" s="178"/>
-      <c r="H40" s="178"/>
+      <c r="H40" s="241" t="s">
+        <v>3677</v>
+      </c>
       <c r="I40" s="178"/>
       <c r="J40" s="178"/>
       <c r="K40" s="178"/>
@@ -60154,10 +60168,13 @@
     <hyperlink ref="H17" r:id="rId26" xr:uid="{72DABF36-9C87-4E52-80B5-167ABBB35160}"/>
     <hyperlink ref="H18" r:id="rId27" xr:uid="{30D89E00-7AB4-4DB0-990C-6EB06736198F}"/>
     <hyperlink ref="H14" r:id="rId28" xr:uid="{E9ECF918-A5FD-41DC-A756-FB091B6F35F9}"/>
+    <hyperlink ref="H20" r:id="rId29" xr:uid="{AB4FF3FA-6966-4A46-BB44-63D98A4A91E1}"/>
+    <hyperlink ref="H35" r:id="rId30" xr:uid="{0D5512D3-9F49-4D2E-9164-5413B56A48E8}"/>
+    <hyperlink ref="H40" r:id="rId31" xr:uid="{55D89E46-6C73-4AE8-9C16-9A316900D08D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId29"/>
+    <tablePart r:id="rId32"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/Herrnhuter NaturkundlerInnen.xlsx
+++ b/data/Herrnhuter NaturkundlerInnen.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="255" documentId="11_3A46093C230D0D87799BC6192E74F14DB86AC19C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48E75C98-99BD-4F54-B274-3DAF34D348AE}"/>
+  <xr:revisionPtr revIDLastSave="256" documentId="11_3A46093C230D0D87799BC6192E74F14DB86AC19C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B8E91AC-FC32-4F51-9ADA-A11E4CBCBFDC}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="14100" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6950,11 +6950,11 @@
 M0005100 [1814ff.: J.B.v. Albertini: Adnota ad Floram Montis Gratiarum [Gnadenberg] 1814] |
 M0005300 [1821: J.B.v. Albertini: Flora Gnadenfreisensis 1819-1821] |
 M0005200 [1842: [anonym]: Albertini’s Flora Gnadenfrei’s 1819-1821] |
-M0005400 [nach 1840: [anonym]: Flora Albertini Gnadenfreyensis (Verändert nach Cur. 4. Aufl. 1840.) |
-1821:  „Flora Gnadenfreyensis. 1819/20. 8°. Dazu: Catalogi auxiliares tres ad Fl. G.“ 2 Exemplare; a) (Mspt., datirt vom 5. Juli 1821. Mspt. Sammlung der Schles. Ges.) (Karl Gustav Limpricht: "Nachträge zu den Laub- und Lebermoosen", in: Ferdinand Cohn, Kryptogamen-Flora von Schlesien, Beslau: J.U. Kern's Verlag 1876, S. 413-444, 444, ebenfalls erwähnt in Körber: "Verzeichniss der dem Henschel'schen Globus aggregirten botanischen Manuscript-Sammlung der Schlesischen Gesellschaft", in: Bericht über die Thätigkeit der Botanischen Section der Schlesischen Gesellschaft für Vaterländische Kultur, 1871, S. 88-93, 88); b) UA, Cim.II.16. Flora Gnadenfreiensis, 1819-1821, Johann Baptist von Albertini, 3 Hefte; Gnadenfrei/ Piława Górna/ Ober-Peilau in Schlesien, 3 separate Hefte mit Signatur: Cim.II.16.I „FLORA GNADENFREIENSIS, Inde a vere 1819.“; [J.B.v. Albertini], 1819, 90 Seiten, 73 mit Text, (Stolz, 1916, 112), Cim.II.16.II „NOTAMINA ad Floram Gnadenfreiensem. Inde a vere 1819.“; [J.B.v. Albertini], 1819, 202 Seiten, dazwischen Leerseiten mit Text, gebunden (Stolz, 1916, 112), Cim.II.16.III „FLORA GNADENFREYENSIS 1819. 1820. pp.“, [J.B.v. Albertini], 1819, geheftet,Einleitung mit Angabe des Gebietes der Flora Gnadenfreiensis, und der Referenzliteratur, Gesamtbestand der Flora am „5. Jul. 1821“ 1.355 Arten, Cim.II.16.III „Diarium botanicum, numerans Stirpens quoquo die inventas.“ [Ein botanisches Tagebuch, das jeden Tag den gefundenen Bestand zählt]; lose, deutsch Aufistung Botanischer Exkursionen, mit Datum und Route und neu gefundenem Bestand, 1819, 117 Exkursionen mit 957 Arten, 1820, 90 Exkursionen mit 398 Arten plus Ergänzungen am „30.Sept. 1820“ 1354 Arten |
+M0005400 [nach 1840: [anonym]: Flora Albertini Gnadenfreyensis (Verändert nach Cur. 4. Aufl. 1840.)] |
+[1821:  „Flora Gnadenfreyensis. 1819/20. 8°. Dazu: Catalogi auxiliares tres ad Fl. G.“ 2 Exemplare; a) (Mspt., datirt vom 5. Juli 1821. Mspt. Sammlung der Schles. Ges.) (Karl Gustav Limpricht: "Nachträge zu den Laub- und Lebermoosen", in: Ferdinand Cohn, Kryptogamen-Flora von Schlesien, Beslau: J.U. Kern's Verlag 1876, S. 413-444, 444, ebenfalls erwähnt in Körber: "Verzeichniss der dem Henschel'schen Globus aggregirten botanischen Manuscript-Sammlung der Schlesischen Gesellschaft", in: Bericht über die Thätigkeit der Botanischen Section der Schlesischen Gesellschaft für Vaterländische Kultur, 1871, S. 88-93, 88); b) UA, Cim.II.16. Flora Gnadenfreiensis, 1819-1821, Johann Baptist von Albertini, 3 Hefte; Gnadenfrei/ Piława Górna/ Ober-Peilau in Schlesien, 3 separate Hefte mit Signatur: Cim.II.16.I „FLORA GNADENFREIENSIS, Inde a vere 1819.“; [J.B.v. Albertini], 1819, 90 Seiten, 73 mit Text, (Stolz, 1916, 112), Cim.II.16.II „NOTAMINA ad Floram Gnadenfreiensem. Inde a vere 1819.“; [J.B.v. Albertini], 1819, 202 Seiten, dazwischen Leerseiten mit Text, gebunden (Stolz, 1916, 112), Cim.II.16.III „FLORA GNADENFREYENSIS 1819. 1820. pp.“, [J.B.v. Albertini], 1819, geheftet,Einleitung mit Angabe des Gebietes der Flora Gnadenfreiensis, und der Referenzliteratur, Gesamtbestand der Flora am „5. Jul. 1821“ 1.355 Arten, Cim.II.16.III „Diarium botanicum, numerans Stirpens quoquo die inventas.“ [Ein botanisches Tagebuch, das jeden Tag den gefundenen Bestand zählt]; lose, deutsch Aufistung Botanischer Exkursionen, mit Datum und Route und neu gefundenem Bestand, 1819, 117 Exkursionen mit 957 Arten, 1820, 90 Exkursionen mit 398 Arten plus Ergänzungen am „30.Sept. 1820“ 1354 Arten |
 1822: Kryptogamische Gewächse um Gnadenberg, 1814-1817 und um Gnadenfrey, 1820-1821 gesammelt,  4°, Manuskr. 1822, im Archiv der Schlesischen Gesellschaft für vaterländische Cultur Breslau (erwähnt von: Körber: "Verzeichniss der dem Henschel'schen Globus aggregirten botanischen Manuscript-Sammlung der Schlesischen Gesellschaft", in: Bericht über die Thätigkeit der Botanischen Section der Schlesischen Gesellschaft für Vaterländische Kultur, 1871, S. 88-93, 88; Funkenachlass HB Dresdense Scan 10)|
 weitere Floren über Riesengebirge, Gnadenberg, Böhmische Berge, Leitmeritzer Gegend | 
-[1842] Kopien/Anschriften von Thust : UA NB VI.185.7 , Albertini: „Res Botanicae“, „Albertini’s Flora Gnadenfrei’s“, aus dem Nachlass von Thust, Absch. um 1842, Abschrift kompiliert aus: Albertini: „Flora Gnadenfreiensis, Indea vere 1819“ und Albertini: „Notamina ad Floram Gnadenfr. Indea vere 1819; 153 gez. S. plus ungez. 1 kolol. Zeichnung dat. „Okt. 1842“; UA NB VI.185.8  Albertini: „Flora Albertini Gnadenfreyensis“, Abschrift nach der 4. Aufl. 1840, aus dem Nachlass von Thust, 48 S. von 1018 Arten, plus Pilze und Vergleich Pilze Gnadenfrei und Gnadenfeld |</t>
+[1842] Kopien/Anschriften von Thust : UA NB VI.185.7 , Albertini: „Res Botanicae“, „Albertini’s Flora Gnadenfrei’s“, aus dem Nachlass von Thust, Absch. um 1842, Abschrift kompiliert aus: Albertini: „Flora Gnadenfreiensis, Indea vere 1819“ und Albertini: „Notamina ad Floram Gnadenfr. Indea vere 1819; 153 gez. S. plus ungez. 1 kolol. Zeichnung dat. „Okt. 1842“; UA NB VI.185.8  Albertini: „Flora Albertini Gnadenfreyensis“, Abschrift nach der 4. Aufl. 1840, aus dem Nachlass von Thust, 48 S. von 1018 Arten, plus Pilze und Vergleich Pilze Gnadenfrei und Gnadenfeld |]</t>
   </si>
   <si>
     <t>R0002600 [Albertini; Schweinitz: Conspectus fungorum in Lusatiae Superioris 1805] |

--- a/data/Herrnhuter NaturkundlerInnen.xlsx
+++ b/data/Herrnhuter NaturkundlerInnen.xlsx
@@ -13107,7 +13107,7 @@
     <t xml:space="preserve">Bemerkungen</t>
   </si>
   <si>
-    <t xml:space="preserve">Unitätsarchiv Herrnhut Germany</t>
+    <t xml:space="preserve">Unitätsarchiv Herrnhut (Germany)</t>
   </si>
   <si>
     <t xml:space="preserve">UA</t>
